--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="484">
   <si>
     <t>IDSocio</t>
   </si>
@@ -103,6 +103,12 @@
     <t>Rutina</t>
   </si>
   <si>
+    <t>121435</t>
+  </si>
+  <si>
+    <t>33026</t>
+  </si>
+  <si>
     <t>119059</t>
   </si>
   <si>
@@ -112,64 +118,79 @@
     <t>324484</t>
   </si>
   <si>
-    <t>33026</t>
-  </si>
-  <si>
-    <t>121435</t>
-  </si>
-  <si>
     <t>325528</t>
   </si>
   <si>
+    <t>340308</t>
+  </si>
+  <si>
+    <t>340209</t>
+  </si>
+  <si>
     <t>339391</t>
   </si>
   <si>
-    <t>340209</t>
+    <t>341327</t>
   </si>
   <si>
     <t>340380</t>
   </si>
   <si>
-    <t>340308</t>
+    <t>342109</t>
+  </si>
+  <si>
+    <t>342185</t>
+  </si>
+  <si>
+    <t>342371</t>
+  </si>
+  <si>
+    <t>342472</t>
   </si>
   <si>
     <t>340848</t>
   </si>
   <si>
-    <t>341327</t>
+    <t>343329</t>
+  </si>
+  <si>
+    <t>342672</t>
+  </si>
+  <si>
+    <t>343618</t>
+  </si>
+  <si>
+    <t>342841</t>
+  </si>
+  <si>
+    <t>342424</t>
+  </si>
+  <si>
+    <t>344232</t>
   </si>
   <si>
     <t>341431</t>
   </si>
   <si>
+    <t>342440</t>
+  </si>
+  <si>
+    <t>343047</t>
+  </si>
+  <si>
+    <t>344585</t>
+  </si>
+  <si>
+    <t>343209</t>
+  </si>
+  <si>
     <t>341769</t>
   </si>
   <si>
-    <t>342424</t>
-  </si>
-  <si>
-    <t>342185</t>
-  </si>
-  <si>
-    <t>342109</t>
-  </si>
-  <si>
-    <t>342440</t>
-  </si>
-  <si>
-    <t>342472</t>
-  </si>
-  <si>
-    <t>343047</t>
-  </si>
-  <si>
-    <t>342672</t>
-  </si>
-  <si>
-    <t>342371</t>
-  </si>
-  <si>
-    <t>342841</t>
+    <t>344208</t>
+  </si>
+  <si>
+    <t>343706</t>
   </si>
   <si>
     <t>342438</t>
@@ -178,18 +199,21 @@
     <t>342486</t>
   </si>
   <si>
-    <t>343329</t>
-  </si>
-  <si>
-    <t>343618</t>
-  </si>
-  <si>
-    <t>343706</t>
+    <t>344382</t>
+  </si>
+  <si>
+    <t>344463</t>
   </si>
   <si>
     <t>343129</t>
   </si>
   <si>
+    <t>19129</t>
+  </si>
+  <si>
+    <t>30949</t>
+  </si>
+  <si>
     <t>16768</t>
   </si>
   <si>
@@ -199,64 +223,79 @@
     <t>21423</t>
   </si>
   <si>
-    <t>30949</t>
-  </si>
-  <si>
-    <t>19129</t>
-  </si>
-  <si>
     <t>22467</t>
   </si>
   <si>
+    <t>18126</t>
+  </si>
+  <si>
+    <t>18027</t>
+  </si>
+  <si>
     <t>17209</t>
   </si>
   <si>
-    <t>18027</t>
+    <t>19145</t>
   </si>
   <si>
     <t>18198</t>
   </si>
   <si>
-    <t>18126</t>
+    <t>19927</t>
+  </si>
+  <si>
+    <t>20003</t>
+  </si>
+  <si>
+    <t>20189</t>
+  </si>
+  <si>
+    <t>20289</t>
   </si>
   <si>
     <t>18666</t>
   </si>
   <si>
-    <t>19145</t>
+    <t>21146</t>
+  </si>
+  <si>
+    <t>20489</t>
+  </si>
+  <si>
+    <t>21435</t>
+  </si>
+  <si>
+    <t>20658</t>
+  </si>
+  <si>
+    <t>20242</t>
+  </si>
+  <si>
+    <t>22049</t>
   </si>
   <si>
     <t>19249</t>
   </si>
   <si>
+    <t>20257</t>
+  </si>
+  <si>
+    <t>20864</t>
+  </si>
+  <si>
+    <t>22402</t>
+  </si>
+  <si>
+    <t>21026</t>
+  </si>
+  <si>
     <t>19587</t>
   </si>
   <si>
-    <t>20242</t>
-  </si>
-  <si>
-    <t>20003</t>
-  </si>
-  <si>
-    <t>19927</t>
-  </si>
-  <si>
-    <t>20257</t>
-  </si>
-  <si>
-    <t>20289</t>
-  </si>
-  <si>
-    <t>20864</t>
-  </si>
-  <si>
-    <t>20489</t>
-  </si>
-  <si>
-    <t>20189</t>
-  </si>
-  <si>
-    <t>20658</t>
+    <t>22025</t>
+  </si>
+  <si>
+    <t>21523</t>
   </si>
   <si>
     <t>20255</t>
@@ -265,13 +304,10 @@
     <t>20303</t>
   </si>
   <si>
-    <t>21146</t>
-  </si>
-  <si>
-    <t>21435</t>
-  </si>
-  <si>
-    <t>21523</t>
+    <t>22199</t>
+  </si>
+  <si>
+    <t>22280</t>
   </si>
   <si>
     <t>20946</t>
@@ -280,6 +316,12 @@
     <t>VILLA VERDE</t>
   </si>
   <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>HECTOR MANUEL</t>
+  </si>
+  <si>
     <t>VALERIA</t>
   </si>
   <si>
@@ -289,64 +331,73 @@
     <t>LESLYE</t>
   </si>
   <si>
-    <t>HECTOR MANUEL</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
     <t>JOHNNY</t>
   </si>
   <si>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
     <t>LUIS FERNANDO</t>
   </si>
   <si>
-    <t>RICARDO</t>
+    <t>ANGEL</t>
   </si>
   <si>
     <t>ETHAN JOAQUIN</t>
   </si>
   <si>
-    <t>JORGE</t>
+    <t>JOSE MARIA</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>VIVIAN AIMEE</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
   </si>
   <si>
     <t xml:space="preserve">NICOLAS </t>
   </si>
   <si>
-    <t>ANGEL</t>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>ANA</t>
+  </si>
+  <si>
+    <t>IAAN OCTAVIO</t>
+  </si>
+  <si>
+    <t>ZAYDA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
   </si>
   <si>
     <t>LUCIANO GUADALUPE</t>
   </si>
   <si>
+    <t>BETZY MARCELA</t>
+  </si>
+  <si>
+    <t>MARIA ANTONIA</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
     <t xml:space="preserve">JIMENA </t>
   </si>
   <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>JOSE MARIA</t>
-  </si>
-  <si>
-    <t>BETZY MARCELA</t>
-  </si>
-  <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MARIA ANTONIA</t>
-  </si>
-  <si>
-    <t>ANA</t>
-  </si>
-  <si>
-    <t>VIVIAN AIMEE</t>
-  </si>
-  <si>
-    <t>ZAYDA ELIZABETH</t>
+    <t>VICTOR ALEXIS</t>
+  </si>
+  <si>
+    <t>ALINA</t>
   </si>
   <si>
     <t>BRAYAN SALIM</t>
@@ -355,18 +406,21 @@
     <t>OSCAR</t>
   </si>
   <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>IAAN OCTAVIO</t>
-  </si>
-  <si>
-    <t>ALINA</t>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAYRA MELISSA </t>
   </si>
   <si>
     <t xml:space="preserve">ALEJANDRA </t>
   </si>
   <si>
+    <t>CAMILO</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
     <t>OLVERA</t>
   </si>
   <si>
@@ -376,61 +430,73 @@
     <t>RIOS</t>
   </si>
   <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>CAMILO</t>
-  </si>
-  <si>
     <t>AGUILA</t>
   </si>
   <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
     <t>HARO</t>
   </si>
   <si>
-    <t>CAMACHO</t>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t xml:space="preserve">ZARATE </t>
   </si>
   <si>
-    <t>FRANCO</t>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>LORETO</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>MONTALVO</t>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>REYNOSA</t>
+  </si>
+  <si>
+    <t>MERAZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>VARGAS</t>
   </si>
   <si>
+    <t xml:space="preserve">HERNANDEZ </t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>OSUNA</t>
+  </si>
+  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HERNANDEZ </t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LORETO</t>
-  </si>
-  <si>
-    <t>MERAZ</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
   </si>
   <si>
     <t xml:space="preserve">FERIA </t>
@@ -439,18 +505,21 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>REYNOSA</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
+    <t xml:space="preserve">REYES </t>
+  </si>
+  <si>
+    <t>ESCUDERO</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OVALLE</t>
+  </si>
+  <si>
     <t>MURILLO</t>
   </si>
   <si>
@@ -460,67 +529,64 @@
     <t>OLIVAS</t>
   </si>
   <si>
-    <t>OVALLE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
+    <t>DAVALOS</t>
+  </si>
+  <si>
     <t>CELIO</t>
   </si>
   <si>
+    <t>SALINAS</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>DAVALOS</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>TOPETE</t>
   </si>
   <si>
     <t>SWERRANO</t>
   </si>
   <si>
-    <t>SALINAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>GARAY</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>BARRA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>RICHKARDAY</t>
+  </si>
+  <si>
+    <t>NUÑEZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
   </si>
   <si>
     <t>URIAS</t>
   </si>
   <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TOPETE</t>
-  </si>
-  <si>
-    <t>NUÑEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>BARRA</t>
-  </si>
-  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>GARAY</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>OSUNA</t>
+    <t>CASTELLANOS</t>
   </si>
   <si>
     <t>52</t>
@@ -529,6 +595,12 @@
     <t>1</t>
   </si>
   <si>
+    <t>6865999642</t>
+  </si>
+  <si>
+    <t>6865115659</t>
+  </si>
+  <si>
     <t>6863511539</t>
   </si>
   <si>
@@ -538,64 +610,79 @@
     <t>6161286154</t>
   </si>
   <si>
-    <t>6865115659</t>
-  </si>
-  <si>
-    <t>6865999642</t>
-  </si>
-  <si>
     <t>6195092751</t>
   </si>
   <si>
+    <t>6862641945</t>
+  </si>
+  <si>
+    <t>6864221370</t>
+  </si>
+  <si>
     <t>6863360339</t>
   </si>
   <si>
-    <t>6864221370</t>
+    <t>6865534615</t>
   </si>
   <si>
     <t>6866192595</t>
   </si>
   <si>
-    <t>6862641945</t>
+    <t>6151107814</t>
+  </si>
+  <si>
+    <t>6861640070</t>
+  </si>
+  <si>
+    <t>6863890309</t>
+  </si>
+  <si>
+    <t>6861434493</t>
   </si>
   <si>
     <t>6861236171</t>
   </si>
   <si>
-    <t>6865534615</t>
+    <t>6865255663</t>
+  </si>
+  <si>
+    <t>9931258390</t>
+  </si>
+  <si>
+    <t>6862251224</t>
+  </si>
+  <si>
+    <t>6442093389</t>
+  </si>
+  <si>
+    <t>4151245575</t>
+  </si>
+  <si>
+    <t>6862316874</t>
   </si>
   <si>
     <t>6866068064</t>
   </si>
   <si>
+    <t>6862559890</t>
+  </si>
+  <si>
+    <t>6866017324</t>
+  </si>
+  <si>
+    <t>6862147023</t>
+  </si>
+  <si>
+    <t>6862308375</t>
+  </si>
+  <si>
     <t>6862828171</t>
   </si>
   <si>
-    <t>4151245575</t>
-  </si>
-  <si>
-    <t>6861640070</t>
-  </si>
-  <si>
-    <t>6151107814</t>
-  </si>
-  <si>
-    <t>6862559890</t>
-  </si>
-  <si>
-    <t>6861434493</t>
-  </si>
-  <si>
-    <t>6866017324</t>
-  </si>
-  <si>
-    <t>9931258390</t>
-  </si>
-  <si>
-    <t>6863890309</t>
-  </si>
-  <si>
-    <t>6442093389</t>
+    <t>6865624438</t>
+  </si>
+  <si>
+    <t>6862400244</t>
   </si>
   <si>
     <t>6861320570</t>
@@ -604,18 +691,21 @@
     <t>6641882731</t>
   </si>
   <si>
-    <t>6865255663</t>
-  </si>
-  <si>
-    <t>6862251224</t>
-  </si>
-  <si>
-    <t>6862400244</t>
+    <t>6861853385</t>
+  </si>
+  <si>
+    <t>6862890006</t>
   </si>
   <si>
     <t>6863095804</t>
   </si>
   <si>
+    <t>AV SIDENITA</t>
+  </si>
+  <si>
+    <t>MONTE BLANCO 3872</t>
+  </si>
+  <si>
     <t>CARPATOS</t>
   </si>
   <si>
@@ -625,45 +715,51 @@
     <t>AV DEL JILGUERO 1052</t>
   </si>
   <si>
-    <t>MONTE BLANCO 3872</t>
-  </si>
-  <si>
-    <t>AV SIDENITA</t>
+    <t>N</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>ALARCOS 3576</t>
   </si>
   <si>
-    <t>C</t>
+    <t>AVENIDA SAN PEDRO MEZQUITL</t>
   </si>
   <si>
     <t>DSFH</t>
   </si>
   <si>
+    <t>RIO CAOCA 3556</t>
+  </si>
+  <si>
     <t>AV CASCADA SAN ANDRES 4039</t>
   </si>
   <si>
-    <t>AVENIDA SAN PEDRO MEZQUITL</t>
-  </si>
-  <si>
-    <t>RIO CAOCA 3556</t>
+    <t>RUISEÑORES</t>
   </si>
   <si>
     <t>FRANCISCO BARRIOS</t>
   </si>
   <si>
+    <t>MONTE BLANCO</t>
+  </si>
+  <si>
     <t>Femenino</t>
   </si>
   <si>
     <t>Masculino</t>
   </si>
   <si>
+    <t>20-12-2003</t>
+  </si>
+  <si>
+    <t>22-07-1973</t>
+  </si>
+  <si>
     <t>20-08-2005</t>
   </si>
   <si>
@@ -673,64 +769,79 @@
     <t>30-10-1995</t>
   </si>
   <si>
-    <t>22-07-1973</t>
-  </si>
-  <si>
-    <t>20-12-2003</t>
-  </si>
-  <si>
     <t>04-06-1973</t>
   </si>
   <si>
+    <t>10-02-1977</t>
+  </si>
+  <si>
+    <t>13-08-2003</t>
+  </si>
+  <si>
     <t>16-05-2009</t>
   </si>
   <si>
-    <t>13-08-2003</t>
+    <t>27-01-2000</t>
   </si>
   <si>
     <t>15-07-2002</t>
   </si>
   <si>
-    <t>10-02-1977</t>
+    <t>06-03-2009</t>
+  </si>
+  <si>
+    <t>18-05-1961</t>
+  </si>
+  <si>
+    <t>20-06-2010</t>
+  </si>
+  <si>
+    <t>10-04-1980</t>
   </si>
   <si>
     <t>17-11-2007</t>
   </si>
   <si>
-    <t>27-01-2000</t>
+    <t>22-12-1995</t>
+  </si>
+  <si>
+    <t>03-06-1988</t>
+  </si>
+  <si>
+    <t>03-01-2009</t>
+  </si>
+  <si>
+    <t>18-04-2008</t>
+  </si>
+  <si>
+    <t>15-07-1997</t>
+  </si>
+  <si>
+    <t>02-06-2000</t>
   </si>
   <si>
     <t>27-10-1987</t>
   </si>
   <si>
+    <t>21-06-1992</t>
+  </si>
+  <si>
+    <t>22-09-1969</t>
+  </si>
+  <si>
+    <t>29-08-1994</t>
+  </si>
+  <si>
+    <t>31-01-2009</t>
+  </si>
+  <si>
     <t>31-08-2007</t>
   </si>
   <si>
-    <t>15-07-1997</t>
-  </si>
-  <si>
-    <t>18-05-1961</t>
-  </si>
-  <si>
-    <t>06-03-2009</t>
-  </si>
-  <si>
-    <t>21-06-1992</t>
-  </si>
-  <si>
-    <t>10-04-1980</t>
-  </si>
-  <si>
-    <t>22-09-1969</t>
-  </si>
-  <si>
-    <t>03-06-1988</t>
-  </si>
-  <si>
-    <t>20-06-2010</t>
-  </si>
-  <si>
-    <t>18-04-2008</t>
+    <t>07-04-2010</t>
+  </si>
+  <si>
+    <t>04-10-2006</t>
   </si>
   <si>
     <t>12-10-2002</t>
@@ -739,18 +850,21 @@
     <t>15-11-1988</t>
   </si>
   <si>
-    <t>22-12-1995</t>
-  </si>
-  <si>
-    <t>03-01-2009</t>
-  </si>
-  <si>
-    <t>04-10-2006</t>
+    <t>23-02-1985</t>
+  </si>
+  <si>
+    <t>08-04-2005</t>
   </si>
   <si>
     <t>13-05-2006</t>
   </si>
   <si>
+    <t>KARLACAMILO2003@ICLOUD.COM</t>
+  </si>
+  <si>
+    <t>HECTOR30@GMAIL.COM</t>
+  </si>
+  <si>
     <t>OLVERAVALERIA322@GMAIL.COM</t>
   </si>
   <si>
@@ -760,64 +874,79 @@
     <t>OLIVASLESLYE2@GMAIL.COM</t>
   </si>
   <si>
-    <t>HECTOR30@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>KARLACAMILO2003@ICLOUD.COM</t>
-  </si>
-  <si>
     <t>JONNY.AGUILA@GMAIL.COM</t>
   </si>
   <si>
+    <t>JIMMYSDF39@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>RICHI.CAMACHO20@GMAIL.COM</t>
+  </si>
+  <si>
     <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
   </si>
   <si>
-    <t>RICHI.CAMACHO20@GMAIL.COM</t>
+    <t>GLITCH0127@GMAIL.COM</t>
   </si>
   <si>
     <t>ETHAN.ZARATE@UABC.EDU.MX</t>
   </si>
   <si>
-    <t>JIMMYSDF39@GMAIL.COM</t>
+    <t>JC7651065@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CHUCHUNEL61@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VIVIANAIMEELORETO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALEJANDROROBLESJART@GMAIL.COM</t>
   </si>
   <si>
     <t>TORRES.NICOLAS2007@GAMIL.COM</t>
   </si>
   <si>
-    <t>GLITCH0127@GMAIL.COM</t>
+    <t>KIMBERLYCKIMO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CORREOPENDIENTE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CARRILLOIAAN@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ZAYDABARRA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
   </si>
   <si>
     <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
   </si>
   <si>
+    <t>BETZY.OMARCE21@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MAALIN_22@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>JR21675@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>EDWSUCOR@GMAIL.COM</t>
+  </si>
+  <si>
     <t>J0802562@GMAIL.COM</t>
   </si>
   <si>
-    <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CHUCHUNEL61@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JC7651065@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>BETZY.OMARCE21@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ALEJANDROROBLESJART@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>MAALIN_22@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>CORREOPENDIENTE@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>VIVIANAIMEELORETO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ZAYDABARRA@GMAIL.COM</t>
+    <t>5624438@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALINITA292@GMAIL.COM</t>
   </si>
   <si>
     <t>SALIMSOTO17@GMAIL.COM</t>
@@ -826,18 +955,21 @@
     <t>OSCAR.88GV@GMAIL.COM</t>
   </si>
   <si>
-    <t>KIMBERLYCKIMO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CARRILLOIAAN@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ALINITA292@GMAIL.COM</t>
+    <t>JULIOREYESS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MAYRAESC@GMAIL.COM</t>
   </si>
   <si>
     <t>ALEJANDRA13@GMAIL.COM</t>
   </si>
   <si>
+    <t>07-09-2022 17:16:11</t>
+  </si>
+  <si>
+    <t>28-06-2021 08:27:50</t>
+  </si>
+  <si>
     <t>29-08-2022 17:00:29</t>
   </si>
   <si>
@@ -847,64 +979,79 @@
     <t>20-11-2025 10:11:37</t>
   </si>
   <si>
-    <t>28-06-2021 08:27:50</t>
-  </si>
-  <si>
-    <t>07-09-2022 17:16:11</t>
-  </si>
-  <si>
     <t>26-11-2025 18:16:09</t>
   </si>
   <si>
+    <t>02-02-2026 17:24:44</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:23:20</t>
+  </si>
+  <si>
     <t>30-01-2026 16:25:54</t>
   </si>
   <si>
-    <t>02-02-2026 15:23:20</t>
+    <t>05-02-2026 14:43:26</t>
   </si>
   <si>
     <t>02-02-2026 19:54:30</t>
   </si>
   <si>
-    <t>02-02-2026 17:24:44</t>
+    <t>09-02-2026 11:19:55</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:42:28</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:09:38</t>
+  </si>
+  <si>
+    <t>09-02-2026 20:01:55</t>
   </si>
   <si>
     <t>04-02-2026 04:56:34</t>
   </si>
   <si>
-    <t>05-02-2026 14:43:26</t>
+    <t>12-02-2026 17:11:31</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:33:08</t>
+  </si>
+  <si>
+    <t>13-02-2026 21:07:16</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:33:16</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:07:14</t>
+  </si>
+  <si>
+    <t>16-02-2026 17:42:45</t>
   </si>
   <si>
     <t>05-02-2026 19:00:48</t>
   </si>
   <si>
+    <t>09-02-2026 19:28:04</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:49:30</t>
+  </si>
+  <si>
+    <t>17-02-2026 16:52:54</t>
+  </si>
+  <si>
+    <t>12-02-2026 10:56:58</t>
+  </si>
+  <si>
     <t>07-02-2026 09:15:00</t>
   </si>
   <si>
-    <t>09-02-2026 19:07:14</t>
-  </si>
-  <si>
-    <t>09-02-2026 14:42:28</t>
-  </si>
-  <si>
-    <t>09-02-2026 11:19:55</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:28:04</t>
-  </si>
-  <si>
-    <t>09-02-2026 20:01:55</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:49:30</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:33:08</t>
-  </si>
-  <si>
-    <t>09-02-2026 18:09:38</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:33:16</t>
+    <t>16-02-2026 17:19:52</t>
+  </si>
+  <si>
+    <t>14-02-2026 11:17:39</t>
   </si>
   <si>
     <t>09-02-2026 19:20:31</t>
@@ -913,13 +1060,10 @@
     <t>09-02-2026 20:25:31</t>
   </si>
   <si>
-    <t>12-02-2026 17:11:31</t>
-  </si>
-  <si>
-    <t>13-02-2026 21:07:16</t>
-  </si>
-  <si>
-    <t>14-02-2026 11:17:39</t>
+    <t>17-02-2026 06:30:32</t>
+  </si>
+  <si>
+    <t>17-02-2026 12:05:45</t>
   </si>
   <si>
     <t>11-02-2026 20:04:50</t>
@@ -928,33 +1072,48 @@
     <t>Tarifas 2026 LE</t>
   </si>
   <si>
+    <t>inscripcion promo 199</t>
+  </si>
+  <si>
+    <t>Forzoso</t>
+  </si>
+  <si>
     <t>Sin contrato</t>
   </si>
   <si>
-    <t>Forzoso</t>
+    <t>PROMO FEBRERO 12 MESES</t>
   </si>
   <si>
     <t>CONVENIOS $549</t>
   </si>
   <si>
-    <t>PROMO FEBRERO 12 MESES</t>
+    <t>1 MES $899</t>
   </si>
   <si>
     <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
   </si>
   <si>
-    <t>1 MES $899</t>
+    <t>3 MESES $1,899</t>
+  </si>
+  <si>
+    <t>499</t>
   </si>
   <si>
     <t>549</t>
   </si>
   <si>
-    <t>499</t>
-  </si>
-  <si>
     <t>899</t>
   </si>
   <si>
+    <t>633</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:10:39</t>
+  </si>
+  <si>
+    <t>06-02-2026 08:23:55</t>
+  </si>
+  <si>
     <t>03-02-2026 16:23:07</t>
   </si>
   <si>
@@ -964,64 +1123,79 @@
     <t>14-02-2026 09:47:10</t>
   </si>
   <si>
-    <t>06-02-2026 08:23:55</t>
-  </si>
-  <si>
-    <t>03-02-2026 17:10:39</t>
-  </si>
-  <si>
     <t>10-02-2026 06:46:00</t>
   </si>
   <si>
+    <t>02-02-2026 17:34:10</t>
+  </si>
+  <si>
+    <t>04-02-2026 15:47:22</t>
+  </si>
+  <si>
     <t>03-02-2026 11:38:00</t>
   </si>
   <si>
-    <t>04-02-2026 15:47:22</t>
+    <t>05-02-2026 14:49:36</t>
   </si>
   <si>
     <t>02-02-2026 19:59:58</t>
   </si>
   <si>
-    <t>02-02-2026 17:34:10</t>
+    <t>13-02-2026 11:22:23</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:44:26</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:20:05</t>
+  </si>
+  <si>
+    <t>09-02-2026 20:06:47</t>
   </si>
   <si>
     <t>06-02-2026 05:01:48</t>
   </si>
   <si>
-    <t>05-02-2026 14:49:36</t>
+    <t>12-02-2026 17:19:12</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:37:35</t>
+  </si>
+  <si>
+    <t>13-02-2026 21:10:08</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:37:59</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:10:59</t>
+  </si>
+  <si>
+    <t>17-02-2026 19:32:54</t>
   </si>
   <si>
     <t>09-02-2026 17:50:19</t>
   </si>
   <si>
+    <t>09-02-2026 19:29:53</t>
+  </si>
+  <si>
+    <t>14-02-2026 08:55:57</t>
+  </si>
+  <si>
+    <t>17-02-2026 16:54:41</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:53:04</t>
+  </si>
+  <si>
     <t>07-02-2026 09:21:40</t>
   </si>
   <si>
-    <t>09-02-2026 19:10:59</t>
-  </si>
-  <si>
-    <t>09-02-2026 14:44:26</t>
-  </si>
-  <si>
-    <t>13-02-2026 11:22:23</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:29:53</t>
-  </si>
-  <si>
-    <t>09-02-2026 20:06:47</t>
-  </si>
-  <si>
-    <t>14-02-2026 08:55:57</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:37:35</t>
-  </si>
-  <si>
-    <t>09-02-2026 18:20:05</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:37:59</t>
+    <t>16-02-2026 17:23:38</t>
+  </si>
+  <si>
+    <t>14-02-2026 11:24:40</t>
   </si>
   <si>
     <t>09-02-2026 19:23:06</t>
@@ -1030,13 +1204,10 @@
     <t>09-02-2026 20:34:45</t>
   </si>
   <si>
-    <t>12-02-2026 17:19:12</t>
-  </si>
-  <si>
-    <t>13-02-2026 21:10:08</t>
-  </si>
-  <si>
-    <t>14-02-2026 11:24:40</t>
+    <t>17-02-2026 06:36:06</t>
+  </si>
+  <si>
+    <t>17-02-2026 12:13:51</t>
   </si>
   <si>
     <t>11-02-2026 20:09:00</t>
@@ -1045,82 +1216,100 @@
     <t>03-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>06-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>14-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>06-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>10-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>02-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>04-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>02-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>05-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>13-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>09-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>12-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>17-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>17-05-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>07-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>13-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>12-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>11-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>03-02-2026 17:08:49</t>
+  </si>
+  <si>
+    <t>06-02-2026 08:22:42</t>
+  </si>
+  <si>
     <t>03-02-2026 13:06:24</t>
   </si>
   <si>
     <t>14-02-2026 09:46:17</t>
   </si>
   <si>
-    <t>06-02-2026 08:22:42</t>
-  </si>
-  <si>
-    <t>03-02-2026 17:08:49</t>
+    <t>02-02-2026 17:33:28</t>
+  </si>
+  <si>
+    <t>05-02-2026 14:49:16</t>
   </si>
   <si>
     <t>02-02-2026 19:58:03</t>
   </si>
   <si>
-    <t>02-02-2026 17:33:28</t>
+    <t>09-02-2026 18:19:25</t>
   </si>
   <si>
     <t>06-02-2026 05:01:07</t>
   </si>
   <si>
-    <t>05-02-2026 14:49:16</t>
+    <t>12-02-2026 17:18:19</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:36:57</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:37:25</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:10:20</t>
   </si>
   <si>
     <t>09-02-2026 17:49:53</t>
   </si>
   <si>
+    <t>14-02-2026 08:55:02</t>
+  </si>
+  <si>
     <t>07-02-2026 09:20:44</t>
   </si>
   <si>
-    <t>09-02-2026 19:10:20</t>
-  </si>
-  <si>
-    <t>14-02-2026 08:55:02</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:36:57</t>
-  </si>
-  <si>
-    <t>09-02-2026 18:19:25</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:37:25</t>
+    <t>16-02-2026 17:22:53</t>
+  </si>
+  <si>
+    <t>14-02-2026 11:24:09</t>
   </si>
   <si>
     <t>09-02-2026 19:22:51</t>
@@ -1129,15 +1318,18 @@
     <t>09-02-2026 20:33:58</t>
   </si>
   <si>
-    <t>12-02-2026 17:18:19</t>
-  </si>
-  <si>
-    <t>14-02-2026 11:24:09</t>
+    <t>17-02-2026 06:34:33</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>26030522048250001473</t>
+  </si>
+  <si>
+    <t>26020522131750001322</t>
+  </si>
+  <si>
     <t>26030522045250001467</t>
   </si>
   <si>
@@ -1147,64 +1339,79 @@
     <t>26150522345040001698</t>
   </si>
   <si>
-    <t>26020522131750001322</t>
-  </si>
-  <si>
-    <t>26030522048250001473</t>
-  </si>
-  <si>
     <t>26020522223470000776</t>
   </si>
   <si>
+    <t>26020522018870001160</t>
+  </si>
+  <si>
+    <t>26020522078020001242</t>
+  </si>
+  <si>
     <t>26020522037270001186</t>
   </si>
   <si>
-    <t>26020522078020001242</t>
+    <t>26020522107360001285</t>
   </si>
   <si>
     <t>26020522022780001167</t>
   </si>
   <si>
-    <t>26020522018870001160</t>
+    <t>26020522318800000908</t>
+  </si>
+  <si>
+    <t>26020522193750000724</t>
+  </si>
+  <si>
+    <t>26020522206580000736</t>
+  </si>
+  <si>
+    <t>26020522212980000757</t>
   </si>
   <si>
     <t>26020522121930001316</t>
   </si>
   <si>
-    <t>26020522107360001285</t>
+    <t>26020522299590000883</t>
+  </si>
+  <si>
+    <t>26020522234930000790</t>
+  </si>
+  <si>
+    <t>26020522331740000929</t>
+  </si>
+  <si>
+    <t>26020522247350000807</t>
+  </si>
+  <si>
+    <t>26020522209900000743</t>
+  </si>
+  <si>
+    <t>26020522444580001061</t>
   </si>
   <si>
     <t>26010522204130003399</t>
   </si>
   <si>
+    <t>26020522210970000750</t>
+  </si>
+  <si>
+    <t>26020522344200000936</t>
+  </si>
+  <si>
+    <t>26020522435540001049</t>
+  </si>
+  <si>
+    <t>26020522389340000968</t>
+  </si>
+  <si>
     <t>26020522157150000681</t>
   </si>
   <si>
-    <t>26020522209900000743</t>
-  </si>
-  <si>
-    <t>26020522193750000724</t>
-  </si>
-  <si>
-    <t>26020522318800000908</t>
-  </si>
-  <si>
-    <t>26020522210970000750</t>
-  </si>
-  <si>
-    <t>26020522212980000757</t>
-  </si>
-  <si>
-    <t>26020522344200000936</t>
-  </si>
-  <si>
-    <t>26020522234930000790</t>
-  </si>
-  <si>
-    <t>26020522206580000736</t>
-  </si>
-  <si>
-    <t>26020522247350000807</t>
+    <t>26020522399070000985</t>
+  </si>
+  <si>
+    <t>26020522347310000939</t>
   </si>
   <si>
     <t>26020522210660000748</t>
@@ -1213,13 +1420,10 @@
     <t>26020522213890000759</t>
   </si>
   <si>
-    <t>26020522299590000883</t>
-  </si>
-  <si>
-    <t>26020522331740000929</t>
-  </si>
-  <si>
-    <t>26020522347310000939</t>
+    <t>26020522419620001023</t>
+  </si>
+  <si>
+    <t>26020522426030001036</t>
   </si>
   <si>
     <t>26020522277990000848</t>
@@ -1228,6 +1432,9 @@
     <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
   </si>
   <si>
+    <t>PASE 2 DÍAS GRATIS WEB</t>
+  </si>
+  <si>
     <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
   </si>
   <si>
@@ -1237,6 +1444,9 @@
     <t>MAGALI  ROJAS RIVAS</t>
   </si>
   <si>
+    <t>1899</t>
+  </si>
+  <si>
     <t>N/D</t>
   </si>
   <si>
@@ -1244,6 +1454,9 @@
   </si>
   <si>
     <t>Arturo Israel  Flores Oronia</t>
+  </si>
+  <si>
+    <t>Eliazar Flores Vargas</t>
   </si>
   <si>
     <t>Manuel Moreno Del Bosque</t>
@@ -1610,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -1707,76 +1920,79 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="F2" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="G2" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="I2" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="J2" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K2" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="L2" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="M2" t="s">
-        <v>274</v>
-      </c>
-      <c r="N2" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="O2" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="P2" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="Q2" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="R2" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="S2" t="s">
-        <v>342</v>
+        <v>399</v>
+      </c>
+      <c r="T2" t="s">
+        <v>414</v>
       </c>
       <c r="U2" t="s">
-        <v>373</v>
+        <v>435</v>
+      </c>
+      <c r="V2" t="s">
+        <v>192</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>374</v>
+        <v>436</v>
       </c>
       <c r="AA2" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="AB2" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC2" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -1784,79 +2000,79 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="G3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H3" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="I3" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="J3" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K3" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="L3" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="M3" t="s">
-        <v>275</v>
+        <v>317</v>
       </c>
       <c r="O3" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P3" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q3" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R3" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="S3" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="T3" t="s">
-        <v>354</v>
+        <v>415</v>
       </c>
       <c r="U3" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V3" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>375</v>
+        <v>437</v>
       </c>
       <c r="AA3" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB3" t="s">
-        <v>408</v>
+        <v>477</v>
       </c>
       <c r="AC3" t="s">
-        <v>412</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -1864,85 +2080,76 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H4" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="I4" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="J4" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K4" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="L4" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="M4" t="s">
-        <v>276</v>
+        <v>318</v>
+      </c>
+      <c r="N4" t="s">
+        <v>351</v>
       </c>
       <c r="O4" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="P4" t="s">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="Q4" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="R4" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="S4" t="s">
-        <v>343</v>
-      </c>
-      <c r="T4" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="U4" t="s">
-        <v>373</v>
-      </c>
-      <c r="V4" t="s">
-        <v>170</v>
+        <v>435</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>376</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="AA4" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="AB4" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC4" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1950,79 +2157,79 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F5" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="G5" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H5" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="I5" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="J5" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K5" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="L5" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="M5" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="O5" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P5" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q5" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R5" t="s">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="S5" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T5" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="U5" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V5" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>377</v>
+        <v>439</v>
       </c>
       <c r="AA5" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB5" t="s">
-        <v>407</v>
+        <v>478</v>
       </c>
       <c r="AC5" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2030,79 +2237,85 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="F6" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="G6" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H6" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="I6" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="J6" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K6" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="L6" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="M6" t="s">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="O6" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P6" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q6" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R6" t="s">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="S6" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
       <c r="T6" t="s">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="U6" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V6" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>378</v>
+        <v>440</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>473</v>
       </c>
       <c r="AA6" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB6" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC6" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -2110,79 +2323,79 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F7" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="G7" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="H7" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="J7" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K7" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="L7" t="s">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="M7" t="s">
-        <v>279</v>
+        <v>321</v>
       </c>
       <c r="N7" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="O7" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="P7" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
       <c r="Q7" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="R7" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
       <c r="S7" t="s">
-        <v>345</v>
+        <v>402</v>
       </c>
       <c r="U7" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>379</v>
+        <v>441</v>
       </c>
       <c r="Y7" t="s">
-        <v>403</v>
+        <v>471</v>
       </c>
       <c r="Z7" t="s">
-        <v>404</v>
+        <v>473</v>
       </c>
       <c r="AA7" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="AB7" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC7" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -2190,79 +2403,79 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="F8" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="G8" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H8" t="s">
-        <v>177</v>
+        <v>199</v>
+      </c>
+      <c r="I8" t="s">
+        <v>233</v>
       </c>
       <c r="J8" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K8" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="L8" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="M8" t="s">
-        <v>280</v>
-      </c>
-      <c r="N8" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="O8" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="P8" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="Q8" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="R8" t="s">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="S8" t="s">
-        <v>342</v>
+        <v>403</v>
+      </c>
+      <c r="T8" t="s">
+        <v>418</v>
       </c>
       <c r="U8" t="s">
-        <v>170</v>
+        <v>435</v>
+      </c>
+      <c r="V8" t="s">
+        <v>192</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>380</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>404</v>
+        <v>442</v>
       </c>
       <c r="AA8" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="AB8" t="s">
-        <v>407</v>
+        <v>479</v>
       </c>
       <c r="AC8" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -2270,79 +2483,79 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F9" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="G9" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H9" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="J9" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K9" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="L9" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
       <c r="M9" t="s">
-        <v>281</v>
+        <v>323</v>
       </c>
       <c r="N9" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="O9" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="P9" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
       <c r="Q9" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="R9" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="S9" t="s">
-        <v>346</v>
+        <v>404</v>
       </c>
       <c r="U9" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>381</v>
+        <v>443</v>
       </c>
       <c r="Y9" t="s">
-        <v>403</v>
+        <v>471</v>
       </c>
       <c r="Z9" t="s">
-        <v>404</v>
+        <v>473</v>
       </c>
       <c r="AA9" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="AB9" t="s">
-        <v>409</v>
+        <v>479</v>
       </c>
       <c r="AC9" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -2350,79 +2563,79 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="F10" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="G10" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="J10" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K10" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="L10" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="M10" t="s">
-        <v>282</v>
+        <v>324</v>
+      </c>
+      <c r="N10" t="s">
+        <v>351</v>
       </c>
       <c r="O10" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="P10" t="s">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="Q10" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="R10" t="s">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="S10" t="s">
-        <v>347</v>
-      </c>
-      <c r="T10" t="s">
-        <v>358</v>
+        <v>399</v>
       </c>
       <c r="U10" t="s">
-        <v>373</v>
-      </c>
-      <c r="V10" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>382</v>
+        <v>444</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>473</v>
       </c>
       <c r="AA10" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="AB10" t="s">
-        <v>407</v>
+        <v>480</v>
       </c>
       <c r="AC10" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -2430,79 +2643,79 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="F11" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="G11" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H11" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="I11" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="J11" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K11" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="L11" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="M11" t="s">
-        <v>283</v>
+        <v>325</v>
       </c>
       <c r="O11" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P11" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q11" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R11" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="S11" t="s">
-        <v>347</v>
+        <v>405</v>
       </c>
       <c r="T11" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="U11" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V11" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>383</v>
+        <v>445</v>
       </c>
       <c r="AA11" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB11" t="s">
-        <v>409</v>
+        <v>478</v>
       </c>
       <c r="AC11" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -2510,85 +2723,79 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="G12" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H12" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="I12" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="J12" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K12" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="L12" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="M12" t="s">
-        <v>284</v>
+        <v>326</v>
       </c>
       <c r="O12" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P12" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q12" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R12" t="s">
-        <v>323</v>
+        <v>374</v>
       </c>
       <c r="S12" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="T12" t="s">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="U12" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V12" t="s">
-        <v>373</v>
+        <v>192</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>384</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="AA12" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB12" t="s">
-        <v>407</v>
+        <v>479</v>
       </c>
       <c r="AC12" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -2596,79 +2803,79 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F13" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="G13" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H13" t="s">
-        <v>182</v>
-      </c>
-      <c r="I13" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J13" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K13" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="L13" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="M13" t="s">
-        <v>285</v>
+        <v>327</v>
+      </c>
+      <c r="N13" t="s">
+        <v>351</v>
       </c>
       <c r="O13" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="P13" t="s">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="Q13" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="R13" t="s">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c r="S13" t="s">
-        <v>348</v>
-      </c>
-      <c r="T13" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="U13" t="s">
-        <v>373</v>
-      </c>
-      <c r="V13" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>385</v>
+        <v>447</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>474</v>
       </c>
       <c r="AA13" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="AB13" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC13" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -2676,85 +2883,73 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="G14" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H14" t="s">
-        <v>183</v>
-      </c>
-      <c r="I14" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J14" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K14" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="L14" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="M14" t="s">
-        <v>286</v>
+        <v>328</v>
+      </c>
+      <c r="N14" t="s">
+        <v>351</v>
       </c>
       <c r="O14" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="P14" t="s">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="Q14" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="R14" t="s">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="S14" t="s">
-        <v>349</v>
-      </c>
-      <c r="T14" t="s">
-        <v>362</v>
+        <v>407</v>
       </c>
       <c r="U14" t="s">
-        <v>373</v>
-      </c>
-      <c r="V14" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>386</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="AA14" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="AB14" t="s">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="AC14" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -2762,79 +2957,79 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F15" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="G15" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H15" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="I15" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="J15" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K15" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="L15" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="M15" t="s">
-        <v>287</v>
+        <v>329</v>
       </c>
       <c r="O15" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P15" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q15" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R15" t="s">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="S15" t="s">
-        <v>350</v>
+        <v>407</v>
       </c>
       <c r="T15" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="U15" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V15" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>387</v>
+        <v>449</v>
       </c>
       <c r="AA15" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB15" t="s">
-        <v>407</v>
+        <v>479</v>
       </c>
       <c r="AC15" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2842,79 +3037,73 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F16" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="G16" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H16" t="s">
-        <v>185</v>
-      </c>
-      <c r="I16" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J16" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K16" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="L16" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="M16" t="s">
-        <v>288</v>
+        <v>330</v>
+      </c>
+      <c r="N16" t="s">
+        <v>351</v>
       </c>
       <c r="O16" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="P16" t="s">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="Q16" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="R16" t="s">
-        <v>327</v>
+        <v>378</v>
       </c>
       <c r="S16" t="s">
-        <v>349</v>
-      </c>
-      <c r="T16" t="s">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="U16" t="s">
-        <v>373</v>
-      </c>
-      <c r="V16" t="s">
-        <v>170</v>
+        <v>435</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>388</v>
+        <v>450</v>
       </c>
       <c r="AA16" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="AB16" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
       <c r="AC16" t="s">
-        <v>412</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2922,73 +3111,85 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F17" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="G17" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H17" t="s">
-        <v>186</v>
+        <v>208</v>
+      </c>
+      <c r="I17" t="s">
+        <v>236</v>
       </c>
       <c r="J17" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="K17" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="L17" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="M17" t="s">
-        <v>289</v>
-      </c>
-      <c r="N17" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="O17" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="P17" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="Q17" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="R17" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="S17" t="s">
-        <v>349</v>
+        <v>400</v>
+      </c>
+      <c r="T17" t="s">
+        <v>422</v>
       </c>
       <c r="U17" t="s">
-        <v>170</v>
+        <v>435</v>
+      </c>
+      <c r="V17" t="s">
+        <v>435</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>389</v>
+        <v>451</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>474</v>
       </c>
       <c r="AA17" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="AB17" t="s">
-        <v>408</v>
+        <v>480</v>
       </c>
       <c r="AC17" t="s">
-        <v>412</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2996,79 +3197,79 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="F18" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G18" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H18" t="s">
-        <v>187</v>
+        <v>209</v>
+      </c>
+      <c r="I18" t="s">
+        <v>233</v>
       </c>
       <c r="J18" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="K18" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="L18" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="M18" t="s">
-        <v>290</v>
-      </c>
-      <c r="N18" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="O18" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="P18" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="Q18" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="R18" t="s">
-        <v>329</v>
+        <v>380</v>
       </c>
       <c r="S18" t="s">
-        <v>351</v>
+        <v>408</v>
+      </c>
+      <c r="T18" t="s">
+        <v>423</v>
       </c>
       <c r="U18" t="s">
-        <v>170</v>
+        <v>435</v>
+      </c>
+      <c r="V18" t="s">
+        <v>192</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>390</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>405</v>
+        <v>452</v>
       </c>
       <c r="AA18" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="AB18" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC18" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -3076,73 +3277,79 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="F19" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="G19" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H19" t="s">
-        <v>188</v>
+        <v>210</v>
+      </c>
+      <c r="I19" t="s">
+        <v>233</v>
       </c>
       <c r="J19" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K19" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="L19" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="M19" t="s">
-        <v>291</v>
-      </c>
-      <c r="N19" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="O19" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="P19" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="Q19" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="R19" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="S19" t="s">
-        <v>349</v>
+        <v>402</v>
+      </c>
+      <c r="T19" t="s">
+        <v>424</v>
       </c>
       <c r="U19" t="s">
-        <v>373</v>
+        <v>435</v>
+      </c>
+      <c r="V19" t="s">
+        <v>435</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>391</v>
+        <v>453</v>
       </c>
       <c r="AA19" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="AB19" t="s">
-        <v>407</v>
+        <v>478</v>
       </c>
       <c r="AC19" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -3150,73 +3357,73 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="G20" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H20" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="J20" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="K20" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="L20" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="M20" t="s">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="N20" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="O20" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="P20" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
       <c r="Q20" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="R20" t="s">
-        <v>331</v>
+        <v>382</v>
       </c>
       <c r="S20" t="s">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="U20" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>392</v>
+        <v>454</v>
       </c>
       <c r="AA20" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="AB20" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC20" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -3224,85 +3431,79 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="F21" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G21" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H21" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="I21" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="J21" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K21" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="L21" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="M21" t="s">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="O21" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P21" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q21" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R21" t="s">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="S21" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="T21" t="s">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="U21" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V21" t="s">
-        <v>373</v>
+        <v>192</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>393</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>403</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>406</v>
+        <v>455</v>
       </c>
       <c r="AA21" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB21" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC21" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -3310,79 +3511,79 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="F22" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="G22" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H22" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="I22" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="J22" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K22" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="L22" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="M22" t="s">
-        <v>294</v>
+        <v>336</v>
       </c>
       <c r="O22" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P22" t="s">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="Q22" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R22" t="s">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="S22" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="T22" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="U22" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V22" t="s">
-        <v>373</v>
+        <v>192</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>394</v>
+        <v>456</v>
       </c>
       <c r="AA22" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB22" t="s">
-        <v>407</v>
+        <v>481</v>
       </c>
       <c r="AC22" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -3390,79 +3591,79 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E23" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F23" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="G23" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H23" t="s">
+        <v>214</v>
+      </c>
+      <c r="J23" t="s">
+        <v>244</v>
+      </c>
+      <c r="K23" t="s">
+        <v>267</v>
+      </c>
+      <c r="L23" t="s">
+        <v>302</v>
+      </c>
+      <c r="M23" t="s">
+        <v>337</v>
+      </c>
+      <c r="N23" t="s">
+        <v>351</v>
+      </c>
+      <c r="O23" t="s">
+        <v>354</v>
+      </c>
+      <c r="P23" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>362</v>
+      </c>
+      <c r="R23" t="s">
+        <v>385</v>
+      </c>
+      <c r="S23" t="s">
+        <v>409</v>
+      </c>
+      <c r="U23" t="s">
         <v>192</v>
-      </c>
-      <c r="I23" t="s">
-        <v>206</v>
-      </c>
-      <c r="J23" t="s">
-        <v>214</v>
-      </c>
-      <c r="K23" t="s">
-        <v>237</v>
-      </c>
-      <c r="L23" t="s">
-        <v>266</v>
-      </c>
-      <c r="M23" t="s">
-        <v>295</v>
-      </c>
-      <c r="O23" t="s">
-        <v>305</v>
-      </c>
-      <c r="P23" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>311</v>
-      </c>
-      <c r="R23" t="s">
-        <v>334</v>
-      </c>
-      <c r="S23" t="s">
-        <v>349</v>
-      </c>
-      <c r="T23" t="s">
-        <v>367</v>
-      </c>
-      <c r="U23" t="s">
-        <v>373</v>
-      </c>
-      <c r="V23" t="s">
-        <v>170</v>
       </c>
       <c r="W23" t="s">
         <v>2</v>
       </c>
       <c r="X23" t="s">
-        <v>395</v>
+        <v>457</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>473</v>
       </c>
       <c r="AA23" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="AB23" t="s">
-        <v>409</v>
+        <v>477</v>
       </c>
       <c r="AC23" t="s">
-        <v>412</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -3470,79 +3671,85 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="F24" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="G24" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H24" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="I24" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="J24" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="K24" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="L24" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="M24" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="O24" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P24" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q24" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R24" t="s">
-        <v>335</v>
+        <v>386</v>
       </c>
       <c r="S24" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="T24" t="s">
-        <v>368</v>
+        <v>427</v>
       </c>
       <c r="U24" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V24" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W24" t="s">
         <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>396</v>
+        <v>458</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>473</v>
       </c>
       <c r="AA24" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB24" t="s">
-        <v>407</v>
+        <v>481</v>
       </c>
       <c r="AC24" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -3550,79 +3757,73 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="F25" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H25" t="s">
-        <v>194</v>
-      </c>
-      <c r="I25" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J25" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="K25" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="L25" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="M25" t="s">
-        <v>297</v>
+        <v>339</v>
+      </c>
+      <c r="N25" t="s">
+        <v>351</v>
       </c>
       <c r="O25" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="P25" t="s">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="Q25" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="R25" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
       <c r="S25" t="s">
-        <v>349</v>
-      </c>
-      <c r="T25" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="U25" t="s">
-        <v>373</v>
-      </c>
-      <c r="V25" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="W25" t="s">
         <v>2</v>
       </c>
       <c r="X25" t="s">
-        <v>397</v>
+        <v>459</v>
       </c>
       <c r="AA25" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="AB25" t="s">
-        <v>407</v>
+        <v>479</v>
       </c>
       <c r="AC25" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -3630,79 +3831,85 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F26" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="G26" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H26" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="I26" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="J26" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="K26" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="L26" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="M26" t="s">
-        <v>298</v>
+        <v>340</v>
       </c>
       <c r="O26" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P26" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q26" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R26" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
       <c r="S26" t="s">
-        <v>349</v>
+        <v>401</v>
       </c>
       <c r="T26" t="s">
-        <v>370</v>
+        <v>428</v>
       </c>
       <c r="U26" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V26" t="s">
-        <v>170</v>
+        <v>435</v>
       </c>
       <c r="W26" t="s">
         <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>398</v>
+        <v>460</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>475</v>
       </c>
       <c r="AA26" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB26" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC26" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3710,79 +3917,73 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="F27" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="G27" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H27" t="s">
-        <v>196</v>
-      </c>
-      <c r="I27" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="J27" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="K27" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="M27" t="s">
-        <v>299</v>
+        <v>341</v>
+      </c>
+      <c r="N27" t="s">
+        <v>351</v>
       </c>
       <c r="O27" t="s">
-        <v>305</v>
+        <v>354</v>
       </c>
       <c r="P27" t="s">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="Q27" t="s">
-        <v>311</v>
+        <v>363</v>
       </c>
       <c r="R27" t="s">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="S27" t="s">
-        <v>352</v>
-      </c>
-      <c r="T27" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="U27" t="s">
-        <v>373</v>
-      </c>
-      <c r="V27" t="s">
-        <v>170</v>
+        <v>435</v>
       </c>
       <c r="W27" t="s">
         <v>2</v>
       </c>
       <c r="X27" t="s">
-        <v>399</v>
+        <v>461</v>
       </c>
       <c r="AA27" t="s">
-        <v>311</v>
+        <v>476</v>
       </c>
       <c r="AB27" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC27" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3790,73 +3991,73 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E28" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="F28" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="G28" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H28" t="s">
-        <v>197</v>
-      </c>
-      <c r="J28" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K28" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="L28" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="M28" t="s">
-        <v>300</v>
+        <v>342</v>
       </c>
       <c r="N28" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="O28" t="s">
-        <v>304</v>
+        <v>354</v>
       </c>
       <c r="P28" t="s">
-        <v>306</v>
+        <v>356</v>
       </c>
       <c r="Q28" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="R28" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="S28" t="s">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="U28" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="W28" t="s">
         <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>400</v>
+        <v>462</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>472</v>
       </c>
       <c r="AA28" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="AB28" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC28" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3864,79 +4065,79 @@
         <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F29" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="G29" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H29" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="I29" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="J29" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="K29" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="M29" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="O29" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="P29" t="s">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="Q29" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="R29" t="s">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="S29" t="s">
-        <v>343</v>
+        <v>412</v>
       </c>
       <c r="T29" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="U29" t="s">
-        <v>373</v>
+        <v>435</v>
       </c>
       <c r="V29" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="W29" t="s">
         <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>401</v>
+        <v>463</v>
       </c>
       <c r="AA29" t="s">
-        <v>311</v>
+        <v>360</v>
       </c>
       <c r="AB29" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="AC29" t="s">
-        <v>411</v>
+        <v>482</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3944,73 +4145,553 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="F30" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="G30" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="H30" t="s">
-        <v>199</v>
+        <v>221</v>
+      </c>
+      <c r="I30" t="s">
+        <v>241</v>
       </c>
       <c r="J30" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="K30" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="L30" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s">
-        <v>302</v>
+        <v>344</v>
       </c>
       <c r="N30" t="s">
-        <v>303</v>
+        <v>352</v>
       </c>
       <c r="O30" t="s">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="P30" t="s">
-        <v>306</v>
+        <v>355</v>
       </c>
       <c r="Q30" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="R30" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="S30" t="s">
-        <v>353</v>
+        <v>411</v>
+      </c>
+      <c r="T30" t="s">
+        <v>430</v>
       </c>
       <c r="U30" t="s">
-        <v>170</v>
+        <v>435</v>
+      </c>
+      <c r="V30" t="s">
+        <v>435</v>
       </c>
       <c r="W30" t="s">
         <v>2</v>
       </c>
       <c r="X30" t="s">
-        <v>402</v>
+        <v>464</v>
       </c>
       <c r="AA30" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>477</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H31" t="s">
+        <v>222</v>
+      </c>
+      <c r="I31" t="s">
+        <v>233</v>
+      </c>
+      <c r="J31" t="s">
+        <v>244</v>
+      </c>
+      <c r="K31" t="s">
+        <v>275</v>
+      </c>
+      <c r="L31" t="s">
         <v>310</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="M31" t="s">
+        <v>345</v>
+      </c>
+      <c r="O31" t="s">
+        <v>353</v>
+      </c>
+      <c r="P31" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>360</v>
+      </c>
+      <c r="R31" t="s">
+        <v>393</v>
+      </c>
+      <c r="S31" t="s">
+        <v>401</v>
+      </c>
+      <c r="T31" t="s">
+        <v>431</v>
+      </c>
+      <c r="U31" t="s">
+        <v>435</v>
+      </c>
+      <c r="V31" t="s">
+        <v>192</v>
+      </c>
+      <c r="W31" t="s">
+        <v>2</v>
+      </c>
+      <c r="X31" t="s">
+        <v>465</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>478</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32" t="s">
+        <v>189</v>
+      </c>
+      <c r="G32" t="s">
+        <v>191</v>
+      </c>
+      <c r="H32" t="s">
+        <v>223</v>
+      </c>
+      <c r="I32" t="s">
+        <v>242</v>
+      </c>
+      <c r="J32" t="s">
+        <v>245</v>
+      </c>
+      <c r="K32" t="s">
+        <v>276</v>
+      </c>
+      <c r="L32" t="s">
+        <v>311</v>
+      </c>
+      <c r="M32" t="s">
+        <v>346</v>
+      </c>
+      <c r="O32" t="s">
+        <v>353</v>
+      </c>
+      <c r="P32" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>360</v>
+      </c>
+      <c r="R32" t="s">
+        <v>394</v>
+      </c>
+      <c r="S32" t="s">
         <v>407</v>
       </c>
-      <c r="AC30" t="s">
-        <v>411</v>
+      <c r="T32" t="s">
+        <v>432</v>
+      </c>
+      <c r="U32" t="s">
+        <v>435</v>
+      </c>
+      <c r="V32" t="s">
+        <v>435</v>
+      </c>
+      <c r="W32" t="s">
+        <v>2</v>
+      </c>
+      <c r="X32" t="s">
+        <v>466</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>479</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" t="s">
+        <v>162</v>
+      </c>
+      <c r="F33" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" t="s">
+        <v>191</v>
+      </c>
+      <c r="H33" t="s">
+        <v>224</v>
+      </c>
+      <c r="I33" t="s">
+        <v>233</v>
+      </c>
+      <c r="J33" t="s">
+        <v>245</v>
+      </c>
+      <c r="K33" t="s">
+        <v>277</v>
+      </c>
+      <c r="L33" t="s">
+        <v>312</v>
+      </c>
+      <c r="M33" t="s">
+        <v>347</v>
+      </c>
+      <c r="O33" t="s">
+        <v>353</v>
+      </c>
+      <c r="P33" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>360</v>
+      </c>
+      <c r="R33" t="s">
+        <v>395</v>
+      </c>
+      <c r="S33" t="s">
+        <v>407</v>
+      </c>
+      <c r="T33" t="s">
+        <v>433</v>
+      </c>
+      <c r="U33" t="s">
+        <v>435</v>
+      </c>
+      <c r="V33" t="s">
+        <v>192</v>
+      </c>
+      <c r="W33" t="s">
+        <v>2</v>
+      </c>
+      <c r="X33" t="s">
+        <v>467</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>480</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" t="s">
+        <v>149</v>
+      </c>
+      <c r="G34" t="s">
+        <v>191</v>
+      </c>
+      <c r="H34" t="s">
+        <v>225</v>
+      </c>
+      <c r="I34" t="s">
+        <v>243</v>
+      </c>
+      <c r="J34" t="s">
+        <v>245</v>
+      </c>
+      <c r="K34" t="s">
+        <v>278</v>
+      </c>
+      <c r="L34" t="s">
+        <v>313</v>
+      </c>
+      <c r="M34" t="s">
+        <v>348</v>
+      </c>
+      <c r="N34" t="s">
+        <v>352</v>
+      </c>
+      <c r="O34" t="s">
+        <v>353</v>
+      </c>
+      <c r="P34" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>360</v>
+      </c>
+      <c r="R34" t="s">
+        <v>396</v>
+      </c>
+      <c r="S34" t="s">
+        <v>409</v>
+      </c>
+      <c r="T34" t="s">
+        <v>434</v>
+      </c>
+      <c r="U34" t="s">
+        <v>435</v>
+      </c>
+      <c r="V34" t="s">
+        <v>192</v>
+      </c>
+      <c r="W34" t="s">
+        <v>2</v>
+      </c>
+      <c r="X34" t="s">
+        <v>468</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>360</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>477</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" t="s">
+        <v>164</v>
+      </c>
+      <c r="F35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G35" t="s">
+        <v>191</v>
+      </c>
+      <c r="H35" t="s">
+        <v>226</v>
+      </c>
+      <c r="J35" t="s">
+        <v>244</v>
+      </c>
+      <c r="K35" t="s">
+        <v>279</v>
+      </c>
+      <c r="L35" t="s">
+        <v>314</v>
+      </c>
+      <c r="M35" t="s">
+        <v>349</v>
+      </c>
+      <c r="N35" t="s">
+        <v>351</v>
+      </c>
+      <c r="O35" t="s">
+        <v>354</v>
+      </c>
+      <c r="P35" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>361</v>
+      </c>
+      <c r="R35" t="s">
+        <v>397</v>
+      </c>
+      <c r="S35" t="s">
+        <v>409</v>
+      </c>
+      <c r="U35" t="s">
+        <v>192</v>
+      </c>
+      <c r="W35" t="s">
+        <v>2</v>
+      </c>
+      <c r="X35" t="s">
+        <v>469</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>480</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F36" t="s">
+        <v>189</v>
+      </c>
+      <c r="G36" t="s">
+        <v>191</v>
+      </c>
+      <c r="H36" t="s">
+        <v>227</v>
+      </c>
+      <c r="J36" t="s">
+        <v>244</v>
+      </c>
+      <c r="K36" t="s">
+        <v>280</v>
+      </c>
+      <c r="L36" t="s">
+        <v>315</v>
+      </c>
+      <c r="M36" t="s">
+        <v>350</v>
+      </c>
+      <c r="N36" t="s">
+        <v>351</v>
+      </c>
+      <c r="O36" t="s">
+        <v>354</v>
+      </c>
+      <c r="P36" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>361</v>
+      </c>
+      <c r="R36" t="s">
+        <v>398</v>
+      </c>
+      <c r="S36" t="s">
+        <v>413</v>
+      </c>
+      <c r="U36" t="s">
+        <v>192</v>
+      </c>
+      <c r="W36" t="s">
+        <v>2</v>
+      </c>
+      <c r="X36" t="s">
+        <v>470</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>478</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33026</t>
+          <t>121435</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>KARLA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CAMILO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OVALLE</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,32 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6865115659</t>
+          <t>6865999642</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MONTE BLANCO 3872</t>
+          <t>AV SIDENITA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22-07-1973</t>
+          <t>20-12-2003</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HECTOR30@GMAIL.COM</t>
+          <t>KARLACAMILO2003@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>28-06-2021 08:27:50</t>
+          <t>07-09-2022 17:16:11</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -659,17 +659,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>06-02-2026 08:23:55</t>
+          <t>03-02-2026 17:10:39</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>06-02-2026 08:22:42</t>
+          <t>03-02-2026 17:08:49</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26020522131750001322</t>
+          <t>26030522048250001473</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>121435</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KARLA</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CAMILO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>OVALLE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,32 +748,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6865999642</t>
+          <t>6865115659</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AV SIDENITA</t>
+          <t>MONTE BLANCO 3872</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20-12-2003</t>
+          <t>22-07-1973</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>KARLACAMILO2003@ICLOUD.COM</t>
+          <t>HECTOR30@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>07-09-2022 17:16:11</t>
+          <t>28-06-2021 08:27:50</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -794,17 +794,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-02-2026 17:10:39</t>
+          <t>06-02-2026 08:23:55</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>03-02-2026 17:08:49</t>
+          <t>06-02-2026 08:22:42</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26030522048250001473</t>
+          <t>26020522131750001322</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -836,24 +836,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>325528</t>
+          <t>119059</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,48 +863,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JOHNNY</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AGUILA</t>
+          <t>OLVERA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6195092751</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6863511539</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CARPATOS</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>04-06-1973</t>
+          <t>20-08-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JONNY.AGUILA@GMAIL.COM</t>
+          <t>OLVERAVALERIA322@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>26-11-2025 18:16:09</t>
+          <t>29-08-2022 17:00:29</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -929,18 +933,18 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10-02-2026 06:46:00</t>
+          <t>03-02-2026 16:23:07</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -951,19 +955,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26020522223470000776</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26030522045250001467</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -983,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>119059</t>
+          <t>230542</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>RAMSES IVAN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OLVERA</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>BAYLON</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,57 +1014,53 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863511539</t>
+          <t>6864633183</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CARPATOS</t>
+          <t>AV AVES DEL PARAISO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20-08-2005</t>
+          <t>14-08-2007</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>OLVERAVALERIA322@GMAIL.COM</t>
+          <t>22402080067892@CECYTEBC.EDU.MX</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>29-08-2022 17:00:29</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>20-04-2024 12:13:17</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-02-2026 16:23:07</t>
+          <t>03-02-2026 13:07:22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1076,13 +1068,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>03-02-2026 13:06:24</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,36 +1090,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26030522045250001467</t>
+          <t>26020522039060001189</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>230542</t>
+          <t>340308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RAMSES IVAN</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BAYLON</t>
+          <t>DAVALOS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6864633183</t>
+          <t>6862641945</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AV AVES DEL PARAISO</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14-08-2007</t>
+          <t>10-02-1977</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>22402080067892@CECYTEBC.EDU.MX</t>
+          <t>JIMMYSDF39@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>20-04-2024 12:13:17</t>
+          <t>02-02-2026 17:24:44</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1195,17 +1195,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-02-2026 13:07:22</t>
+          <t>02-02-2026 17:34:10</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-02-2026 13:06:24</t>
+          <t>02-02-2026 17:33:28</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26020522039060001189</t>
+          <t>26020522018870001160</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1249,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340308</t>
+          <t>339391</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DAVALOS</t>
+          <t>CELIO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,14 +1284,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6862641945</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6863360339</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1299,60 +1295,56 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10-02-1977</t>
+          <t>16-05-2009</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JIMMYSDF39@GMAIL.COM</t>
+          <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 17:24:44</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>30-01-2026 16:25:54</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 17:34:10</t>
+          <t>03-02-2026 11:38:00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-02-2026 17:33:28</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1360,19 +1352,27 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26020522018870001160</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26020522037270001186</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1384,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>339391</t>
+          <t>340848</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CELIO</t>
+          <t>SWERRANO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1419,10 +1419,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6863360339</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6861236171</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ALARCOS 3576</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1430,56 +1434,60 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16-05-2009</t>
+          <t>17-11-2007</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
+          <t>TORRES.NICOLAS2007@GAMIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>30-01-2026 16:25:54</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 04:56:34</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-02-2026 11:38:00</t>
+          <t>06-02-2026 05:01:48</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>06-02-2026 05:01:07</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1487,7 +1495,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26020522037270001186</t>
+          <t>26020522121930001316</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,12 +1505,12 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+          <t>MAGALI ROJAS RIVAS</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1519,12 +1527,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>324484</t>
+          <t>340380</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LESLYE</t>
+          <t>ETHAN JOAQUIN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t xml:space="preserve">ZARATE </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,32 +1562,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6161286154</t>
+          <t>6866192595</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AV DEL JILGUERO 1052</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30-10-1995</t>
+          <t>15-07-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>OLIVASLESLYE2@GMAIL.COM</t>
+          <t>ETHAN.ZARATE@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>20-11-2025 10:11:37</t>
+          <t>02-02-2026 19:54:30</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1600,17 +1608,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>14-02-2026 09:47:10</t>
+          <t>02-02-2026 19:59:58</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>14-02-2026 09:46:17</t>
+          <t>02-02-2026 19:58:03</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1630,19 +1638,11 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26150522345040001698</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522022780001167</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>499</t>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340848</t>
+          <t>341431</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t>LUCIANO GUADALUPE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SWERRANO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6861236171</t>
+          <t>6866068064</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ALARCOS 3576</t>
+          <t>DSFH</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>17-11-2007</t>
+          <t>27-10-1987</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>TORRES.NICOLAS2007@GAMIL.COM</t>
+          <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>04-02-2026 04:56:34</t>
+          <t>05-02-2026 19:00:48</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>06-02-2026 05:01:48</t>
+          <t>09-02-2026 17:50:19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>06-02-2026 05:01:07</t>
+          <t>09-02-2026 17:49:53</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26020522121930001316</t>
+          <t>26010522204130003399</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>MAGALI ROJAS RIVAS</t>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1805,12 +1805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341431</t>
+          <t>324484</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LUCIANO GUADALUPE</t>
+          <t>LESLYE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,32 +1840,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6866068064</t>
+          <t>6161286154</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DSFH</t>
+          <t>AV DEL JILGUERO 1052</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27-10-1987</t>
+          <t>30-10-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
+          <t>OLIVASLESLYE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>05-02-2026 19:00:48</t>
+          <t>20-11-2025 10:11:37</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-02-2026 17:50:19</t>
+          <t>14-02-2026 09:47:10</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>09-02-2026 17:49:53</t>
+          <t>14-02-2026 09:46:17</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26010522204130003399</t>
+          <t>26150522345040001698</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1948,12 +1948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341769</t>
+          <t>325528</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,95 +1963,87 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENA </t>
+          <t>JOHNNY</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>AGUILA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>URIAS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6862828171</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AV CASCADA SAN ANDRES 4039</t>
-        </is>
-      </c>
+          <t>6195092751</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31-08-2007</t>
+          <t>04-06-1973</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>J0802562@GMAIL.COM</t>
+          <t>JONNY.AGUILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>07-02-2026 09:15:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>26-11-2025 18:16:09</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>07-02-2026 09:21:40</t>
+          <t>10-02-2026 06:46:00</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>07-02-2026 09:20:44</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2059,14 +2051,22 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522157150000681</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26020522223470000776</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2083,12 +2083,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340380</t>
+          <t>341769</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ETHAN JOAQUIN</t>
+          <t xml:space="preserve">JIMENA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZARATE </t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>URIAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,32 +2118,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6866192595</t>
+          <t>6862828171</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>AV CASCADA SAN ANDRES 4039</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15-07-2002</t>
+          <t>31-08-2007</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ETHAN.ZARATE@UABC.EDU.MX</t>
+          <t>J0802562@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-02-2026 19:54:30</t>
+          <t>07-02-2026 09:15:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2164,17 +2164,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-02-2026 19:59:58</t>
+          <t>07-02-2026 09:21:40</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-02-2026 19:58:03</t>
+          <t>07-02-2026 09:20:44</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26020522022780001167</t>
+          <t>26020522157150000681</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>342438</t>
+          <t>342440</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BRAYAN SALIM</t>
+          <t>BETZY MARCELA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERIA </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,53 +2388,53 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6861320570</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>FRANCISCO BARRIOS</t>
-        </is>
-      </c>
+          <t>6862559890</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12-10-2002</t>
+          <t>21-06-1992</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SALIMSOTO17@GMAIL.COM</t>
+          <t>BETZY.OMARCE21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>09-02-2026 19:20:31</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>09-02-2026 19:28:04</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>09-02-2026 19:23:06</t>
+          <t>09-02-2026 19:29:53</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2442,21 +2442,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>09-02-2026 19:22:51</t>
-        </is>
-      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2464,14 +2456,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26020522210660000748</t>
+          <t>26020522210970000750</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2488,12 +2480,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342486</t>
+          <t>342371</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20303</t>
+          <t>20189</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2503,17 +2495,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>VIVIAN AIMEE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2523,7 +2515,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6641882731</t>
+          <t>6863890309</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2533,22 +2525,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15-11-1988</t>
+          <t>20-06-2010</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>OSCAR.88GV@GMAIL.COM</t>
+          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 20:25:31</t>
+          <t>09-02-2026 18:09:38</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2569,7 +2561,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 20:34:45</t>
+          <t>09-02-2026 18:20:05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2579,7 +2571,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>09-02-2026 20:33:58</t>
+          <t>09-02-2026 18:19:25</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2599,7 +2591,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26020522213890000759</t>
+          <t>26020522206580000736</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2611,7 +2603,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2623,12 +2615,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>342371</t>
+          <t>342185</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2638,17 +2630,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VIVIAN AIMEE</t>
+          <t>JESUS MANUEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2658,53 +2650,53 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6863890309</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861640070</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>18-05-1961</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
+          <t>CHUCHUNEL61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09-02-2026 18:09:38</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>09-02-2026 14:42:28</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 18:20:05</t>
+          <t>09-02-2026 14:44:26</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2712,21 +2704,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:19:25</t>
-        </is>
-      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2734,19 +2718,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26020522206580000736</t>
+          <t>26020522193750000724</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2758,12 +2742,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>343329</t>
+          <t>342438</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2773,17 +2757,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KIMBERLY</t>
+          <t>BRAYAN SALIM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t xml:space="preserve">FERIA </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2793,32 +2777,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6865255663</t>
+          <t>6861320570</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>FRANCISCO BARRIOS</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>22-12-1995</t>
+          <t>12-10-2002</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>KIMBERLYCKIMO@GMAIL.COM</t>
+          <t>SALIMSOTO17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12-02-2026 17:11:31</t>
+          <t>09-02-2026 19:20:31</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2839,17 +2823,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>12-02-2026 17:19:12</t>
+          <t>09-02-2026 19:23:06</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>12-02-2026 17:18:19</t>
+          <t>09-02-2026 19:22:51</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2859,7 +2843,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2869,7 +2853,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26020522299590000883</t>
+          <t>26020522210660000748</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2881,7 +2865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2893,12 +2877,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>343618</t>
+          <t>342486</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2908,17 +2892,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IAAN OCTAVIO</t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2928,10 +2912,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6862251224</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6641882731</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2939,56 +2927,60 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03-01-2009</t>
+          <t>15-11-1988</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CARRILLOIAAN@GMAIL.COM</t>
+          <t>OSCAR.88GV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>13-02-2026 21:07:16</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 20:25:31</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>13-02-2026 21:10:08</t>
+          <t>09-02-2026 20:34:45</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>09-02-2026 20:33:58</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2996,36 +2988,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26020522331740000929</t>
+          <t>26020522213890000759</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342440</t>
+          <t>342424</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3035,17 +3027,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BETZY MARCELA</t>
+          <t>ARANTZA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3055,10 +3047,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6862559890</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>4151245575</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AVENIDA SAN PEDRO MEZQUITL</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3066,42 +3062,38 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21-06-1992</t>
+          <t>15-07-1997</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BETZY.OMARCE21@GMAIL.COM</t>
+          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 19:28:04</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:07:14</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 19:29:53</t>
+          <t>09-02-2026 19:10:59</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3109,13 +3101,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:10:20</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3123,19 +3123,19 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26020522210970000750</t>
+          <t>26020522209900000743</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342185</t>
+          <t>340209</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JESUS MANUEL</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6861640070</t>
+          <t>6864221370</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3193,17 +3193,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18-05-1961</t>
+          <t>13-08-2003</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CHUCHUNEL61@GMAIL.COM</t>
+          <t>RICHI.CAMACHO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:28</t>
+          <t>02-02-2026 15:23:20</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3218,28 +3218,28 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 14:44:26</t>
+          <t>04-02-2026 15:47:22</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -3250,19 +3250,27 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26020522193750000724</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26020522078020001242</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3274,12 +3282,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342109</t>
+          <t>342672</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3289,17 +3297,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>JOSE MARIA</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3309,67 +3317,75 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6151107814</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>9931258390</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>06-03-2009</t>
+          <t>03-06-1988</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>JC7651065@GMAIL.COM</t>
+          <t>CORREOPENDIENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:55</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:33:08</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>13-02-2026 11:22:23</t>
+          <t>10-02-2026 15:37:35</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:36:57</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3377,32 +3393,24 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26020522318800000908</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>MAGALI ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522234930000790</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3544,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342424</t>
+          <t>343047</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3551,17 +3559,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ARANTZA</t>
+          <t>MARIA ANTONIA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3571,12 +3579,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4151245575</t>
+          <t>6866017324</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AVENIDA SAN PEDRO MEZQUITL</t>
+          <t>RIO CAOCA 3556</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3586,17 +3594,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>15-07-1997</t>
+          <t>22-09-1969</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
+          <t>MAALIN_22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 19:07:14</t>
+          <t>11-02-2026 16:49:30</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3607,7 +3615,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3617,17 +3625,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:59</t>
+          <t>14-02-2026 08:55:57</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:20</t>
+          <t>14-02-2026 08:55:02</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3637,7 +3645,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3647,11 +3655,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26020522209900000743</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>26020522344200000936</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>MAGALI  ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>499</t>
@@ -3659,24 +3675,24 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344232</t>
+          <t>343209</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3686,17 +3702,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RICHKARDAY</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3706,28 +3722,24 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6862316874</t>
+          <t>6862308375</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>02-06-2000</t>
+          <t>31-01-2009</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
+          <t>EDWSUCOR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16-02-2026 17:42:45</t>
+          <t>12-02-2026 10:56:58</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3742,28 +3754,28 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>17-02-2026 19:32:54</t>
+          <t>16-02-2026 13:53:04</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3774,22 +3786,18 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26020522444580001061</t>
+          <t>26020522389340000968</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3806,12 +3814,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>344585</t>
+          <t>342109</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>19927</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3821,17 +3829,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>JOSE MARIA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3841,7 +3849,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6862147023</t>
+          <t>6151107814</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3852,17 +3860,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>06-03-2009</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>JR21675@GMAIL.COM</t>
+          <t>JC7651065@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>17-02-2026 16:52:54</t>
+          <t>09-02-2026 11:19:55</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3877,28 +3885,28 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>17-02-2026 16:54:41</t>
+          <t>13-02-2026 11:22:23</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3909,14 +3917,22 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26020522435540001049</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26020522318800000908</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>MAGALI ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3933,12 +3949,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>340209</t>
+          <t>343706</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3948,17 +3964,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>ALINA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>ALEJO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3968,67 +3984,75 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6864221370</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6862400244</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>13-08-2003</t>
+          <t>04-10-2006</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>RICHI.CAMACHO20@GMAIL.COM</t>
+          <t>ALINITA292@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-02-2026 15:23:20</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 11:17:39</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>04-02-2026 15:47:22</t>
+          <t>14-02-2026 11:24:40</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14-02-2026 11:24:09</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4036,27 +4060,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26020522078020001242</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522347310000939</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4068,12 +4084,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>344924</t>
+          <t>344382</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4083,17 +4099,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ASHLY VIVIANA</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4103,67 +4119,79 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6863062937</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6861853385</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MONTE BLANCO</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24-09-2012</t>
+          <t>23-02-1985</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CECYECY1976@GMAIL.COM</t>
+          <t>JULIOREYESS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18-02-2026 18:11:34</t>
+          <t>17-02-2026 06:30:32</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:02</t>
+          <t>17-02-2026 06:36:06</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>17-02-2026 06:34:33</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4171,36 +4199,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26020522471760001096</t>
+          <t>26020522419620001023</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>343047</t>
+          <t>344463</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4210,17 +4238,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MARIA ANTONIA</t>
+          <t xml:space="preserve">MAYRA MELISSA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>ESCUDERO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4230,14 +4258,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6866017324</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>RIO CAOCA 3556</t>
-        </is>
-      </c>
+          <t>6862890006</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4245,60 +4269,56 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22-09-1969</t>
+          <t>08-04-2005</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MAALIN_22@HOTMAIL.COM</t>
+          <t>MAYRAESC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11-02-2026 16:49:30</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>17-02-2026 12:05:45</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>14-02-2026 08:55:57</t>
+          <t>17-02-2026 12:13:51</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>14-02-2026 08:55:02</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4306,44 +4326,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26020522344200000936</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>MAGALI  ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522426030001036</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343209</t>
+          <t>344577</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4353,17 +4365,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4373,24 +4385,28 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6862308375</t>
+          <t>6863899539</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31-01-2009</t>
+          <t>20-10-2007</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>EDWSUCOR@GMAIL.COM</t>
+          <t>MORGARSEB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12-02-2026 10:56:58</t>
+          <t>17-02-2026 16:44:08</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4415,18 +4431,18 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16-02-2026 13:53:04</t>
+          <t>19-02-2026 16:54:35</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -4437,15 +4453,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26020522389340000968</t>
+          <t>26020522499870001128</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>549</t>
@@ -4465,12 +4485,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342672</t>
+          <t>342841</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4480,17 +4500,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>ZAYDA ELIZABETH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MERAZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4500,7 +4520,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9931258390</t>
+          <t>6442093389</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4515,17 +4535,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>03-06-1988</t>
+          <t>18-04-2008</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CORREOPENDIENTE@GMAIL.COM</t>
+          <t>ZAYDABARRA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-02-2026 15:33:08</t>
+          <t>10-02-2026 19:33:16</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4546,7 +4566,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:35</t>
+          <t>10-02-2026 19:37:59</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4556,7 +4576,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10-02-2026 15:36:57</t>
+          <t>10-02-2026 19:37:25</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4566,7 +4586,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4576,7 +4596,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26020522234930000790</t>
+          <t>26020522247350000807</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4588,7 +4608,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4600,12 +4620,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342841</t>
+          <t>342472</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4615,17 +4635,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ZAYDA ELIZABETH</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MERAZ</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4635,14 +4655,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6442093389</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861434493</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4650,60 +4666,56 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18-04-2008</t>
+          <t>10-04-1980</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ZAYDABARRA@GMAIL.COM</t>
+          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:16</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>09-02-2026 20:01:55</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10-02-2026 19:37:59</t>
+          <t>09-02-2026 20:06:47</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>10-02-2026 19:37:25</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4711,14 +4723,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26020522247350000807</t>
+          <t>26020522212980000757</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4735,12 +4747,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343706</t>
+          <t>343329</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4750,17 +4762,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ALINA</t>
+          <t>KIMBERLY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ALEJO</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4770,7 +4782,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6862400244</t>
+          <t>6865255663</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4785,17 +4797,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>04-10-2006</t>
+          <t>22-12-1995</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ALINITA292@GMAIL.COM</t>
+          <t>KIMBERLYCKIMO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>14-02-2026 11:17:39</t>
+          <t>12-02-2026 17:11:31</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4816,17 +4828,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>14-02-2026 11:24:40</t>
+          <t>12-02-2026 17:19:12</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>14-02-2026 11:24:09</t>
+          <t>12-02-2026 17:18:19</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4846,7 +4858,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26020522347310000939</t>
+          <t>26020522299590000883</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4858,7 +4870,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4870,12 +4882,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>344382</t>
+          <t>343618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4885,17 +4897,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>IAAN OCTAVIO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>REYNOSA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4905,14 +4917,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861853385</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>MONTE BLANCO</t>
-        </is>
-      </c>
+          <t>6862251224</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4920,64 +4928,56 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23-02-1985</t>
+          <t>03-01-2009</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JULIOREYESS@GMAIL.COM</t>
+          <t>CARRILLOIAAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>17-02-2026 06:30:32</t>
+          <t>13-02-2026 21:07:16</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>17-02-2026 06:36:06</t>
+          <t>13-02-2026 21:10:08</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>17-02-2026 06:34:33</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4985,14 +4985,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26020522419620001023</t>
+          <t>26020522331740000929</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5009,12 +5009,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>344463</t>
+          <t>344232</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5024,17 +5024,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYRA MELISSA </t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ESCUDERO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>RICHKARDAY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6862890006</t>
+          <t>6862316874</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5055,17 +5055,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>08-04-2005</t>
+          <t>02-06-2000</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MAYRAESC@GMAIL.COM</t>
+          <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17-02-2026 12:05:45</t>
+          <t>16-02-2026 17:42:45</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>17-02-2026 12:13:51</t>
+          <t>17-02-2026 19:32:54</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5112,36 +5112,44 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26020522426030001036</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>26020522444580001061</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342472</t>
+          <t>344585</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5151,17 +5159,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5171,28 +5179,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6861434493</t>
+          <t>6862147023</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>10-04-1980</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
+          <t>JR21675@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 20:01:55</t>
+          <t>17-02-2026 16:52:54</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5207,22 +5215,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-02-2026 20:06:47</t>
+          <t>17-02-2026 16:54:41</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -5239,36 +5247,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26020522212980000757</t>
+          <t>26020522435540001049</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344208</t>
+          <t>344924</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5278,17 +5286,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VICTOR ALEXIS</t>
+          <t>ASHLY VIVIANA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5298,79 +5306,67 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6865624438</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>RUISEÑORES</t>
-        </is>
-      </c>
+          <t>6863062937</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>07-04-2010</t>
+          <t>24-09-2012</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5624438@GMAIL.COM</t>
+          <t>CECYECY1976@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:52</t>
+          <t>18-02-2026 18:11:34</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>16-02-2026 17:23:38</t>
+          <t>18-02-2026 18:14:02</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>16-02-2026 17:22:53</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5378,22 +5374,161 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26020522399070000985</t>
+          <t>26020522471760001096</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>344208</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>22025</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VICTOR ALEXIS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HARO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6865624438</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>RUISEÑORES</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>07-04-2010</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5624438@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:19:52</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:23:38</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:22:53</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26020522399070000985</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>121435</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KARLA</t>
+          <t>HECTOR MANUEL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CAMILO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>OVALLE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,32 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6865999642</t>
+          <t>6865115659</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AV SIDENITA</t>
+          <t>MONTE BLANCO 3872</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20-12-2003</t>
+          <t>22-07-1973</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>KARLACAMILO2003@ICLOUD.COM</t>
+          <t>HECTOR30@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>07-09-2022 17:16:11</t>
+          <t>28-06-2021 08:27:50</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -659,17 +659,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-02-2026 17:10:39</t>
+          <t>06-02-2026 08:23:55</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>03-02-2026 17:08:49</t>
+          <t>06-02-2026 08:22:42</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26030522048250001473</t>
+          <t>26020522131750001322</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -701,24 +701,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>33026</t>
+          <t>121435</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HECTOR MANUEL</t>
+          <t>KARLA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CAMILO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OVALLE</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,32 +748,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6865115659</t>
+          <t>6865999642</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MONTE BLANCO 3872</t>
+          <t>AV SIDENITA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22-07-1973</t>
+          <t>20-12-2003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HECTOR30@GMAIL.COM</t>
+          <t>KARLACAMILO2003@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-06-2021 08:27:50</t>
+          <t>07-09-2022 17:16:11</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -794,17 +794,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>06-02-2026 08:23:55</t>
+          <t>03-02-2026 17:10:39</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>06-02-2026 08:22:42</t>
+          <t>03-02-2026 17:08:49</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26020522131750001322</t>
+          <t>26030522048250001473</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -836,24 +836,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>119059</t>
+          <t>340308</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OLVERA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>DAVALOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,71 +883,75 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6863511539</t>
+          <t>6862641945</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CARPATOS</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-08-2005</t>
+          <t>10-02-1977</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>OLVERAVALERIA322@GMAIL.COM</t>
+          <t>JIMMYSDF39@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>29-08-2022 17:00:29</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 17:24:44</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-02-2026 16:23:07</t>
+          <t>02-02-2026 17:34:10</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:33:28</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,36 +959,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26030522045250001467</t>
+          <t>26020522018870001160</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>230542</t>
+          <t>339391</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RAMSES IVAN</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BAYLON</t>
+          <t>CELIO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,14 +1018,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6864633183</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AV AVES DEL PARAISO</t>
-        </is>
-      </c>
+          <t>6863360339</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1029,38 +1029,42 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14-08-2007</t>
+          <t>16-05-2009</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22402080067892@CECYTEBC.EDU.MX</t>
+          <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20-04-2024 12:13:17</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>30-01-2026 16:25:54</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-02-2026 13:07:22</t>
+          <t>03-02-2026 11:38:00</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1068,21 +1072,13 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>03-02-2026 13:06:24</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1090,19 +1086,27 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020522039060001189</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26020522037270001186</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1114,12 +1118,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>340308</t>
+          <t>119059</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>OLVERA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DAVALOS</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1149,75 +1153,71 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6862641945</t>
+          <t>6863511539</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>CARPATOS</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10-02-1977</t>
+          <t>20-08-2005</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>JIMMYSDF39@GMAIL.COM</t>
+          <t>OLVERAVALERIA322@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-02-2026 17:24:44</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>29-08-2022 17:00:29</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 17:34:10</t>
+          <t>03-02-2026 16:23:07</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-02-2026 17:33:28</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1225,36 +1225,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26020522018870001160</t>
+          <t>26030522045250001467</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>339391</t>
+          <t>230542</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>RAMSES IVAN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CELIO</t>
+          <t>BAYLON</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,10 +1284,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6863360339</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6864633183</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AV AVES DEL PARAISO</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1295,42 +1299,38 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16-05-2009</t>
+          <t>14-08-2007</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
+          <t>22402080067892@CECYTEBC.EDU.MX</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>30-01-2026 16:25:54</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>20-04-2024 12:13:17</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-02-2026 11:38:00</t>
+          <t>03-02-2026 13:07:22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1338,13 +1338,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>03-02-2026 13:06:24</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1352,27 +1360,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26020522037270001186</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522039060001189</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1805,12 +1805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>324484</t>
+          <t>325528</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,95 +1820,87 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LESLYE</t>
+          <t>JOHNNY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>AGUILA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6161286154</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AV DEL JILGUERO 1052</t>
-        </is>
-      </c>
+          <t>6195092751</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30-10-1995</t>
+          <t>04-06-1973</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OLIVASLESLYE2@GMAIL.COM</t>
+          <t>JONNY.AGUILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>20-11-2025 10:11:37</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>26-11-2025 18:16:09</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>14-02-2026 09:47:10</t>
+          <t>10-02-2026 06:46:00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>14-02-2026 09:46:17</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1916,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26150522345040001698</t>
+          <t>26020522223470000776</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1931,29 +1923,29 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>325528</t>
+          <t>341769</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,87 +1955,95 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JOHNNY</t>
+          <t xml:space="preserve">JIMENA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGUILA</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>URIAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6862828171</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AV CASCADA SAN ANDRES 4039</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>31-08-2007</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>07-02-2026 09:15:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>07-02-2026 09:21:40</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>07-02-2026 09:20:44</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>6195092751</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>04-06-1973</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>JONNY.AGUILA@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>26-11-2025 18:16:09</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>CONVENIOS $549</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>10-02-2026 06:46:00</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2051,44 +2051,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522223470000776</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522157150000681</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341769</t>
+          <t>342371</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>20189</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENA </t>
+          <t>VIVIAN AIMEE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>URIAS</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,12 +2110,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6862828171</t>
+          <t>6863890309</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AV CASCADA SAN ANDRES 4039</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2133,17 +2125,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31-08-2007</t>
+          <t>20-06-2010</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>J0802562@GMAIL.COM</t>
+          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>07-02-2026 09:15:00</t>
+          <t>09-02-2026 18:09:38</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2164,17 +2156,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>07-02-2026 09:21:40</t>
+          <t>09-02-2026 18:20:05</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>07-02-2026 09:20:44</t>
+          <t>09-02-2026 18:19:25</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2194,7 +2186,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26020522157150000681</t>
+          <t>26020522206580000736</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2206,24 +2198,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341327</t>
+          <t>324484</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>LESLYE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,32 +2245,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6865534615</t>
+          <t>6161286154</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AV DEL JILGUERO 1052</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>27-01-2000</t>
+          <t>30-10-1995</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>GLITCH0127@GMAIL.COM</t>
+          <t>OLIVASLESLYE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>05-02-2026 14:43:26</t>
+          <t>20-11-2025 10:11:37</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2299,17 +2291,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>05-02-2026 14:49:36</t>
+          <t>14-02-2026 09:47:10</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>05-02-2026 14:49:16</t>
+          <t>14-02-2026 09:46:17</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2329,11 +2321,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26020522107360001285</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26150522345040001698</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>499</t>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2353,12 +2353,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>342440</t>
+          <t>341327</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BETZY MARCELA</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SALINAS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,67 +2388,75 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6862559890</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6865534615</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>21-06-1992</t>
+          <t>27-01-2000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BETZY.OMARCE21@GMAIL.COM</t>
+          <t>GLITCH0127@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>09-02-2026 19:28:04</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 14:43:26</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>09-02-2026 19:29:53</t>
+          <t>05-02-2026 14:49:36</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>05-02-2026 14:49:16</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2456,19 +2464,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26020522210970000750</t>
+          <t>26020522107360001285</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2480,12 +2488,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342371</t>
+          <t>342424</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2495,17 +2503,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VIVIAN AIMEE</t>
+          <t>ARANTZA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2515,12 +2523,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6863890309</t>
+          <t>4151245575</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>AVENIDA SAN PEDRO MEZQUITL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2530,17 +2538,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>15-07-1997</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
+          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 18:09:38</t>
+          <t>09-02-2026 19:07:14</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2551,7 +2559,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2561,7 +2569,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 18:20:05</t>
+          <t>09-02-2026 19:10:59</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2571,7 +2579,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>09-02-2026 18:19:25</t>
+          <t>09-02-2026 19:10:20</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2591,7 +2599,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26020522206580000736</t>
+          <t>26020522209900000743</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2603,7 +2611,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2615,12 +2623,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>342185</t>
+          <t>342440</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2630,17 +2638,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JESUS MANUEL</t>
+          <t>BETZY MARCELA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2650,28 +2658,28 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861640070</t>
+          <t>6862559890</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18-05-1961</t>
+          <t>21-06-1992</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CHUCHUNEL61@GMAIL.COM</t>
+          <t>BETZY.OMARCE21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:28</t>
+          <t>09-02-2026 19:28:04</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2686,17 +2694,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 14:44:26</t>
+          <t>09-02-2026 19:29:53</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2707,7 +2715,7 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2718,19 +2726,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26020522193750000724</t>
+          <t>26020522210970000750</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3012,12 +3020,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342424</t>
+          <t>342185</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3027,17 +3035,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ARANTZA</t>
+          <t>JESUS MANUEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3047,53 +3055,53 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4151245575</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>AVENIDA SAN PEDRO MEZQUITL</t>
-        </is>
-      </c>
+          <t>6861640070</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>15-07-1997</t>
+          <t>18-05-1961</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
+          <t>CHUCHUNEL61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 19:07:14</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>09-02-2026 14:42:28</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:59</t>
+          <t>09-02-2026 14:44:26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3101,21 +3109,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>09-02-2026 19:10:20</t>
-        </is>
-      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3123,19 +3123,19 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26020522209900000743</t>
+          <t>26020522193750000724</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3282,12 +3282,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342672</t>
+          <t>343047</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>MARIA ANTONIA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9931258390</t>
+          <t>6866017324</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>RIO CAOCA 3556</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3332,17 +3332,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03-06-1988</t>
+          <t>22-09-1969</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CORREOPENDIENTE@GMAIL.COM</t>
+          <t>MAALIN_22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10-02-2026 15:33:08</t>
+          <t>11-02-2026 16:49:30</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3363,17 +3363,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:35</t>
+          <t>14-02-2026 08:55:57</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>10-02-2026 15:36:57</t>
+          <t>14-02-2026 08:55:02</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3393,11 +3393,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26020522234930000790</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26020522344200000936</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>MAGALI  ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>499</t>
@@ -3405,12 +3413,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3552,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>343047</t>
+          <t>342672</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3559,17 +3567,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MARIA ANTONIA</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3579,12 +3587,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6866017324</t>
+          <t>9931258390</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>RIO CAOCA 3556</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3594,17 +3602,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>22-09-1969</t>
+          <t>03-06-1988</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MAALIN_22@HOTMAIL.COM</t>
+          <t>CORREOPENDIENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>11-02-2026 16:49:30</t>
+          <t>10-02-2026 15:33:08</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3625,17 +3633,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>14-02-2026 08:55:57</t>
+          <t>10-02-2026 15:37:35</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>14-02-2026 08:55:02</t>
+          <t>10-02-2026 15:36:57</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3655,19 +3663,11 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26020522344200000936</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>MAGALI  ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522234930000790</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>499</t>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342109</t>
+          <t>343706</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3829,17 +3829,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOSE MARIA</t>
+          <t>ALINA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>ALEJO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3849,67 +3849,75 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6151107814</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6862400244</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>06-03-2009</t>
+          <t>04-10-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>JC7651065@GMAIL.COM</t>
+          <t>ALINITA292@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:55</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 11:17:39</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>13-02-2026 11:22:23</t>
+          <t>14-02-2026 11:24:40</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14-02-2026 11:24:09</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3917,44 +3925,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26020522318800000908</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>MAGALI ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522347310000939</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>343706</t>
+          <t>344382</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3964,17 +3964,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ALINA</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ALEJO</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3984,35 +3984,39 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6862400244</t>
+          <t>6861853385</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>MONTE BLANCO</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>04-10-2006</t>
+          <t>23-02-1985</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ALINITA292@GMAIL.COM</t>
+          <t>JULIOREYESS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>14-02-2026 11:17:39</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>17-02-2026 06:30:32</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4030,17 +4034,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>14-02-2026 11:24:40</t>
+          <t>17-02-2026 06:36:06</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>14-02-2026 11:24:09</t>
+          <t>17-02-2026 06:34:33</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4060,7 +4064,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26020522347310000939</t>
+          <t>26020522419620001023</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4072,7 +4076,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4084,12 +4088,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>344382</t>
+          <t>344463</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4099,17 +4103,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t xml:space="preserve">MAYRA MELISSA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>ESCUDERO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4119,57 +4123,53 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6861853385</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>MONTE BLANCO</t>
-        </is>
-      </c>
+          <t>6862890006</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>23-02-1985</t>
+          <t>08-04-2005</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>JULIOREYESS@GMAIL.COM</t>
+          <t>MAYRAESC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>17-02-2026 06:30:32</t>
+          <t>17-02-2026 12:05:45</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>17-02-2026 06:36:06</t>
+          <t>17-02-2026 12:13:51</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4177,21 +4177,13 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>17-02-2026 06:34:33</t>
-        </is>
-      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4199,14 +4191,14 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26020522419620001023</t>
+          <t>26020522426030001036</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4223,12 +4215,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>344463</t>
+          <t>344577</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4238,17 +4230,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYRA MELISSA </t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ESCUDERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4258,28 +4250,28 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6862890006</t>
+          <t>6863899539</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>08-04-2005</t>
+          <t>20-10-2007</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MAYRAESC@GMAIL.COM</t>
+          <t>MORGARSEB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17-02-2026 12:05:45</t>
+          <t>17-02-2026 16:44:08</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4304,12 +4296,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>17-02-2026 12:13:51</t>
+          <t>19-02-2026 16:54:35</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4326,11 +4318,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26020522426030001036</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>26020522499870001128</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>549</t>
@@ -4338,24 +4338,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>344577</t>
+          <t>342109</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>19927</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>JOSE MARIA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6863899539</t>
+          <t>6151107814</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4396,17 +4396,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20-10-2007</t>
+          <t>06-03-2009</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MORGARSEB@GMAIL.COM</t>
+          <t>JC7651065@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17-02-2026 16:44:08</t>
+          <t>09-02-2026 11:19:55</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:35</t>
+          <t>13-02-2026 11:22:23</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26020522499870001128</t>
+          <t>26020522318800000908</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+          <t>MAGALI ROJAS RIVAS</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4485,12 +4485,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342841</t>
+          <t>344673</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ZAYDA ELIZABETH</t>
+          <t>BRENDA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MERAZ</t>
+          <t>ZUÑIGA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4520,14 +4520,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6442093389</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861439833</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4535,60 +4531,56 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18-04-2008</t>
+          <t>20-09-1968</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ZAYDABARRA@GMAIL.COM</t>
+          <t>ESTANCIAINFANTILABC@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:16</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>17-02-2026 19:03:36</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 19:37:59</t>
+          <t>23-02-2026 18:38:56</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>10-02-2026 19:37:25</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4596,36 +4588,44 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26020522247350000807</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+          <t>26020522596630001223</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>MARIA DE LA PAZ MENDEZ ROCHA</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342472</t>
+          <t>343329</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t>KIMBERLY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4655,10 +4655,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861434493</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6865255663</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4666,56 +4670,60 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>10-04-1980</t>
+          <t>22-12-1995</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
+          <t>KIMBERLYCKIMO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 20:01:55</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:11:31</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 20:06:47</t>
+          <t>12-02-2026 17:19:12</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>12-02-2026 17:18:19</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4723,14 +4731,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26020522212980000757</t>
+          <t>26020522299590000883</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4747,12 +4755,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343329</t>
+          <t>343618</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4762,17 +4770,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KIMBERLY</t>
+          <t>IAAN OCTAVIO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>REYNOSA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4782,75 +4790,67 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6865255663</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6862251224</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>22-12-1995</t>
+          <t>03-01-2009</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>KIMBERLYCKIMO@GMAIL.COM</t>
+          <t>CARRILLOIAAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>12-02-2026 17:11:31</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>13-02-2026 21:07:16</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>12-02-2026 17:19:12</t>
+          <t>13-02-2026 21:10:08</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>12-02-2026 17:18:19</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4858,36 +4858,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26020522299590000883</t>
+          <t>26020522331740000929</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343618</t>
+          <t>342472</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4897,17 +4897,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAAN OCTAVIO</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4917,28 +4917,28 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6862251224</t>
+          <t>6861434493</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>03-01-2009</t>
+          <t>10-04-1980</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CARRILLOIAAN@GMAIL.COM</t>
+          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>13-02-2026 21:07:16</t>
+          <t>09-02-2026 20:01:55</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>13-02-2026 21:10:08</t>
+          <t>09-02-2026 20:06:47</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26020522331740000929</t>
+          <t>26020522212980000757</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -4997,24 +4997,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>344232</t>
+          <t>346038</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5024,17 +5024,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t xml:space="preserve">ANGEL </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RICHKARDAY</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5044,28 +5044,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6862316874</t>
+          <t>6863831807</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>02-06-2000</t>
+          <t>21-11-2007</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
+          <t>LEONFE520712@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>16-02-2026 17:42:45</t>
+          <t>23-02-2026 20:04:40</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>17-02-2026 19:32:54</t>
+          <t>23-02-2026 20:05:45</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -5112,19 +5112,11 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26020522444580001061</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522601120001244</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
           <t>899</t>
@@ -5144,12 +5136,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344585</t>
+          <t>342841</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5159,17 +5151,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>ZAYDA ELIZABETH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MERAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5179,67 +5171,75 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6862147023</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6442093389</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>18-04-2008</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JR21675@GMAIL.COM</t>
+          <t>ZAYDABARRA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>17-02-2026 16:52:54</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:33:16</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>17-02-2026 16:54:41</t>
+          <t>10-02-2026 19:37:59</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:37:25</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5247,36 +5247,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26020522435540001049</t>
+          <t>26020522247350000807</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344924</t>
+          <t>344232</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5286,17 +5286,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ASHLY VIVIANA</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>RICHKARDAY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6863062937</t>
+          <t>6862316874</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5317,17 +5317,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>24-09-2012</t>
+          <t>02-06-2000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CECYECY1976@GMAIL.COM</t>
+          <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18-02-2026 18:11:34</t>
+          <t>16-02-2026 17:42:45</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5342,28 +5342,28 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:02</t>
+          <t>17-02-2026 19:32:54</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -5374,36 +5374,44 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26020522471760001096</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26020522444580001061</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344208</t>
+          <t>344585</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5413,17 +5421,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VICTOR ALEXIS</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5433,14 +5441,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6865624438</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>RUISEÑORES</t>
-        </is>
-      </c>
+          <t>6862147023</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5448,64 +5452,56 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>07-04-2010</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>5624438@GMAIL.COM</t>
+          <t>JR21675@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:52</t>
+          <t>17-02-2026 16:52:54</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>16-02-2026 17:23:38</t>
+          <t>17-02-2026 16:54:41</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>16-02-2026 17:22:53</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5513,22 +5509,288 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26020522399070000985</t>
+          <t>26020522435540001049</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>344924</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>22741</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ASHLY VIVIANA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MIRANDA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NAVARRETE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6863062937</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>24-09-2012</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>CECYECY1976@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:11:34</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:14:02</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26020522471760001096</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>344208</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>22025</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VICTOR ALEXIS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>HARO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6865624438</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>RUISEÑORES</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>07-04-2010</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5624438@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:19:52</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:23:38</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:22:53</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26020522399070000985</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,24 +836,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>340308</t>
+          <t>339391</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DAVALOS</t>
+          <t>CELIO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,14 +883,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6862641945</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6863360339</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -898,60 +894,56 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>10-02-1977</t>
+          <t>16-05-2009</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JIMMYSDF39@GMAIL.COM</t>
+          <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-02-2026 17:24:44</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>30-01-2026 16:25:54</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-02-2026 17:34:10</t>
+          <t>03-02-2026 11:38:00</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-02-2026 17:33:28</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -959,19 +951,27 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26020522018870001160</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26020522037270001186</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -983,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>339391</t>
+          <t>340308</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CELIO</t>
+          <t>DAVALOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,10 +1018,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863360339</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6862641945</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1029,56 +1033,60 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>16-05-2009</t>
+          <t>10-02-1977</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
+          <t>JIMMYSDF39@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>30-01-2026 16:25:54</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 17:24:44</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-02-2026 11:38:00</t>
+          <t>02-02-2026 17:34:10</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:33:28</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1086,27 +1094,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020522037270001186</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522018870001160</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340848</t>
+          <t>325528</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1399,34 +1399,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t>JOHNNY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>AGUILA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SWERRANO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6861236171</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ALARCOS 3576</t>
-        </is>
-      </c>
+          <t>6195092751</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1434,60 +1430,56 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>17-11-2007</t>
+          <t>04-06-1973</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>TORRES.NICOLAS2007@GAMIL.COM</t>
+          <t>JONNY.AGUILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>04-02-2026 04:56:34</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>26-11-2025 18:16:09</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>06-02-2026 05:01:48</t>
+          <t>10-02-2026 06:46:00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>06-02-2026 05:01:07</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1495,7 +1487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26020522121930001316</t>
+          <t>26020522223470000776</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1505,17 +1497,17 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>MAGALI ROJAS RIVAS</t>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1527,12 +1519,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340380</t>
+          <t>340848</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1534,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ETHAN JOAQUIN</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZARATE </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>SWERRANO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,12 +1554,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6866192595</t>
+          <t>6861236171</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ALARCOS 3576</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1577,17 +1569,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-07-2002</t>
+          <t>17-11-2007</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ETHAN.ZARATE@UABC.EDU.MX</t>
+          <t>TORRES.NICOLAS2007@GAMIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 19:54:30</t>
+          <t>04-02-2026 04:56:34</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1608,17 +1600,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 19:59:58</t>
+          <t>06-02-2026 05:01:48</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-02-2026 19:58:03</t>
+          <t>06-02-2026 05:01:07</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1628,7 +1620,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1638,11 +1630,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26020522022780001167</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26020522121930001316</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>MAGALI ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>499</t>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1662,12 +1662,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>341431</t>
+          <t>341327</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LUCIANO GUADALUPE</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SALINAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6866068064</t>
+          <t>6865534615</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DSFH</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27-10-1987</t>
+          <t>27-01-2000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
+          <t>GLITCH0127@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>05-02-2026 19:00:48</t>
+          <t>05-02-2026 14:43:26</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>09-02-2026 17:50:19</t>
+          <t>05-02-2026 14:49:36</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>09-02-2026 17:49:53</t>
+          <t>05-02-2026 14:49:16</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1773,19 +1773,11 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26010522204130003399</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522107360001285</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>499</t>
@@ -1793,7 +1785,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1805,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>325528</t>
+          <t>324484</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,87 +1812,95 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>JOHNNY</t>
+          <t>LESLYE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGUILA</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6161286154</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AV DEL JILGUERO 1052</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>30-10-1995</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OLIVASLESLYE2@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>20-11-2025 10:11:37</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>14-02-2026 09:47:10</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>14-02-2026 09:46:17</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6195092751</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>04-06-1973</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>JONNY.AGUILA@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>26-11-2025 18:16:09</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>CONVENIOS $549</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>10-02-2026 06:46:00</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26020522223470000776</t>
+          <t>26150522345040001698</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1923,29 +1923,29 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341769</t>
+          <t>342371</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>20189</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENA </t>
+          <t>VIVIAN AIMEE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>URIAS</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6862828171</t>
+          <t>6863890309</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AV CASCADA SAN ANDRES 4039</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31-08-2007</t>
+          <t>20-06-2010</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
+          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>07-02-2026 09:15:00</t>
+          <t>09-02-2026 18:09:38</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2021,17 +2021,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>07-02-2026 09:21:40</t>
+          <t>09-02-2026 18:20:05</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>07-02-2026 09:20:44</t>
+          <t>09-02-2026 18:19:25</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522157150000681</t>
+          <t>26020522206580000736</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2075,12 +2075,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>342371</t>
+          <t>342185</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VIVIAN AIMEE</t>
+          <t>JESUS MANUEL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,53 +2110,53 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6863890309</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861640070</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>18-05-1961</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
+          <t>CHUCHUNEL61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>09-02-2026 18:09:38</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>09-02-2026 14:42:28</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>09-02-2026 18:20:05</t>
+          <t>09-02-2026 14:44:26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2164,21 +2164,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:19:25</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2186,19 +2178,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26020522206580000736</t>
+          <t>26020522193750000724</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2210,12 +2202,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>324484</t>
+          <t>341431</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2225,17 +2217,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LESLYE</t>
+          <t>LUCIANO GUADALUPE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2245,32 +2237,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6161286154</t>
+          <t>6866068064</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AV DEL JILGUERO 1052</t>
+          <t>DSFH</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>30-10-1995</t>
+          <t>27-10-1987</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>OLIVASLESLYE2@GMAIL.COM</t>
+          <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20-11-2025 10:11:37</t>
+          <t>05-02-2026 19:00:48</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2291,17 +2283,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>14-02-2026 09:47:10</t>
+          <t>09-02-2026 17:50:19</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>14-02-2026 09:46:17</t>
+          <t>09-02-2026 17:49:53</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2321,7 +2313,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26150522345040001698</t>
+          <t>26010522204130003399</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2341,7 +2333,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2353,12 +2345,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341327</t>
+          <t>341769</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2360,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t xml:space="preserve">JIMENA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>URIAS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,32 +2380,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6865534615</t>
+          <t>6862828171</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AV CASCADA SAN ANDRES 4039</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27-01-2000</t>
+          <t>31-08-2007</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>GLITCH0127@GMAIL.COM</t>
+          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>05-02-2026 14:43:26</t>
+          <t>07-02-2026 09:15:00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2434,17 +2426,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>05-02-2026 14:49:36</t>
+          <t>07-02-2026 09:21:40</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>05-02-2026 14:49:16</t>
+          <t>07-02-2026 09:20:44</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2464,7 +2456,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26020522107360001285</t>
+          <t>26020522157150000681</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2488,12 +2480,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342424</t>
+          <t>342440</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2503,17 +2495,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ARANTZA</t>
+          <t>BETZY MARCELA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2523,14 +2515,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4151245575</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>AVENIDA SAN PEDRO MEZQUITL</t>
-        </is>
-      </c>
+          <t>6862559890</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2538,38 +2526,42 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15-07-1997</t>
+          <t>21-06-1992</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
+          <t>BETZY.OMARCE21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 19:07:14</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>09-02-2026 19:28:04</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:59</t>
+          <t>09-02-2026 19:29:53</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2577,21 +2569,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>09-02-2026 19:10:20</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2599,19 +2583,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26020522209900000743</t>
+          <t>26020522210970000750</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2623,12 +2607,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>342440</t>
+          <t>340209</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2638,17 +2622,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BETZY MARCELA</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2658,28 +2642,28 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6862559890</t>
+          <t>6864221370</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21-06-1992</t>
+          <t>13-08-2003</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BETZY.OMARCE21@GMAIL.COM</t>
+          <t>RICHI.CAMACHO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09-02-2026 19:28:04</t>
+          <t>02-02-2026 15:23:20</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2704,12 +2688,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 19:29:53</t>
+          <t>04-02-2026 15:47:22</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2726,11 +2710,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26020522210970000750</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26020522078020001242</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>549</t>
@@ -3020,12 +3012,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342185</t>
+          <t>342672</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3035,17 +3027,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JESUS MANUEL</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3055,67 +3047,75 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6861640070</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>9931258390</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18-05-1961</t>
+          <t>03-06-1988</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CHUCHUNEL61@GMAIL.COM</t>
+          <t>CORREOPENDIENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:28</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:33:08</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 14:44:26</t>
+          <t>10-02-2026 15:37:35</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:36:57</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3123,14 +3123,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26020522193750000724</t>
+          <t>26020522234930000790</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340209</t>
+          <t>340380</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>ETHAN JOAQUIN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t xml:space="preserve">ZARATE </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3182,10 +3182,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6864221370</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6866192595</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3193,56 +3197,60 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13-08-2003</t>
+          <t>15-07-2002</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>RICHI.CAMACHO20@GMAIL.COM</t>
+          <t>ETHAN.ZARATE@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-02-2026 15:23:20</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 19:54:30</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-02-2026 15:47:22</t>
+          <t>02-02-2026 19:59:58</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>02-02-2026 19:58:03</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3250,22 +3258,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26020522078020001242</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522022780001167</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3282,12 +3282,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>343047</t>
+          <t>343129</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARIA ANTONIA</t>
+          <t xml:space="preserve">ALEJANDRA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3317,14 +3317,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6866017324</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>RIO CAOCA 3556</t>
-        </is>
-      </c>
+          <t>6863095804</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3332,60 +3328,56 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>22-09-1969</t>
+          <t>13-05-2006</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MAALIN_22@HOTMAIL.COM</t>
+          <t>ALEJANDRA13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11-02-2026 16:49:30</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>11-02-2026 20:04:50</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>14-02-2026 08:55:57</t>
+          <t>11-02-2026 20:09:00</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>14-02-2026 08:55:02</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3393,44 +3385,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26020522344200000936</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>MAGALI  ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522277990000848</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>343129</t>
+          <t>344382</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3440,17 +3424,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRA </t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3460,67 +3444,79 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6863095804</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6861853385</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MONTE BLANCO</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13-05-2006</t>
+          <t>23-02-1985</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ALEJANDRA13@GMAIL.COM</t>
+          <t>JULIOREYESS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>11-02-2026 20:04:50</t>
+          <t>17-02-2026 06:30:32</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>11-02-2026 20:09:00</t>
+          <t>17-02-2026 06:36:06</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>17-02-2026 06:34:33</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3528,19 +3524,19 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26020522277990000848</t>
+          <t>26020522419620001023</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3552,12 +3548,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342672</t>
+          <t>344463</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3567,17 +3563,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t xml:space="preserve">MAYRA MELISSA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ESCUDERO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3587,14 +3583,10 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9931258390</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6862890006</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3602,60 +3594,56 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>03-06-1988</t>
+          <t>08-04-2005</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CORREOPENDIENTE@GMAIL.COM</t>
+          <t>MAYRAESC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10-02-2026 15:33:08</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>17-02-2026 12:05:45</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:35</t>
+          <t>17-02-2026 12:13:51</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>10-02-2026 15:36:57</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3663,19 +3651,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26020522234930000790</t>
+          <t>26020522426030001036</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3687,12 +3675,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>343209</t>
+          <t>344577</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3702,17 +3690,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3722,24 +3710,28 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6862308375</t>
+          <t>6863899539</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31-01-2009</t>
+          <t>20-10-2007</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>EDWSUCOR@GMAIL.COM</t>
+          <t>MORGARSEB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>12-02-2026 10:56:58</t>
+          <t>17-02-2026 16:44:08</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3764,18 +3756,18 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-02-2026 13:53:04</t>
+          <t>19-02-2026 16:54:35</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3786,15 +3778,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26020522389340000968</t>
+          <t>26020522499870001128</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>549</t>
@@ -3802,24 +3798,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343706</t>
+          <t>342109</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>19927</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3829,17 +3825,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ALINA</t>
+          <t>JOSE MARIA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ALEJO</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3849,75 +3845,67 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6862400244</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6151107814</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>04-10-2006</t>
+          <t>06-03-2009</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ALINITA292@GMAIL.COM</t>
+          <t>JC7651065@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>14-02-2026 11:17:39</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>09-02-2026 11:19:55</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>14-02-2026 11:24:40</t>
+          <t>13-02-2026 11:22:23</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>14-02-2026 11:24:09</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3925,36 +3913,44 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26020522347310000939</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26020522318800000908</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>MAGALI ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>344382</t>
+          <t>344673</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3964,17 +3960,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>BRENDA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>ZUÑIGA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3984,79 +3980,67 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6861853385</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>MONTE BLANCO</t>
-        </is>
-      </c>
+          <t>6861439833</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23-02-1985</t>
+          <t>20-09-1968</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>JULIOREYESS@GMAIL.COM</t>
+          <t>ESTANCIAINFANTILABC@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>17-02-2026 06:30:32</t>
+          <t>17-02-2026 19:03:36</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>17-02-2026 06:36:06</t>
+          <t>23-02-2026 18:38:56</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>17-02-2026 06:34:33</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4064,19 +4048,27 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26020522419620001023</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>26020522596630001223</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>MARIA DE LA PAZ MENDEZ ROCHA</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4088,12 +4080,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>344463</t>
+          <t>342424</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4103,17 +4095,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYRA MELISSA </t>
+          <t>ARANTZA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ESCUDERO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4123,10 +4115,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6862890006</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>4151245575</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AVENIDA SAN PEDRO MEZQUITL</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4134,56 +4130,60 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>08-04-2005</t>
+          <t>15-07-1997</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MAYRAESC@GMAIL.COM</t>
+          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>17-02-2026 12:05:45</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:07:14</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>17-02-2026 12:13:51</t>
+          <t>09-02-2026 19:10:59</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:10:20</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4191,19 +4191,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26020522426030001036</t>
+          <t>26020522209900000743</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4215,12 +4215,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>344577</t>
+          <t>343047</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4230,17 +4230,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>MARIA ANTONIA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4250,67 +4250,75 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6863899539</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6866017324</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>RIO CAOCA 3556</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20-10-2007</t>
+          <t>22-09-1969</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MORGARSEB@GMAIL.COM</t>
+          <t>MAALIN_22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17-02-2026 16:44:08</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 16:49:30</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:35</t>
+          <t>14-02-2026 08:55:57</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>14-02-2026 08:55:02</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4318,7 +4326,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26020522499870001128</t>
+          <t>26020522344200000936</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4328,34 +4336,34 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+          <t>MAGALI  ROJAS RIVAS</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342109</t>
+          <t>343209</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4365,17 +4373,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JOSE MARIA</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4385,28 +4393,24 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6151107814</t>
+          <t>6862308375</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>06-03-2009</t>
+          <t>31-01-2009</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>JC7651065@GMAIL.COM</t>
+          <t>EDWSUCOR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:55</t>
+          <t>12-02-2026 10:56:58</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4431,18 +4435,18 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>13-02-2026 11:22:23</t>
+          <t>16-02-2026 13:53:04</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -4453,19 +4457,15 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26020522318800000908</t>
+          <t>26020522389340000968</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>MAGALI ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
           <t>549</t>
@@ -4485,12 +4485,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>344673</t>
+          <t>343329</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BRENDA</t>
+          <t>KIMBERLY</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ZUÑIGA</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4520,10 +4520,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6861439833</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6865255663</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4531,56 +4535,60 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>20-09-1968</t>
+          <t>22-12-1995</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ESTANCIAINFANTILABC@OUTLOOK.COM</t>
+          <t>KIMBERLYCKIMO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17-02-2026 19:03:36</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:11:31</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>23-02-2026 18:38:56</t>
+          <t>12-02-2026 17:19:12</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>12-02-2026 17:18:19</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4588,44 +4596,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26020522596630001223</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>MARIA DE LA PAZ MENDEZ ROCHA</t>
-        </is>
-      </c>
+          <t>26020522299590000883</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343329</t>
+          <t>343618</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KIMBERLY</t>
+          <t>IAAN OCTAVIO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>REYNOSA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4655,75 +4655,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6865255663</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6862251224</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22-12-1995</t>
+          <t>03-01-2009</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>KIMBERLYCKIMO@GMAIL.COM</t>
+          <t>CARRILLOIAAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>12-02-2026 17:11:31</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>13-02-2026 21:07:16</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-02-2026 17:19:12</t>
+          <t>13-02-2026 21:10:08</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>12-02-2026 17:18:19</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4731,36 +4723,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26020522299590000883</t>
+          <t>26020522331740000929</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343618</t>
+          <t>342472</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4770,17 +4762,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IAAN OCTAVIO</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4790,28 +4782,28 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6862251224</t>
+          <t>6861434493</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>03-01-2009</t>
+          <t>10-04-1980</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CARRILLOIAAN@GMAIL.COM</t>
+          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>13-02-2026 21:07:16</t>
+          <t>09-02-2026 20:01:55</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4836,12 +4828,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>13-02-2026 21:10:08</t>
+          <t>09-02-2026 20:06:47</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4858,7 +4850,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26020522331740000929</t>
+          <t>26020522212980000757</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4870,24 +4862,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342472</t>
+          <t>342841</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4897,17 +4889,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t>ZAYDA ELIZABETH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>MERAZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4917,10 +4909,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861434493</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6442093389</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4928,56 +4924,60 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>10-04-1980</t>
+          <t>18-04-2008</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
+          <t>ZAYDABARRA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 20:01:55</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:33:16</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 20:06:47</t>
+          <t>10-02-2026 19:37:59</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:37:25</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4985,14 +4985,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26020522212980000757</t>
+          <t>26020522247350000807</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5009,12 +5009,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>346038</t>
+          <t>343706</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>88203</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5024,17 +5024,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL </t>
+          <t>ALINA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>ALEJO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5044,67 +5044,75 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6863831807</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6862400244</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21-11-2007</t>
+          <t>04-10-2006</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>LEONFE520712@GMAIL.COM</t>
+          <t>ALINITA292@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>23-02-2026 20:04:40</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 11:17:39</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>23-02-2026 20:05:45</t>
+          <t>14-02-2026 11:24:40</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>14-02-2026 11:24:09</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5112,36 +5120,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26020522601120001244</t>
+          <t>26020522347310000939</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342841</t>
+          <t>346152</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>88317</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5151,17 +5159,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ZAYDA ELIZABETH</t>
+          <t>ANGEL FERNANDO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MERAZ</t>
+          <t xml:space="preserve">ARVIZU </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5171,75 +5179,67 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6442093389</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6622041131</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18-04-2008</t>
+          <t>30-03-2003</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ZAYDABARRA@GMAIL.COM</t>
+          <t>A23311109@UTHERMOSI8LLO.EDU.MX</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:16</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>24-02-2026 13:50:53</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-02-2026 19:37:59</t>
+          <t>24-02-2026 13:53:01</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>10-02-2026 19:37:25</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5247,24 +5247,24 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26020522247350000807</t>
+          <t>26020522619580001267</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5406,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344585</t>
+          <t>345712</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>87877</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5421,17 +5421,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t xml:space="preserve">ROSALINA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>PINEDA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5441,33 +5441,33 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6862147023</t>
+          <t>6861717262</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>14-02-1973</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>JR21675@GMAIL.COM</t>
+          <t>ROXYPYNEBVY@GAMIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17-02-2026 16:52:54</t>
+          <t>23-02-2026 11:25:36</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5477,28 +5477,28 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>17-02-2026 16:54:41</t>
+          <t>25-02-2026 13:02:47</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -5509,14 +5509,18 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26020522435540001049</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
+          <t>26020522652010001320</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5533,12 +5537,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344924</t>
+          <t>346038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5548,17 +5552,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ASHLY VIVIANA</t>
+          <t xml:space="preserve">ANGEL </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5568,28 +5572,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863062937</t>
+          <t>6863831807</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>24-09-2012</t>
+          <t>21-11-2007</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CECYECY1976@GMAIL.COM</t>
+          <t>LEONFE520712@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>18-02-2026 18:11:34</t>
+          <t>23-02-2026 20:04:40</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5604,28 +5608,28 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:02</t>
+          <t>23-02-2026 20:05:45</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5636,19 +5640,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26020522471760001096</t>
+          <t>26020522601120001244</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5660,12 +5664,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344208</t>
+          <t>344585</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5675,17 +5679,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VICTOR ALEXIS</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5695,14 +5699,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6865624438</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>RUISEÑORES</t>
-        </is>
-      </c>
+          <t>6862147023</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5710,64 +5710,56 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>07-04-2010</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5624438@GMAIL.COM</t>
+          <t>JR21675@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:52</t>
+          <t>17-02-2026 16:52:54</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>16-02-2026 17:23:38</t>
+          <t>17-02-2026 16:54:41</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>16-02-2026 17:22:53</t>
-        </is>
-      </c>
+          <t>17-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5775,22 +5767,554 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26020522399070000985</t>
+          <t>26020522435540001049</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>344924</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>22741</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ASHLY VIVIANA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MIRANDA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NAVARRETE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6863062937</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>24-09-2012</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>CECYECY1976@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:11:34</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>18-02-2026 18:14:02</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26020522471760001096</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>344208</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>22025</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VICTOR ALEXIS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>HARO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6865624438</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>RUISEÑORES</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>07-04-2010</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5624438@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:19:52</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:23:38</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:22:53</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26020522399070000985</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>346607</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>88772</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ABRAHAM EDUARDO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>URQUIDEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>AVILEZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6866037590</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>31-07-1995</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>EDUARDOAVLILEZ60@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:32:46</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:37:57</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:37:13</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26020522667910001346</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>346608</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>88773</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>JESUS ANTONIO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LUCERO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6861254848</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>05-02-2007</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>TONNNYYLUUCERO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:43:27</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:50:30</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26020522668100001348</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,12 +848,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>339391</t>
+          <t>119059</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>OLVERA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CELIO</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,28 +883,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6863360339</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6863511539</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CARPATOS</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>16-05-2009</t>
+          <t>20-08-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
+          <t>OLVERAVALERIA322@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>30-01-2026 16:25:54</t>
+          <t>29-08-2022 17:00:29</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -929,7 +933,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-02-2026 11:38:00</t>
+          <t>03-02-2026 16:23:07</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -940,7 +944,7 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -951,19 +955,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26020522037270001186</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26030522045250001467</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -971,7 +967,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -983,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340308</t>
+          <t>230542</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>RAMSES IVAN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DAVALOS</t>
+          <t>BAYLON</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,12 +1014,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6862641945</t>
+          <t>6864633183</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>AV AVES DEL PARAISO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,17 +1029,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>10-02-1977</t>
+          <t>14-08-2007</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JIMMYSDF39@GMAIL.COM</t>
+          <t>22402080067892@CECYTEBC.EDU.MX</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 17:24:44</t>
+          <t>20-04-2024 12:13:17</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1064,17 +1060,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 17:34:10</t>
+          <t>03-02-2026 13:07:22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 17:33:28</t>
+          <t>03-02-2026 13:06:24</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1094,7 +1090,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020522018870001160</t>
+          <t>26020522039060001189</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1106,7 +1102,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1118,12 +1114,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>119059</t>
+          <t>339391</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OLVERA</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>CELIO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,32 +1149,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6863511539</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CARPATOS</t>
-        </is>
-      </c>
+          <t>6863360339</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20-08-2005</t>
+          <t>16-05-2009</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>OLVERAVALERIA322@GMAIL.COM</t>
+          <t>LUISFERNANDOCHIDO69@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>29-08-2022 17:00:29</t>
+          <t>30-01-2026 16:25:54</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1203,7 +1195,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-02-2026 16:23:07</t>
+          <t>03-02-2026 11:38:00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1214,7 +1206,7 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1225,11 +1217,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26030522045250001467</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26020522037270001186</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1249,12 +1249,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>230542</t>
+          <t>340308</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RAMSES IVAN</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BAYLON</t>
+          <t>DAVALOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6864633183</t>
+          <t>6862641945</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AV AVES DEL PARAISO</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14-08-2007</t>
+          <t>10-02-1977</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22402080067892@CECYTEBC.EDU.MX</t>
+          <t>JIMMYSDF39@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>20-04-2024 12:13:17</t>
+          <t>02-02-2026 17:24:44</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-02-2026 13:07:22</t>
+          <t>02-02-2026 17:34:10</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-02-2026 13:06:24</t>
+          <t>02-02-2026 17:33:28</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26020522039060001189</t>
+          <t>26020522018870001160</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340848</t>
+          <t>324484</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t>LESLYE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SWERRANO</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,32 +1554,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6861236171</t>
+          <t>6161286154</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALARCOS 3576</t>
+          <t>AV DEL JILGUERO 1052</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>17-11-2007</t>
+          <t>30-10-1995</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>TORRES.NICOLAS2007@GAMIL.COM</t>
+          <t>OLIVASLESLYE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>04-02-2026 04:56:34</t>
+          <t>20-11-2025 10:11:37</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1600,17 +1600,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>06-02-2026 05:01:48</t>
+          <t>14-02-2026 09:47:10</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>06-02-2026 05:01:07</t>
+          <t>14-02-2026 09:46:17</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26020522121930001316</t>
+          <t>26150522345040001698</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>MAGALI ROJAS RIVAS</t>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1662,12 +1662,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>341327</t>
+          <t>340848</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>SWERRANO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6865534615</t>
+          <t>6861236171</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ALARCOS 3576</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27-01-2000</t>
+          <t>17-11-2007</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GLITCH0127@GMAIL.COM</t>
+          <t>TORRES.NICOLAS2007@GAMIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>05-02-2026 14:43:26</t>
+          <t>04-02-2026 04:56:34</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1743,17 +1743,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>05-02-2026 14:49:36</t>
+          <t>06-02-2026 05:01:48</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>05-02-2026 14:49:16</t>
+          <t>06-02-2026 05:01:07</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1773,11 +1773,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26020522107360001285</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26020522121930001316</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>MAGALI ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>499</t>
@@ -1785,7 +1793,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1797,12 +1805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>324484</t>
+          <t>341431</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1812,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LESLYE</t>
+          <t>LUCIANO GUADALUPE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,32 +1840,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6161286154</t>
+          <t>6866068064</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AV DEL JILGUERO 1052</t>
+          <t>DSFH</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30-10-1995</t>
+          <t>27-10-1987</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OLIVASLESLYE2@GMAIL.COM</t>
+          <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>20-11-2025 10:11:37</t>
+          <t>05-02-2026 19:00:48</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1878,17 +1886,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>14-02-2026 09:47:10</t>
+          <t>09-02-2026 17:50:19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>14-02-2026 09:46:17</t>
+          <t>09-02-2026 17:49:53</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1908,7 +1916,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26150522345040001698</t>
+          <t>26010522204130003399</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1928,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1940,12 +1948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>342371</t>
+          <t>341769</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VIVIAN AIMEE</t>
+          <t xml:space="preserve">JIMENA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>URIAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,12 +1983,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863890309</t>
+          <t>6862828171</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>AV CASCADA SAN ANDRES 4039</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1990,17 +1998,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>31-08-2007</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
+          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>09-02-2026 18:09:38</t>
+          <t>07-02-2026 09:15:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2021,17 +2029,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>09-02-2026 18:20:05</t>
+          <t>07-02-2026 09:21:40</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>09-02-2026 18:19:25</t>
+          <t>07-02-2026 09:20:44</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2051,7 +2059,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522206580000736</t>
+          <t>26020522157150000681</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2063,7 +2071,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2075,12 +2083,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>342185</t>
+          <t>341327</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JESUS MANUEL</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>SALINAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,10 +2118,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6861640070</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6865534615</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2121,56 +2133,60 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18-05-1961</t>
+          <t>27-01-2000</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CHUCHUNEL61@GMAIL.COM</t>
+          <t>GLITCH0127@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:28</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 14:43:26</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>09-02-2026 14:44:26</t>
+          <t>05-02-2026 14:49:36</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>05-02-2026 14:49:16</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2178,14 +2194,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26020522193750000724</t>
+          <t>26020522107360001285</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2202,12 +2218,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341431</t>
+          <t>340209</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2217,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LUCIANO GUADALUPE</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2237,14 +2253,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6866068064</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>DSFH</t>
-        </is>
-      </c>
+          <t>6864221370</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2252,60 +2264,56 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>27-10-1987</t>
+          <t>13-08-2003</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
+          <t>RICHI.CAMACHO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>05-02-2026 19:00:48</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>02-02-2026 15:23:20</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>09-02-2026 17:50:19</t>
+          <t>04-02-2026 15:47:22</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:49:53</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2313,7 +2321,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26010522204130003399</t>
+          <t>26020522078020001242</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2328,12 +2336,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2345,12 +2353,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341769</t>
+          <t>340380</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2360,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENA </t>
+          <t>ETHAN JOAQUIN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">ZARATE </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>URIAS</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2380,32 +2388,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6862828171</t>
+          <t>6866192595</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AV CASCADA SAN ANDRES 4039</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31-08-2007</t>
+          <t>15-07-2002</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
+          <t>ETHAN.ZARATE@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>07-02-2026 09:15:00</t>
+          <t>02-02-2026 19:54:30</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2426,17 +2434,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>07-02-2026 09:21:40</t>
+          <t>02-02-2026 19:59:58</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>07-02-2026 09:20:44</t>
+          <t>02-02-2026 19:58:03</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2456,7 +2464,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26020522157150000681</t>
+          <t>26020522022780001167</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2468,7 +2476,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2607,12 +2615,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340209</t>
+          <t>342185</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2622,17 +2630,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>JESUS MANUEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2642,7 +2650,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6864221370</t>
+          <t>6861640070</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2653,17 +2661,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13-08-2003</t>
+          <t>18-05-1961</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>RICHI.CAMACHO20@GMAIL.COM</t>
+          <t>CHUCHUNEL61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 15:23:20</t>
+          <t>09-02-2026 14:42:28</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2678,28 +2686,28 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-02-2026 15:47:22</t>
+          <t>09-02-2026 14:44:26</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2710,27 +2718,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26020522078020001242</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522193750000724</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3012,12 +3012,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342672</t>
+          <t>342109</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>19927</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3027,17 +3027,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>JOSE MARIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3047,75 +3047,67 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9931258390</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6151107814</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>03-06-1988</t>
+          <t>06-03-2009</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CORREOPENDIENTE@GMAIL.COM</t>
+          <t>JC7651065@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10-02-2026 15:33:08</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>09-02-2026 11:19:55</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:35</t>
+          <t>13-02-2026 11:22:23</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>10-02-2026 15:36:57</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3123,36 +3115,44 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26020522234930000790</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26020522318800000908</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>MAGALI ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340380</t>
+          <t>343129</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ETHAN JOAQUIN</t>
+          <t xml:space="preserve">ALEJANDRA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZARATE </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3182,75 +3182,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6866192595</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>6863095804</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>15-07-2002</t>
+          <t>13-05-2006</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ETHAN.ZARATE@UABC.EDU.MX</t>
+          <t>ALEJANDRA13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-02-2026 19:54:30</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>11-02-2026 20:04:50</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-02-2026 19:59:58</t>
+          <t>11-02-2026 20:09:00</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>02-02-2026 19:58:03</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3258,19 +3250,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26020522022780001167</t>
+          <t>26020522277990000848</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3282,12 +3274,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>343129</t>
+          <t>342672</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3297,17 +3289,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRA </t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3317,10 +3309,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6863095804</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>9931258390</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3328,56 +3324,60 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13-05-2006</t>
+          <t>03-06-1988</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ALEJANDRA13@GMAIL.COM</t>
+          <t>CORREOPENDIENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11-02-2026 20:04:50</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:33:08</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>11-02-2026 20:09:00</t>
+          <t>10-02-2026 15:37:35</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:36:57</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3385,14 +3385,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26020522277990000848</t>
+          <t>26020522234930000790</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>344382</t>
+          <t>342424</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3424,17 +3424,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>ARANTZA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3444,39 +3444,35 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6861853385</t>
+          <t>4151245575</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MONTE BLANCO</t>
+          <t>AVENIDA SAN PEDRO MEZQUITL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23-02-1985</t>
+          <t>15-07-1997</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JULIOREYESS@GMAIL.COM</t>
+          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>17-02-2026 06:30:32</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:07:14</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3484,7 +3480,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3494,17 +3490,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>17-02-2026 06:36:06</t>
+          <t>09-02-2026 19:10:59</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>17-02-2026 06:34:33</t>
+          <t>09-02-2026 19:10:20</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3524,7 +3520,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26020522419620001023</t>
+          <t>26020522209900000743</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3536,7 +3532,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3548,12 +3544,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>344463</t>
+          <t>344382</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3563,17 +3559,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYRA MELISSA </t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ESCUDERO</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3583,53 +3579,57 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6862890006</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6861853385</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MONTE BLANCO</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>08-04-2005</t>
+          <t>23-02-1985</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MAYRAESC@GMAIL.COM</t>
+          <t>JULIOREYESS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>17-02-2026 12:05:45</t>
+          <t>17-02-2026 06:30:32</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>17-02-2026 12:13:51</t>
+          <t>17-02-2026 06:36:06</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3637,13 +3637,21 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>17-02-2026 06:34:33</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3651,14 +3659,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26020522426030001036</t>
+          <t>26020522419620001023</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3675,12 +3683,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344577</t>
+          <t>344463</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3690,17 +3698,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t xml:space="preserve">MAYRA MELISSA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ESCUDERO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3710,28 +3718,28 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6863899539</t>
+          <t>6862890006</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20-10-2007</t>
+          <t>08-04-2005</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MORGARSEB@GMAIL.COM</t>
+          <t>MAYRAESC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17-02-2026 16:44:08</t>
+          <t>17-02-2026 12:05:45</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3756,12 +3764,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:35</t>
+          <t>17-02-2026 12:13:51</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3778,19 +3786,11 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26020522499870001128</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522426030001036</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>549</t>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3810,12 +3810,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342109</t>
+          <t>342472</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3825,17 +3825,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOSE MARIA</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3845,28 +3845,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6151107814</t>
+          <t>6861434493</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>06-03-2009</t>
+          <t>10-04-1980</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>JC7651065@GMAIL.COM</t>
+          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:55</t>
+          <t>09-02-2026 20:01:55</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3891,18 +3891,18 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>13-02-2026 11:22:23</t>
+          <t>09-02-2026 20:06:47</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3913,19 +3913,11 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26020522318800000908</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>MAGALI ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522212980000757</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>549</t>
@@ -3933,24 +3925,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>344673</t>
+          <t>342841</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3960,17 +3952,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BRENDA</t>
+          <t>ZAYDA ELIZABETH</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ZUÑIGA</t>
+          <t>MERAZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3980,10 +3972,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6861439833</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6442093389</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3991,56 +3987,60 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20-09-1968</t>
+          <t>18-04-2008</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ESTANCIAINFANTILABC@OUTLOOK.COM</t>
+          <t>ZAYDABARRA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>17-02-2026 19:03:36</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:33:16</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>23-02-2026 18:38:56</t>
+          <t>10-02-2026 19:37:59</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:37:25</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4048,27 +4048,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26020522596630001223</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>MARIA DE LA PAZ MENDEZ ROCHA</t>
-        </is>
-      </c>
+          <t>26020522247350000807</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4080,12 +4072,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342424</t>
+          <t>343047</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4095,17 +4087,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ARANTZA</t>
+          <t>MARIA ANTONIA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4115,12 +4107,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4151245575</t>
+          <t>6866017324</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AVENIDA SAN PEDRO MEZQUITL</t>
+          <t>RIO CAOCA 3556</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4130,17 +4122,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>15-07-1997</t>
+          <t>22-09-1969</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
+          <t>MAALIN_22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 19:07:14</t>
+          <t>11-02-2026 16:49:30</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4151,7 +4143,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4161,17 +4153,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:59</t>
+          <t>14-02-2026 08:55:57</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:20</t>
+          <t>14-02-2026 08:55:02</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4181,7 +4173,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4191,11 +4183,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26020522209900000743</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26020522344200000936</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>MAGALI  ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>499</t>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4215,12 +4215,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>343047</t>
+          <t>343209</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4230,17 +4230,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MARIA ANTONIA</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4250,75 +4250,63 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6866017324</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>RIO CAOCA 3556</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+          <t>6862308375</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>22-09-1969</t>
+          <t>31-01-2009</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MAALIN_22@HOTMAIL.COM</t>
+          <t>EDWSUCOR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11-02-2026 16:49:30</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>12-02-2026 10:56:58</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>14-02-2026 08:55:57</t>
+          <t>16-02-2026 13:53:04</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>14-02-2026 08:55:02</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4326,44 +4314,40 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26020522344200000936</t>
+          <t>26020522389340000968</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>MAGALI  ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343209</t>
+          <t>344577</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4373,17 +4357,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4393,24 +4377,28 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6862308375</t>
+          <t>6863899539</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31-01-2009</t>
+          <t>20-10-2007</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>EDWSUCOR@GMAIL.COM</t>
+          <t>MORGARSEB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12-02-2026 10:56:58</t>
+          <t>17-02-2026 16:44:08</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4435,18 +4423,18 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16-02-2026 13:53:04</t>
+          <t>19-02-2026 16:54:35</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -4457,15 +4445,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26020522389340000968</t>
+          <t>26020522499870001128</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>549</t>
@@ -4473,24 +4465,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>343329</t>
+          <t>344673</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4500,17 +4492,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KIMBERLY</t>
+          <t>BRENDA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>ZUÑIGA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4520,14 +4512,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6865255663</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861439833</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4535,60 +4523,56 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22-12-1995</t>
+          <t>20-09-1968</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>KIMBERLYCKIMO@GMAIL.COM</t>
+          <t>ESTANCIAINFANTILABC@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>12-02-2026 17:11:31</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>17-02-2026 19:03:36</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>12-02-2026 17:19:12</t>
+          <t>23-02-2026 18:38:56</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>12-02-2026 17:18:19</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4596,19 +4580,27 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26020522299590000883</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+          <t>26020522596630001223</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>MARIA DE LA PAZ MENDEZ ROCHA</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4620,12 +4612,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343618</t>
+          <t>343329</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4635,17 +4627,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IAAN OCTAVIO</t>
+          <t>KIMBERLY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4655,67 +4647,75 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6862251224</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6865255663</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>03-01-2009</t>
+          <t>22-12-1995</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CARRILLOIAAN@GMAIL.COM</t>
+          <t>KIMBERLYCKIMO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>13-02-2026 21:07:16</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:11:31</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>13-02-2026 21:10:08</t>
+          <t>12-02-2026 17:19:12</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>12-02-2026 17:18:19</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4723,36 +4723,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26020522331740000929</t>
+          <t>26020522299590000883</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342472</t>
+          <t>342371</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>20189</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4762,17 +4762,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t>VIVIAN AIMEE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4782,10 +4782,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6861434493</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6863890309</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4793,42 +4797,38 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>10-04-1980</t>
+          <t>20-06-2010</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
+          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-02-2026 20:01:55</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 18:09:38</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>09-02-2026 20:06:47</t>
+          <t>09-02-2026 18:20:05</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4836,13 +4836,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>09-02-2026 18:19:25</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4850,19 +4858,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26020522212980000757</t>
+          <t>26020522206580000736</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4874,12 +4882,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342841</t>
+          <t>343618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4889,17 +4897,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ZAYDA ELIZABETH</t>
+          <t>IAAN OCTAVIO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MERAZ</t>
+          <t>REYNOSA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4909,75 +4917,67 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6442093389</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6862251224</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18-04-2008</t>
+          <t>03-01-2009</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ZAYDABARRA@GMAIL.COM</t>
+          <t>CARRILLOIAAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:16</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>13-02-2026 21:07:16</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10-02-2026 19:37:59</t>
+          <t>13-02-2026 21:10:08</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>10-02-2026 19:37:25</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4985,24 +4985,24 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26020522247350000807</t>
+          <t>26020522331740000929</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>346152</t>
+          <t>344232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>88317</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5159,17 +5159,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ANGEL FERNANDO</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARVIZU </t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>RICHKARDAY</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5179,33 +5179,33 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6622041131</t>
+          <t>6862316874</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>30-03-2003</t>
+          <t>02-06-2000</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>A23311109@UTHERMOSI8LLO.EDU.MX</t>
+          <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>24-02-2026 13:50:53</t>
+          <t>16-02-2026 17:42:45</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5215,28 +5215,28 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>24-02-2026 13:53:01</t>
+          <t>17-02-2026 19:32:54</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5247,14 +5247,22 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26020522619580001267</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26020522444580001061</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5271,12 +5279,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344232</t>
+          <t>344208</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5286,17 +5294,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>VICTOR ALEXIS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RICHKARDAY</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5306,67 +5314,79 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6862316874</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6865624438</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>RUISEÑORES</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>02-06-2000</t>
+          <t>07-04-2010</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
+          <t>5624438@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16-02-2026 17:42:45</t>
+          <t>16-02-2026 17:19:52</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>17-02-2026 19:32:54</t>
+          <t>16-02-2026 17:23:38</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>16-02-2026 17:22:53</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5374,22 +5394,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26020522444580001061</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522399070000985</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5406,12 +5418,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>345712</t>
+          <t>344585</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>87877</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5421,17 +5433,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSALINA </t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PINEDA</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5441,33 +5453,33 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6861717262</t>
+          <t>6862147023</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14-02-1973</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ROXYPYNEBVY@GAMIL.COM</t>
+          <t>JR21675@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>23-02-2026 11:25:36</t>
+          <t>17-02-2026 16:52:54</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -5477,28 +5489,28 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>25-02-2026 13:02:47</t>
+          <t>17-02-2026 16:54:41</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>17-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -5509,18 +5521,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26020522652010001320</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020522435540001049</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5537,12 +5545,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>346038</t>
+          <t>344924</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>88203</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5552,17 +5560,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL </t>
+          <t>ASHLY VIVIANA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5572,28 +5580,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863831807</t>
+          <t>6863062937</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21-11-2007</t>
+          <t>24-09-2012</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>LEONFE520712@GMAIL.COM</t>
+          <t>CECYECY1976@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>23-02-2026 20:04:40</t>
+          <t>18-02-2026 18:11:34</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5608,28 +5616,28 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>23-02-2026 20:05:45</t>
+          <t>18-02-2026 18:14:02</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5640,19 +5648,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26020522601120001244</t>
+          <t>26020522471760001096</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5664,12 +5672,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344585</t>
+          <t>346152</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>88317</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5679,17 +5687,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>ANGEL FERNANDO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">ARVIZU </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5699,7 +5707,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6862147023</t>
+          <t>6622041131</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5710,22 +5718,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>30-03-2003</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JR21675@GMAIL.COM</t>
+          <t>A23311109@UTHERMOSI8LLO.EDU.MX</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>17-02-2026 16:52:54</t>
+          <t>24-02-2026 13:50:53</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -5735,22 +5743,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-02-2026 16:54:41</t>
+          <t>24-02-2026 13:53:01</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -5767,14 +5775,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26020522435540001049</t>
+          <t>26020522619580001267</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5791,12 +5799,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344924</t>
+          <t>346607</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>88772</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5806,17 +5814,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ASHLY VIVIANA</t>
+          <t>ABRAHAM EDUARDO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>URQUIDEZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>AVILEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5826,67 +5834,79 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6863062937</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6866037590</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>24-09-2012</t>
+          <t>31-07-1995</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CECYECY1976@GMAIL.COM</t>
+          <t>EDUARDOAVLILEZ60@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>18-02-2026 18:11:34</t>
+          <t>25-02-2026 20:32:46</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:02</t>
+          <t>25-02-2026 20:37:57</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:37:13</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5894,36 +5914,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26020522471760001096</t>
+          <t>26020522667910001346</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344208</t>
+          <t>346608</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>88773</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5933,17 +5953,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VICTOR ALEXIS</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>LUCERO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5953,14 +5973,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6865624438</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>RUISEÑORES</t>
-        </is>
-      </c>
+          <t>6861254848</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5968,64 +5984,56 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>07-04-2010</t>
+          <t>05-02-2007</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5624438@GMAIL.COM</t>
+          <t>TONNNYYLUUCERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:52</t>
+          <t>25-02-2026 20:43:27</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>16-02-2026 17:23:38</t>
+          <t>25-02-2026 20:50:30</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>16-02-2026 17:22:53</t>
-        </is>
-      </c>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6033,14 +6041,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26020522399070000985</t>
+          <t>26020522668100001348</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6057,12 +6065,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>346607</t>
+          <t>346759</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>88772</t>
+          <t>88924</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6072,17 +6080,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ABRAHAM EDUARDO</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>URQUIDEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AVILEZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6092,14 +6100,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6866037590</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861523562</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6107,64 +6111,56 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>31-07-1995</t>
+          <t>14-01-1982</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>EDUARDOAVLILEZ60@GMAIL.COM</t>
+          <t>TORRESCHAVEZA63@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>25-02-2026 20:32:46</t>
+          <t>26-02-2026 16:52:41</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>25-02-2026 20:37:57</t>
+          <t>26-02-2026 16:54:55</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>25-02-2026 20:37:13</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6172,14 +6168,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26020522667910001346</t>
+          <t>26020522688090001365</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6196,12 +6192,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>346608</t>
+          <t>345712</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>88773</t>
+          <t>87877</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6211,17 +6207,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t xml:space="preserve">ROSALINA </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>PINEDA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6231,28 +6227,28 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6861254848</t>
+          <t>6861717262</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>05-02-2007</t>
+          <t>14-02-1973</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>TONNNYYLUUCERO@GMAIL.COM</t>
+          <t>ROXYPYNEBVY@GAMIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>25-02-2026 20:43:27</t>
+          <t>23-02-2026 11:25:36</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6277,7 +6273,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>25-02-2026 20:50:30</t>
+          <t>25-02-2026 13:02:47</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -6299,10 +6295,14 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26020522668100001348</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
+          <t>26020522652010001320</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
@@ -6317,6 +6317,133 @@
       <c r="AC44" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>346038</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>88203</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGEL </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>FELIX</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6863831807</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>21-11-2007</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>LEONFE520712@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:04:40</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:05:45</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26020522601120001244</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,12 +848,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>119059</t>
+          <t>84976</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>82759</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>ROBERTO CARLOS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OLVERA</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,32 +883,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6863511539</t>
+          <t>6862402503</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CARPATOS</t>
+          <t>RIO MARRON 3573</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-08-2005</t>
+          <t>25-08-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>OLVERAVALERIA322@GMAIL.COM</t>
+          <t>ROBERTOJR252018@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>29-08-2022 17:00:29</t>
+          <t>12-04-2022 16:15:41</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -918,36 +918,44 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-02-2026 16:23:07</t>
+          <t>27-02-2026 18:59:34</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>27-02-2026 18:58:58</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,36 +963,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26030522045250001467</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26020522723860001405</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>230542</t>
+          <t>273830</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28047</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RAMSES IVAN</t>
+          <t>JASMINE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BAYLON</t>
+          <t>MARIN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,35 +1030,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6864633183</t>
+          <t>6861583545</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AV AVES DEL PARAISO</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14-08-2007</t>
+          <t>04-12-1987</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>22402080067892@CECYTEBC.EDU.MX</t>
+          <t>JAS0412@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20-04-2024 12:13:17</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>13-01-2025 20:31:12</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1060,17 +1080,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-02-2026 13:07:22</t>
+          <t>27-02-2026 16:06:17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>03-02-2026 13:06:24</t>
+          <t>27-02-2026 16:05:37</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1080,7 +1100,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1090,7 +1110,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020522039060001189</t>
+          <t>26020522717590001395</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1102,12 +1122,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1269,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340308</t>
+          <t>119059</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>OLVERA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DAVALOS</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,75 +1304,71 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6862641945</t>
+          <t>6863511539</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>CARPATOS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10-02-1977</t>
+          <t>20-08-2005</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JIMMYSDF39@GMAIL.COM</t>
+          <t>OLVERAVALERIA322@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 17:24:44</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>29-08-2022 17:00:29</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 17:34:10</t>
+          <t>03-02-2026 16:23:07</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-02-2026 17:33:28</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1360,19 +1376,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26020522018870001160</t>
+          <t>26030522045250001467</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1384,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>325528</t>
+          <t>230542</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1399,87 +1415,95 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JOHNNY</t>
+          <t>RAMSES IVAN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AGUILA</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>BAYLON</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6864633183</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AV AVES DEL PARAISO</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>14-08-2007</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>22402080067892@CECYTEBC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>20-04-2024 12:13:17</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>03-02-2026 13:07:22</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>03-02-2026 13:06:24</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>6195092751</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>04-06-1973</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>JONNY.AGUILA@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>26-11-2025 18:16:09</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>CONVENIOS $549</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>10-02-2026 06:46:00</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1487,27 +1511,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26020522223470000776</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522039060001189</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>324484</t>
+          <t>340308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LESLYE</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OLIVAS</t>
+          <t>DAVALOS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,32 +1570,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6161286154</t>
+          <t>6862641945</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AV DEL JILGUERO 1052</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30-10-1995</t>
+          <t>10-02-1977</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>OLIVASLESLYE2@GMAIL.COM</t>
+          <t>JIMMYSDF39@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>20-11-2025 10:11:37</t>
+          <t>02-02-2026 17:24:44</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1600,17 +1616,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>14-02-2026 09:47:10</t>
+          <t>02-02-2026 17:34:10</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>14-02-2026 09:46:17</t>
+          <t>02-02-2026 17:33:28</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1630,19 +1646,11 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26150522345040001698</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522018870001160</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>499</t>
@@ -1650,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1662,12 +1670,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340848</t>
+          <t>325528</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,34 +1685,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t>JOHNNY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>AGUILA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SWERRANO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6861236171</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ALARCOS 3576</t>
-        </is>
-      </c>
+          <t>6195092751</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1712,60 +1716,56 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>17-11-2007</t>
+          <t>04-06-1973</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>TORRES.NICOLAS2007@GAMIL.COM</t>
+          <t>JONNY.AGUILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>04-02-2026 04:56:34</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>26-11-2025 18:16:09</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>06-02-2026 05:01:48</t>
+          <t>10-02-2026 06:46:00</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>06-02-2026 05:01:07</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26020522121930001316</t>
+          <t>26020522223470000776</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>MAGALI ROJAS RIVAS</t>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1805,12 +1805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341431</t>
+          <t>324484</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LUCIANO GUADALUPE</t>
+          <t>LESLYE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>OLIVAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,32 +1840,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6866068064</t>
+          <t>6161286154</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DSFH</t>
+          <t>AV DEL JILGUERO 1052</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27-10-1987</t>
+          <t>30-10-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
+          <t>OLIVASLESLYE2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>05-02-2026 19:00:48</t>
+          <t>20-11-2025 10:11:37</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1886,17 +1886,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-02-2026 17:50:19</t>
+          <t>14-02-2026 09:47:10</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>09-02-2026 17:49:53</t>
+          <t>14-02-2026 09:46:17</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26010522204130003399</t>
+          <t>26150522345040001698</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1948,12 +1948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341769</t>
+          <t>342371</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>20189</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENA </t>
+          <t>VIVIAN AIMEE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>URIAS</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6862828171</t>
+          <t>6863890309</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AV CASCADA SAN ANDRES 4039</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31-08-2007</t>
+          <t>20-06-2010</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
+          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>07-02-2026 09:15:00</t>
+          <t>09-02-2026 18:09:38</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2029,17 +2029,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>07-02-2026 09:21:40</t>
+          <t>09-02-2026 18:20:05</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>07-02-2026 09:20:44</t>
+          <t>09-02-2026 18:19:25</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522157150000681</t>
+          <t>26020522206580000736</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2083,12 +2083,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341327</t>
+          <t>340848</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>SWERRANO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6865534615</t>
+          <t>6861236171</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ALARCOS 3576</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27-01-2000</t>
+          <t>17-11-2007</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>GLITCH0127@GMAIL.COM</t>
+          <t>TORRES.NICOLAS2007@GAMIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>05-02-2026 14:43:26</t>
+          <t>04-02-2026 04:56:34</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2164,17 +2164,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05-02-2026 14:49:36</t>
+          <t>06-02-2026 05:01:48</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>05-02-2026 14:49:16</t>
+          <t>06-02-2026 05:01:07</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2194,11 +2194,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26020522107360001285</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26020522121930001316</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>MAGALI ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>499</t>
@@ -2206,7 +2214,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2218,12 +2226,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340209</t>
+          <t>342440</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2241,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>BETZY MARCELA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,28 +2261,28 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6864221370</t>
+          <t>6862559890</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>13-08-2003</t>
+          <t>21-06-1992</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>RICHI.CAMACHO20@GMAIL.COM</t>
+          <t>BETZY.OMARCE21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 15:23:20</t>
+          <t>09-02-2026 19:28:04</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2299,12 +2307,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-02-2026 15:47:22</t>
+          <t>09-02-2026 19:29:53</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2321,19 +2329,11 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26020522078020001242</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522210970000750</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
           <t>549</t>
@@ -2353,12 +2353,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340380</t>
+          <t>341431</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ETHAN JOAQUIN</t>
+          <t>LUCIANO GUADALUPE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZARATE </t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6866192595</t>
+          <t>6866068064</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>DSFH</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2403,17 +2403,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>15-07-2002</t>
+          <t>27-10-1987</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ETHAN.ZARATE@UABC.EDU.MX</t>
+          <t>LUCIANO.VARGAS@COBACHBC.EDU.MX</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 19:54:30</t>
+          <t>05-02-2026 19:00:48</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2434,17 +2434,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-02-2026 19:59:58</t>
+          <t>09-02-2026 17:50:19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-02-2026 19:58:03</t>
+          <t>09-02-2026 17:49:53</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2464,11 +2464,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26020522022780001167</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26010522204130003399</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2476,7 +2484,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2488,12 +2496,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342440</t>
+          <t>341769</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2503,17 +2511,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BETZY MARCELA</t>
+          <t xml:space="preserve">JIMENA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>URIAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2523,10 +2531,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6862559890</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6862828171</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AV CASCADA SAN ANDRES 4039</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2534,56 +2546,60 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21-06-1992</t>
+          <t>31-08-2007</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BETZY.OMARCE21@GMAIL.COM</t>
+          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 19:28:04</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 09:15:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 19:29:53</t>
+          <t>07-02-2026 09:21:40</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>07-02-2026 09:20:44</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2591,19 +2607,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26020522210970000750</t>
+          <t>26020522157150000681</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2615,12 +2631,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>342185</t>
+          <t>340209</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2630,17 +2646,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JESUS MANUEL</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2650,7 +2666,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861640070</t>
+          <t>6864221370</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2661,17 +2677,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18-05-1961</t>
+          <t>13-08-2003</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CHUCHUNEL61@GMAIL.COM</t>
+          <t>RICHI.CAMACHO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:28</t>
+          <t>02-02-2026 15:23:20</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2686,28 +2702,28 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>09-02-2026 14:44:26</t>
+          <t>04-02-2026 15:47:22</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2718,19 +2734,27 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26020522193750000724</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26020522078020001242</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2742,12 +2766,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>342438</t>
+          <t>340380</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2757,17 +2781,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BRAYAN SALIM</t>
+          <t>ETHAN JOAQUIN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERIA </t>
+          <t xml:space="preserve">ZARATE </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2777,12 +2801,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6861320570</t>
+          <t>6866192595</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>FRANCISCO BARRIOS</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2792,17 +2816,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12-10-2002</t>
+          <t>15-07-2002</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SALIMSOTO17@GMAIL.COM</t>
+          <t>ETHAN.ZARATE@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>09-02-2026 19:20:31</t>
+          <t>02-02-2026 19:54:30</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2823,17 +2847,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>09-02-2026 19:23:06</t>
+          <t>02-02-2026 19:59:58</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>09-02-2026 19:22:51</t>
+          <t>02-02-2026 19:58:03</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2843,7 +2867,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2853,7 +2877,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26020522210660000748</t>
+          <t>26020522022780001167</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2877,12 +2901,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342486</t>
+          <t>341327</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20303</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2892,17 +2916,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OSCAR</t>
+          <t>ANGEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VARGAS</t>
+          <t>SALINAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2912,12 +2936,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6641882731</t>
+          <t>6865534615</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2927,17 +2951,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>15-11-1988</t>
+          <t>27-01-2000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>OSCAR.88GV@GMAIL.COM</t>
+          <t>GLITCH0127@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-02-2026 20:25:31</t>
+          <t>05-02-2026 14:43:26</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2958,17 +2982,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-02-2026 20:34:45</t>
+          <t>05-02-2026 14:49:36</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>09-02-2026 20:33:58</t>
+          <t>05-02-2026 14:49:16</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2988,7 +3012,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26020522213890000759</t>
+          <t>26020522107360001285</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3000,7 +3024,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3012,12 +3036,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342109</t>
+          <t>342438</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3027,17 +3051,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JOSE MARIA</t>
+          <t>BRAYAN SALIM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t xml:space="preserve">FERIA </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3047,10 +3071,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6151107814</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6861320570</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FRANCISCO BARRIOS</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3058,56 +3086,60 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>06-03-2009</t>
+          <t>12-10-2002</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>JC7651065@GMAIL.COM</t>
+          <t>SALIMSOTO17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 11:19:55</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:20:31</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>13-02-2026 11:22:23</t>
+          <t>09-02-2026 19:23:06</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:22:51</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3115,44 +3147,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26020522318800000908</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>MAGALI ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522210660000748</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>343129</t>
+          <t>342486</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3162,17 +3186,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRA </t>
+          <t>OSCAR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3182,67 +3206,75 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6863095804</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6641882731</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13-05-2006</t>
+          <t>15-11-1988</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ALEJANDRA13@GMAIL.COM</t>
+          <t>OSCAR.88GV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>11-02-2026 20:04:50</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 20:25:31</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>11-02-2026 20:09:00</t>
+          <t>09-02-2026 20:34:45</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>09-02-2026 20:33:58</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3250,19 +3282,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26020522277990000848</t>
+          <t>26020522213890000759</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3274,12 +3306,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342672</t>
+          <t>342185</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3289,17 +3321,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ANA</t>
+          <t>JESUS MANUEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3309,75 +3341,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9931258390</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861640070</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03-06-1988</t>
+          <t>18-05-1961</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CORREOPENDIENTE@GMAIL.COM</t>
+          <t>CHUCHUNEL61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10-02-2026 15:33:08</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>09-02-2026 14:42:28</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:35</t>
+          <t>09-02-2026 14:44:26</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>10-02-2026 15:36:57</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3385,14 +3409,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26020522234930000790</t>
+          <t>26020522193750000724</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3409,12 +3433,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342424</t>
+          <t>344382</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3424,17 +3448,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ARANTZA</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3444,35 +3468,39 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4151245575</t>
+          <t>6861853385</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AVENIDA SAN PEDRO MEZQUITL</t>
+          <t>MONTE BLANCO</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>15-07-1997</t>
+          <t>23-02-1985</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
+          <t>JULIOREYESS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 19:07:14</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>17-02-2026 06:30:32</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3480,7 +3508,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3490,17 +3518,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:59</t>
+          <t>17-02-2026 06:36:06</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:20</t>
+          <t>17-02-2026 06:34:33</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3520,7 +3548,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26020522209900000743</t>
+          <t>26020522419620001023</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3532,7 +3560,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3544,12 +3572,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>344382</t>
+          <t>344463</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3559,17 +3587,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t xml:space="preserve">MAYRA MELISSA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>ESCUDERO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3579,57 +3607,53 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6861853385</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>MONTE BLANCO</t>
-        </is>
-      </c>
+          <t>6862890006</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23-02-1985</t>
+          <t>08-04-2005</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>JULIOREYESS@GMAIL.COM</t>
+          <t>MAYRAESC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>17-02-2026 06:30:32</t>
+          <t>17-02-2026 12:05:45</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>17-02-2026 06:36:06</t>
+          <t>17-02-2026 12:13:51</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3637,21 +3661,13 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>17-02-2026 06:34:33</t>
-        </is>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3659,14 +3675,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26020522419620001023</t>
+          <t>26020522426030001036</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3683,12 +3699,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344463</t>
+          <t>344577</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3698,17 +3714,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAYRA MELISSA </t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ESCUDERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3718,28 +3734,28 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6862890006</t>
+          <t>6863899539</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08-04-2005</t>
+          <t>20-10-2007</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MAYRAESC@GMAIL.COM</t>
+          <t>MORGARSEB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17-02-2026 12:05:45</t>
+          <t>17-02-2026 16:44:08</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3764,12 +3780,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>17-02-2026 12:13:51</t>
+          <t>19-02-2026 16:54:35</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3786,11 +3802,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26020522426030001036</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26020522499870001128</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>549</t>
@@ -3798,7 +3822,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3810,12 +3834,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342472</t>
+          <t>344673</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3825,17 +3849,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t>BRENDA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>ZUÑIGA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3845,7 +3869,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6861434493</t>
+          <t>6861439833</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3856,17 +3880,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>10-04-1980</t>
+          <t>20-09-1968</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
+          <t>ESTANCIAINFANTILABC@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 20:01:55</t>
+          <t>17-02-2026 19:03:36</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3881,22 +3905,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 20:06:47</t>
+          <t>23-02-2026 18:38:56</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3913,19 +3937,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26020522212980000757</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26020522596630001223</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>MARIA DE LA PAZ MENDEZ ROCHA</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3937,12 +3969,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342841</t>
+          <t>342109</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>19927</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3952,17 +3984,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ZAYDA ELIZABETH</t>
+          <t>JOSE MARIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MERAZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3972,75 +4004,67 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6442093389</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6151107814</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>18-04-2008</t>
+          <t>06-03-2009</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ZAYDABARRA@GMAIL.COM</t>
+          <t>JC7651065@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10-02-2026 19:33:16</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>09-02-2026 11:19:55</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-02-2026 19:37:59</t>
+          <t>13-02-2026 11:22:23</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>10-02-2026 19:37:25</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4048,36 +4072,44 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26020522247350000807</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>26020522318800000908</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>MAGALI ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>343047</t>
+          <t>343129</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4087,17 +4119,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MARIA ANTONIA</t>
+          <t xml:space="preserve">ALEJANDRA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4107,14 +4139,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6866017324</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>RIO CAOCA 3556</t>
-        </is>
-      </c>
+          <t>6863095804</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4122,60 +4150,56 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22-09-1969</t>
+          <t>13-05-2006</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MAALIN_22@HOTMAIL.COM</t>
+          <t>ALEJANDRA13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>11-02-2026 16:49:30</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>11-02-2026 20:04:50</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>14-02-2026 08:55:57</t>
+          <t>11-02-2026 20:09:00</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>14-02-2026 08:55:02</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4183,27 +4207,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26020522344200000936</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>MAGALI  ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522277990000848</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4215,12 +4231,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>343209</t>
+          <t>342424</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4230,17 +4246,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>ARANTZA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4250,63 +4266,75 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6862308375</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>4151245575</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AVENIDA SAN PEDRO MEZQUITL</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31-01-2009</t>
+          <t>15-07-1997</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>EDWSUCOR@GMAIL.COM</t>
+          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>12-02-2026 10:56:58</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:07:14</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>16-02-2026 13:53:04</t>
+          <t>09-02-2026 19:10:59</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:10:20</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4314,40 +4342,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26020522389340000968</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26020522209900000743</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>344577</t>
+          <t>342672</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4357,17 +4381,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SEBASTIAN</t>
+          <t>ANA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4377,67 +4401,75 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6863899539</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>9931258390</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20-10-2007</t>
+          <t>03-06-1988</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MORGARSEB@GMAIL.COM</t>
+          <t>CORREOPENDIENTE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17-02-2026 16:44:08</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:33:08</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>19-02-2026 16:54:35</t>
+          <t>10-02-2026 15:37:35</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:36:57</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4445,27 +4477,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26020522499870001128</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522234930000790</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4477,12 +4501,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>344673</t>
+          <t>342841</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4492,17 +4516,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BRENDA</t>
+          <t>ZAYDA ELIZABETH</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ZUÑIGA</t>
+          <t>MERAZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4512,10 +4536,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6861439833</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6442093389</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4523,56 +4551,60 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>20-09-1968</t>
+          <t>18-04-2008</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ESTANCIAINFANTILABC@OUTLOOK.COM</t>
+          <t>ZAYDABARRA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17-02-2026 19:03:36</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:33:16</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>23-02-2026 18:38:56</t>
+          <t>10-02-2026 19:37:59</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:37:25</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4580,27 +4612,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26020522596630001223</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>MARIA DE LA PAZ MENDEZ ROCHA</t>
-        </is>
-      </c>
+          <t>26020522247350000807</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4612,12 +4636,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343329</t>
+          <t>342472</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4627,17 +4651,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KIMBERLY</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4647,14 +4671,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6865255663</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861434493</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4662,60 +4682,56 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22-12-1995</t>
+          <t>10-04-1980</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>KIMBERLYCKIMO@GMAIL.COM</t>
+          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>12-02-2026 17:11:31</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>09-02-2026 20:01:55</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-02-2026 17:19:12</t>
+          <t>09-02-2026 20:06:47</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>12-02-2026 17:18:19</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4723,14 +4739,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26020522299590000883</t>
+          <t>26020522212980000757</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4747,12 +4763,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342371</t>
+          <t>343047</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20189</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4762,17 +4778,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VIVIAN AIMEE</t>
+          <t>MARIA ANTONIA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4782,12 +4798,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6863890309</t>
+          <t>6866017324</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>RIO CAOCA 3556</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4797,17 +4813,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>22-09-1969</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VIVIANAIMEELORETO@GMAIL.COM</t>
+          <t>MAALIN_22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-02-2026 18:09:38</t>
+          <t>11-02-2026 16:49:30</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4828,17 +4844,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>09-02-2026 18:20:05</t>
+          <t>14-02-2026 08:55:57</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>09-02-2026 18:19:25</t>
+          <t>14-02-2026 08:55:02</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4848,7 +4864,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4858,11 +4874,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26020522206580000736</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26020522344200000936</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>MAGALI  ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4870,7 +4894,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4882,12 +4906,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343618</t>
+          <t>343329</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4897,17 +4921,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IAAN OCTAVIO</t>
+          <t>KIMBERLY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4917,67 +4941,75 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6862251224</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6865255663</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>03-01-2009</t>
+          <t>22-12-1995</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CARRILLOIAAN@GMAIL.COM</t>
+          <t>KIMBERLYCKIMO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>13-02-2026 21:07:16</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:11:31</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>13-02-2026 21:10:08</t>
+          <t>12-02-2026 17:19:12</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>12-02-2026 17:18:19</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4985,36 +5017,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26020522331740000929</t>
+          <t>26020522299590000883</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343706</t>
+          <t>343209</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5024,17 +5056,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ALINA</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ALEJO</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5044,75 +5076,63 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6862400244</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
+          <t>6862308375</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>04-10-2006</t>
+          <t>31-01-2009</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ALINITA292@GMAIL.COM</t>
+          <t>EDWSUCOR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>14-02-2026 11:17:39</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>12-02-2026 10:56:58</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>14-02-2026 11:24:40</t>
+          <t>16-02-2026 13:53:04</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>14-02-2026 11:24:09</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5120,36 +5140,40 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26020522347310000939</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
+          <t>26020522389340000968</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344232</t>
+          <t>343618</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5159,17 +5183,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>IAAN OCTAVIO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>REYNOSA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RICHKARDAY</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5179,28 +5203,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6862316874</t>
+          <t>6862251224</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>02-06-2000</t>
+          <t>03-01-2009</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
+          <t>CARRILLOIAAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16-02-2026 17:42:45</t>
+          <t>13-02-2026 21:07:16</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5215,28 +5239,28 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>17-02-2026 19:32:54</t>
+          <t>13-02-2026 21:10:08</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5247,22 +5271,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26020522444580001061</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522331740000929</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5279,12 +5295,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344208</t>
+          <t>343706</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5294,17 +5310,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VICTOR ALEXIS</t>
+          <t>ALINA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>ALEJO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5314,39 +5330,35 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6865624438</t>
+          <t>6862400244</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>RUISEÑORES</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>07-04-2010</t>
+          <t>04-10-2006</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5624438@GMAIL.COM</t>
+          <t>ALINITA292@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16-02-2026 17:19:52</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>14-02-2026 11:17:39</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5364,17 +5376,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>16-02-2026 17:23:38</t>
+          <t>14-02-2026 11:24:40</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>16-02-2026 17:22:53</t>
+          <t>14-02-2026 11:24:09</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5384,7 +5396,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5394,7 +5406,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26020522399070000985</t>
+          <t>26020522347310000939</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5406,24 +5418,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344585</t>
+          <t>344232</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5433,17 +5445,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>JESUS</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>RIOS</t>
+          <t>RICHKARDAY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5453,28 +5465,28 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6862147023</t>
+          <t>6862316874</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>29-08-1994</t>
+          <t>02-06-2000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>JR21675@GMAIL.COM</t>
+          <t>QUINTERO.VALERIA@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17-02-2026 16:52:54</t>
+          <t>16-02-2026 17:42:45</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5489,28 +5501,28 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>17-02-2026 16:54:41</t>
+          <t>17-02-2026 19:32:54</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>17-05-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -5521,14 +5533,22 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26020522435540001049</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26020522444580001061</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5545,12 +5565,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344924</t>
+          <t>344585</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5560,17 +5580,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ASHLY VIVIANA</t>
+          <t>JESUS</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>RIOS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5580,28 +5600,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863062937</t>
+          <t>6862147023</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>24-09-2012</t>
+          <t>29-08-1994</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CECYECY1976@GMAIL.COM</t>
+          <t>JR21675@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>18-02-2026 18:11:34</t>
+          <t>17-02-2026 16:52:54</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5616,22 +5636,22 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:02</t>
+          <t>17-02-2026 16:54:41</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>17-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -5648,36 +5668,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26020522471760001096</t>
+          <t>26020522435540001049</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>346152</t>
+          <t>345712</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>88317</t>
+          <t>87877</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5687,17 +5707,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ANGEL FERNANDO</t>
+          <t xml:space="preserve">ROSALINA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARVIZU </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>PINEDA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5707,28 +5727,28 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6622041131</t>
+          <t>6861717262</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>30-03-2003</t>
+          <t>14-02-1973</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>A23311109@UTHERMOSI8LLO.EDU.MX</t>
+          <t>ROXYPYNEBVY@GAMIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>24-02-2026 13:50:53</t>
+          <t>23-02-2026 11:25:36</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5753,18 +5773,18 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>24-02-2026 13:53:01</t>
+          <t>25-02-2026 13:02:47</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5775,10 +5795,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26020522619580001267</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
+          <t>26020522652010001320</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5799,12 +5823,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>346607</t>
+          <t>344208</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>88772</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5814,17 +5838,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ABRAHAM EDUARDO</t>
+          <t>VICTOR ALEXIS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>URQUIDEZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AVILEZ</t>
+          <t>HARO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5834,12 +5858,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6866037590</t>
+          <t>6865624438</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>RUISEÑORES</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5849,17 +5873,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>31-07-1995</t>
+          <t>07-04-2010</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>EDUARDOAVLILEZ60@GMAIL.COM</t>
+          <t>5624438@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>25-02-2026 20:32:46</t>
+          <t>16-02-2026 17:19:52</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5884,17 +5908,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>25-02-2026 20:37:57</t>
+          <t>16-02-2026 17:23:38</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>25-02-2026 20:37:13</t>
+          <t>16-02-2026 17:22:53</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5904,7 +5928,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5914,7 +5938,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26020522667910001346</t>
+          <t>26020522399070000985</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5938,12 +5962,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>346608</t>
+          <t>344924</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>88773</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5953,17 +5977,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t>ASHLY VIVIANA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5973,33 +5997,33 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6861254848</t>
+          <t>6863062937</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>05-02-2007</t>
+          <t>24-09-2012</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>TONNNYYLUUCERO@GMAIL.COM</t>
+          <t>CECYECY1976@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>25-02-2026 20:43:27</t>
+          <t>18-02-2026 18:11:34</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6019,18 +6043,18 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>25-02-2026 20:50:30</t>
+          <t>18-02-2026 18:14:02</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -6041,7 +6065,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26020522668100001348</t>
+          <t>26020522471760001096</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6053,24 +6077,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>346759</t>
+          <t>346038</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>88924</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6080,17 +6104,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">ANGEL </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6100,7 +6124,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6861523562</t>
+          <t>6863831807</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6111,17 +6135,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>14-01-1982</t>
+          <t>21-11-2007</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>TORRESCHAVEZA63@GMAIL.COM</t>
+          <t>LEONFE520712@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>26-02-2026 16:52:41</t>
+          <t>23-02-2026 20:04:40</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6146,12 +6170,12 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>26-02-2026 16:54:55</t>
+          <t>23-02-2026 20:05:45</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -6168,7 +6192,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26020522688090001365</t>
+          <t>26020522601120001244</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6180,24 +6204,24 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>345712</t>
+          <t>345908</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>87877</t>
+          <t>88073</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6207,17 +6231,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSALINA </t>
+          <t>ABIGAIL MAYTE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PINEDA</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6227,10 +6251,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6861717262</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6861910334</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6238,56 +6266,64 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>14-02-1973</t>
+          <t>01-03-1985</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ROXYPYNEBVY@GAMIL.COM</t>
+          <t>VJACILVLADIMIR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>23-02-2026 11:25:36</t>
+          <t>23-02-2026 17:10:10</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>25-02-2026 13:02:47</t>
+          <t>27-02-2026 20:02:47</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>27-02-2026 20:01:53</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6295,7 +6331,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26020522652010001320</t>
+          <t>26020522725440001413</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -6303,32 +6339,36 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>346038</t>
+          <t>345913</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>88203</t>
+          <t>88078</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6338,17 +6378,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL </t>
+          <t>JACIL VLADIMIR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6358,10 +6398,14 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6863831807</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>5520670041</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6369,56 +6413,64 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21-11-2007</t>
+          <t>26-03-2002</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>LEONFE520712@GMAIL.COM</t>
+          <t>UWUSOUL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>23-02-2026 20:04:40</t>
+          <t>23-02-2026 17:14:41</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>23-02-2026 20:05:45</t>
+          <t>27-02-2026 20:05:58</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>27-02-2026 20:05:19</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6426,24 +6478,687 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26020522601120001244</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr"/>
+          <t>26020522725530001414</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>346607</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>88772</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ABRAHAM EDUARDO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>URQUIDEZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>AVILEZ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6866037590</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>31-07-1995</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>EDUARDOAVLILEZ60@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:32:46</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:37:57</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:37:13</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26020522667910001346</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>346608</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>88773</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JESUS ANTONIO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LUCERO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6861254848</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>05-02-2007</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>TONNNYYLUUCERO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:43:27</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:50:30</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26020522668100001348</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>346890</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>89055</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PERLA </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CORTEZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SALGADO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6863933395</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>AV ARAFO732</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>01-06-2002</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>PERLACOS123@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>27-02-2026 09:45:36</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>27-02-2026 09:54:12</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>27-02-2026 09:53:44</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26020522708020001388</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>346152</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>88317</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ANGEL FERNANDO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARVIZU </t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6622041131</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>30-03-2003</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>A23311109@UTHERMOSI8LLO.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>24-02-2026 13:50:53</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>24-02-2026 13:53:01</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26020522619580001267</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>346759</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>88924</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6861523562</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>14-01-1982</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>TORRESCHAVEZA63@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>26-02-2026 16:52:41</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>Arturo Israel  Flores Oronia</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>con rutina</t>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>26-02-2026 16:54:55</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26020522688090001365</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -2496,12 +2496,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341769</t>
+          <t>340209</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19587</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2511,17 +2511,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENA </t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>URIAS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2531,75 +2531,67 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6862828171</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>AV CASCADA SAN ANDRES 4039</t>
-        </is>
-      </c>
+          <t>6864221370</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31-08-2007</t>
+          <t>13-08-2003</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
+          <t>RICHI.CAMACHO20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>07-02-2026 09:15:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>02-02-2026 15:23:20</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>07-02-2026 09:21:40</t>
+          <t>04-02-2026 15:47:22</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>07-02-2026 09:20:44</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2607,19 +2599,27 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26020522157150000681</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26020522078020001242</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2631,12 +2631,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340209</t>
+          <t>341769</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>19587</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t xml:space="preserve">JIMENA </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>URIAS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2666,67 +2666,75 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6864221370</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6862828171</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AV CASCADA SAN ANDRES 4039</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13-08-2003</t>
+          <t>31-08-2007</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>RICHI.CAMACHO20@GMAIL.COM</t>
+          <t>JIMENAMUNOSURIAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 15:23:20</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 09:15:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-02-2026 15:47:22</t>
+          <t>07-02-2026 09:21:40</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>07-02-2026 09:20:44</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2734,27 +2742,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26020522078020001242</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522157150000681</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3306,12 +3306,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342185</t>
+          <t>344382</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>JESUS MANUEL</t>
+          <t>JULIO CESAR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MOLINA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3341,10 +3341,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6861640070</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6861853385</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MONTE BLANCO</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3352,56 +3356,64 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18-05-1961</t>
+          <t>23-02-1985</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CHUCHUNEL61@GMAIL.COM</t>
+          <t>JULIOREYESS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 14:42:28</t>
+          <t>17-02-2026 06:30:32</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-02-2026 14:44:26</t>
+          <t>17-02-2026 06:36:06</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>17-02-2026 06:34:33</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3409,19 +3421,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26020522193750000724</t>
+          <t>26020522419620001023</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3433,12 +3445,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>344382</t>
+          <t>342185</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>20003</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3448,17 +3460,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JULIO CESAR</t>
+          <t>JESUS MANUEL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MOLINA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3468,14 +3480,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6861853385</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>MONTE BLANCO</t>
-        </is>
-      </c>
+          <t>6861640070</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3483,64 +3491,56 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23-02-1985</t>
+          <t>18-05-1961</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JULIOREYESS@GMAIL.COM</t>
+          <t>CHUCHUNEL61@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>17-02-2026 06:30:32</t>
+          <t>09-02-2026 14:42:28</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>17-02-2026 06:36:06</t>
+          <t>09-02-2026 14:44:26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>17-02-2026 06:34:33</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3548,19 +3548,19 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26020522419620001023</t>
+          <t>26020522193750000724</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4104,12 +4104,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>343129</t>
+          <t>342424</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4119,17 +4119,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEJANDRA </t>
+          <t>ARANTZA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4139,10 +4139,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6863095804</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>4151245575</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AVENIDA SAN PEDRO MEZQUITL</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4150,56 +4154,60 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>13-05-2006</t>
+          <t>15-07-1997</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ALEJANDRA13@GMAIL.COM</t>
+          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>11-02-2026 20:04:50</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:07:14</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>11-02-2026 20:09:00</t>
+          <t>09-02-2026 19:10:59</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>09-02-2026 19:10:20</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4207,19 +4215,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26020522277990000848</t>
+          <t>26020522209900000743</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4231,12 +4239,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342424</t>
+          <t>343129</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4246,17 +4254,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ARANTZA</t>
+          <t xml:space="preserve">ALEJANDRA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4266,14 +4274,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4151245575</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>AVENIDA SAN PEDRO MEZQUITL</t>
-        </is>
-      </c>
+          <t>6863095804</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4281,60 +4285,56 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>15-07-1997</t>
+          <t>13-05-2006</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>HERNANDEZ.CAMPOS.ARANTZA@GMAIL.COM</t>
+          <t>ALEJANDRA13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 19:07:14</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>11-02-2026 20:04:50</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:59</t>
+          <t>11-02-2026 20:09:00</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>09-02-2026 19:10:20</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4342,19 +4342,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26020522209900000743</t>
+          <t>26020522277990000848</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4636,12 +4636,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342472</t>
+          <t>343329</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOSE ALEJANDRO</t>
+          <t>KIMBERLY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4671,10 +4671,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861434493</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6865255663</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4682,56 +4686,60 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>10-04-1980</t>
+          <t>22-12-1995</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
+          <t>KIMBERLYCKIMO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 20:01:55</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:11:31</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 20:06:47</t>
+          <t>12-02-2026 17:19:12</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>12-02-2026 17:18:19</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4739,14 +4747,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26020522212980000757</t>
+          <t>26020522299590000883</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4763,12 +4771,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343047</t>
+          <t>342472</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4778,17 +4786,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MARIA ANTONIA</t>
+          <t>JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4798,14 +4806,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6866017324</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>RIO CAOCA 3556</t>
-        </is>
-      </c>
+          <t>6861434493</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4813,60 +4817,56 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>22-09-1969</t>
+          <t>10-04-1980</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MAALIN_22@HOTMAIL.COM</t>
+          <t>ALEJANDROROBLESJART@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>11-02-2026 16:49:30</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>09-02-2026 20:01:55</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>14-02-2026 08:55:57</t>
+          <t>09-02-2026 20:06:47</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>14-02-2026 08:55:02</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4874,27 +4874,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26020522344200000936</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>MAGALI  ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020522212980000757</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4906,12 +4898,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343329</t>
+          <t>343047</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4921,17 +4913,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KIMBERLY</t>
+          <t>MARIA ANTONIA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4941,12 +4933,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6865255663</t>
+          <t>6866017324</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>RIO CAOCA 3556</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4956,17 +4948,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>22-12-1995</t>
+          <t>22-09-1969</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>KIMBERLYCKIMO@GMAIL.COM</t>
+          <t>MAALIN_22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>12-02-2026 17:11:31</t>
+          <t>11-02-2026 16:49:30</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4987,17 +4979,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>12-02-2026 17:19:12</t>
+          <t>14-02-2026 08:55:57</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>12-02-2026 17:18:19</t>
+          <t>14-02-2026 08:55:02</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5007,7 +4999,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -5017,11 +5009,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26020522299590000883</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26020522344200000936</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>MAGALI  ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>499</t>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5041,12 +5041,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343209</t>
+          <t>343618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>RICARDO</t>
+          <t>IAAN OCTAVIO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>REYNOSA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>CARRILLO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5076,24 +5076,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6862308375</t>
+          <t>6862251224</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>31-01-2009</t>
+          <t>03-01-2009</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>EDWSUCOR@GMAIL.COM</t>
+          <t>CARRILLOIAAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>12-02-2026 10:56:58</t>
+          <t>13-02-2026 21:07:16</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5118,12 +5122,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>16-02-2026 13:53:04</t>
+          <t>13-02-2026 21:10:08</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -5140,14 +5144,10 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26020522389340000968</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26020522331740000929</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
@@ -5168,12 +5168,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343618</t>
+          <t>343209</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5183,17 +5183,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IAAN OCTAVIO</t>
+          <t>RICARDO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CARRILLO</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5203,28 +5203,24 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6862251224</t>
+          <t>6862308375</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>03-01-2009</t>
+          <t>31-01-2009</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CARRILLOIAAN@GMAIL.COM</t>
+          <t>EDWSUCOR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>13-02-2026 21:07:16</t>
+          <t>12-02-2026 10:56:58</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5249,12 +5245,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>13-02-2026 21:10:08</t>
+          <t>16-02-2026 13:53:04</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -5271,10 +5267,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26020522331740000929</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
+          <t>26020522389340000968</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5692,12 +5692,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>345712</t>
+          <t>344924</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>87877</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSALINA </t>
+          <t>ASHLY VIVIANA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PINEDA</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6861717262</t>
+          <t>6863062937</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5738,22 +5738,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>14-02-1973</t>
+          <t>24-09-2012</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ROXYPYNEBVY@GAMIL.COM</t>
+          <t>CECYECY1976@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>23-02-2026 11:25:36</t>
+          <t>18-02-2026 18:11:34</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -5773,18 +5773,18 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>25-02-2026 13:02:47</t>
+          <t>18-02-2026 18:14:02</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5795,14 +5795,10 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26020522652010001320</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020522471760001096</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5811,12 +5807,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5958,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344924</t>
+          <t>345712</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>87877</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5977,17 +5973,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ASHLY VIVIANA</t>
+          <t xml:space="preserve">ROSALINA </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>PINEDA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5997,7 +5993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6863062937</t>
+          <t>6861717262</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6008,22 +6004,22 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>24-09-2012</t>
+          <t>14-02-1973</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CECYECY1976@GMAIL.COM</t>
+          <t>ROXYPYNEBVY@GAMIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18-02-2026 18:11:34</t>
+          <t>23-02-2026 11:25:36</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -6043,18 +6039,18 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>18-02-2026 18:14:02</t>
+          <t>25-02-2026 13:02:47</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -6065,10 +6061,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26020522471760001096</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
+          <t>26020522652010001320</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
@@ -6077,24 +6077,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>346038</t>
+          <t>346607</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>88203</t>
+          <t>88772</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6104,17 +6104,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL </t>
+          <t>ABRAHAM EDUARDO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>URQUIDEZ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>AVILEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6124,10 +6124,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6863831807</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6866037590</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6135,56 +6139,64 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>21-11-2007</t>
+          <t>31-07-1995</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>LEONFE520712@GMAIL.COM</t>
+          <t>EDUARDOAVLILEZ60@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>23-02-2026 20:04:40</t>
+          <t>25-02-2026 20:32:46</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>23-02-2026 20:05:45</t>
+          <t>25-02-2026 20:37:57</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:37:13</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6192,36 +6204,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26020522601120001244</t>
+          <t>26020522667910001346</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>345908</t>
+          <t>346608</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>88773</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6231,17 +6243,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ABIGAIL MAYTE</t>
+          <t>JESUS ANTONIO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>LUCERO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6251,79 +6263,67 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6861910334</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6861254848</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01-03-1985</t>
+          <t>05-02-2007</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>VJACILVLADIMIR@GMAIL.COM</t>
+          <t>TONNNYYLUUCERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>23-02-2026 17:10:10</t>
+          <t>25-02-2026 20:43:27</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>27-02-2026 20:02:47</t>
+          <t>25-02-2026 20:50:30</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>27-02-2026 20:01:53</t>
-        </is>
-      </c>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6331,44 +6331,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26020522725440001413</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522668100001348</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>345913</t>
+          <t>346038</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>88078</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6378,17 +6370,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JACIL VLADIMIR</t>
+          <t xml:space="preserve">ANGEL </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6398,14 +6390,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5520670041</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6863831807</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6413,64 +6401,56 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>26-03-2002</t>
+          <t>21-11-2007</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>UWUSOUL@GMAIL.COM</t>
+          <t>LEONFE520712@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>23-02-2026 17:14:41</t>
+          <t>23-02-2026 20:04:40</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>27-02-2026 20:05:58</t>
+          <t>23-02-2026 20:05:45</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>27-02-2026 20:05:19</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6478,23 +6458,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26020522725530001414</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020522601120001244</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6506,12 +6482,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>346607</t>
+          <t>345908</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>88772</t>
+          <t>88073</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6521,17 +6497,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ABRAHAM EDUARDO</t>
+          <t>ABIGAIL MAYTE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>URQUIDEZ</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AVILEZ</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6541,7 +6517,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6866037590</t>
+          <t>6861910334</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6551,22 +6527,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>31-07-1995</t>
+          <t>01-03-1985</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>EDUARDOAVLILEZ60@GMAIL.COM</t>
+          <t>VJACILVLADIMIR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>25-02-2026 20:32:46</t>
+          <t>23-02-2026 17:10:10</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6591,17 +6567,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>25-02-2026 20:37:57</t>
+          <t>27-02-2026 20:02:47</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>25-02-2026 20:37:13</t>
+          <t>27-02-2026 20:01:53</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6621,11 +6597,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26020522667910001346</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26020522725440001413</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>499</t>
@@ -6633,24 +6617,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>346608</t>
+          <t>345913</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>88773</t>
+          <t>88078</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6660,17 +6644,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JESUS ANTONIO</t>
+          <t>JACIL VLADIMIR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6680,10 +6664,14 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6861254848</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>5520670041</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6691,56 +6679,64 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>05-02-2007</t>
+          <t>26-03-2002</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>TONNNYYLUUCERO@GMAIL.COM</t>
+          <t>UWUSOUL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>25-02-2026 20:43:27</t>
+          <t>23-02-2026 17:14:41</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>25-02-2026 20:50:30</t>
+          <t>27-02-2026 20:05:58</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>27-02-2026 20:05:19</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6748,36 +6744,40 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26020522668100001348</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
+          <t>26020522725530001414</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>346890</t>
+          <t>346152</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>88317</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6787,17 +6787,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERLA </t>
+          <t>ANGEL FERNANDO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t xml:space="preserve">ARVIZU </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6807,79 +6807,67 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6863933395</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>AV ARAFO732</t>
-        </is>
-      </c>
+          <t>6622041131</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>01-06-2002</t>
+          <t>30-03-2003</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>PERLACOS123@GMAIL.COM</t>
+          <t>A23311109@UTHERMOSI8LLO.EDU.MX</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>27-02-2026 09:45:36</t>
+          <t>24-02-2026 13:50:53</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>27-02-2026 09:54:12</t>
+          <t>24-02-2026 13:53:01</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>27-02-2026 09:53:44</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6887,14 +6875,14 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26020522708020001388</t>
+          <t>26020522619580001267</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6911,12 +6899,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>346152</t>
+          <t>346890</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>88317</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6926,17 +6914,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ANGEL FERNANDO</t>
+          <t xml:space="preserve">PERLA </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARVIZU </t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6946,67 +6934,79 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6622041131</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6863933395</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>AV ARAFO732</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30-03-2003</t>
+          <t>01-06-2002</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>A23311109@UTHERMOSI8LLO.EDU.MX</t>
+          <t>PERLACOS123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>24-02-2026 13:50:53</t>
+          <t>27-02-2026 09:45:36</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>24-02-2026 13:53:01</t>
+          <t>27-02-2026 09:54:12</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>27-02-2026 09:53:44</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26020522619580001267</t>
+          <t>26020522708020001388</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,6 +709,669 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>230237</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>27742</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KARLA YARETZI</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>YAHUACA</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ARROYO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6863939274</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>28-11-2007</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>YARETZIYAHUACA212@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>17-04-2024 18:45:26</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>03-03-2026 13:30:43</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>26030522839980002779</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>346598</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>88763</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ENRIQUE ISRAEL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MOTA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DE HOYOS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6864042804</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>21-07-1979</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>25-02-2026 19:49:07</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:07:18</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>26020522860410001589</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>347972</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>90137</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANYELI </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ALVARAN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TABARES</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6867931588</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>25-10-1986</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ANYELIALVARAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:46:32</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:50:07</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>26020522833920001533</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>347997</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90162</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NOEMI</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VERASTEGUI</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6861199558</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV DEL CARRIZO </t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>13-09-1962</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MIMI_FLORESV@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:09:42</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:19:45</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:19:01</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>26020522836240001536</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>347980</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>90145</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LAURA </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6865499684</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CASA DEL LAGO 379</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>03-10-2003</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:59:25</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:07:48</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:07:02</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>26020522834400001534</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347508</t>
+          <t>230237</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89673</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>KARLA YARETZI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>YAHUACA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,47 +613,43 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6861060685</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AV RIO CHAMPOTON</t>
-        </is>
-      </c>
+          <t>6863939274</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>29-09-1958</t>
+          <t>28-11-2007</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SADUCA987@GMAILC.COM</t>
+          <t>YARETZIYAHUACA212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 11:27:00</t>
+          <t>17-04-2024 18:45:26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,29 +659,21 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 11:31:38</t>
+          <t>03-03-2026 13:30:43</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 11:30:55</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,7 +681,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26020522789300001457</t>
+          <t>26030522839980002779</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -705,7 +693,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -717,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>230237</t>
+          <t>346598</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KARLA YARETZI</t>
+          <t>ENRIQUE ISRAEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YAHUACA</t>
+          <t>MOTA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>DE HOYOS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,33 +740,33 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6863939274</t>
+          <t>6864042804</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28-11-2007</t>
+          <t>21-07-1979</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>YARETZIYAHUACA212@GMAIL.COM</t>
+          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>17-04-2024 18:45:26</t>
+          <t>25-02-2026 19:49:07</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -788,17 +776,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 13:30:43</t>
+          <t>03-03-2026 20:07:18</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -809,7 +797,7 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -820,36 +808,40 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26030522839980002779</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26020522860410001589</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346598</t>
+          <t>346036</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +851,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ENRIQUE ISRAEL</t>
+          <t>SANDRA PAOLA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MOTA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DE HOYOS</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,67 +871,79 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6864042804</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6865244707</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21-07-1979</t>
+          <t>08-08-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
+          <t>SANDRAPAOLASILVA08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25-02-2026 19:49:07</t>
+          <t>23-02-2026 20:00:53</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:18</t>
+          <t>05-03-2026 20:37:15</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:36:33</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -947,7 +951,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26020522860410001589</t>
+          <t>26020522931600001695</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -955,10 +959,14 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -975,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347972</t>
+          <t>347814</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90137</t>
+          <t>89979</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANYELI </t>
+          <t>LYDIA MARGARITA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ALVARAN</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TABARES</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,10 +1018,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6867931588</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6862028587</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1021,56 +1033,64 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-10-1986</t>
+          <t>05-08-2000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ANYELIALVARAN@GMAIL.COM</t>
+          <t>LYDIAMAGUILAR05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-03-2026 08:46:32</t>
+          <t>02-03-2026 18:23:16</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 08:50:07</t>
+          <t>05-03-2026 18:33:12</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:32:34</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1078,36 +1098,40 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020522833920001533</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26020522927530001685</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347997</t>
+          <t>347508</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90162</t>
+          <t>89673</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NOEMI</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VERASTEGUI</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1137,32 +1161,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6861199558</t>
+          <t>6861060685</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV DEL CARRIZO </t>
+          <t>AV RIO CHAMPOTON</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>13-09-1962</t>
+          <t>29-09-1958</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MIMI_FLORESV@HOTMAIL.COM</t>
+          <t>SADUCA987@GMAILC.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 10:09:42</t>
+          <t>02-03-2026 11:27:00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1187,17 +1211,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 10:19:45</t>
+          <t>02-03-2026 11:31:38</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 10:19:01</t>
+          <t>02-03-2026 11:30:55</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1207,7 +1231,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1217,7 +1241,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26020522836240001536</t>
+          <t>26020522789300001457</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1229,24 +1253,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347980</t>
+          <t>347805</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90145</t>
+          <t>89970</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1256,17 +1280,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1276,12 +1300,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6865499684</t>
+          <t>6861960430</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CASA DEL LAGO 379</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,17 +1315,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-10-2003</t>
+          <t>24-07-1997</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
+          <t>ANGELINAMARGARITAT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-03-2026 08:59:25</t>
+          <t>02-03-2026 18:18:19</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1311,12 +1335,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1326,17 +1350,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 09:07:48</t>
+          <t>05-03-2026 18:26:25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-03-2026 09:07:02</t>
+          <t>05-03-2026 18:25:28</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1346,7 +1370,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1356,10 +1380,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26020522834400001534</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26020522927170001684</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1368,10 +1396,848 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>334197</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18064</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EDUARDO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ROSALES</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5639259166</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>28-12-1994</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>EDUARDO.HERNANDEZ54@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>12-01-2026 22:11:53</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:22:35</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:22:06</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26020522897300001639</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>347997</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90162</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NOEMI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VERASTEGUI</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6861199558</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV DEL CARRIZO </t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>13-09-1962</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MIMI_FLORESV@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:09:42</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:19:45</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:19:01</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26020522836240001536</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347980</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90145</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LAURA </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6865499684</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CASA DEL LAGO 379</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>03-10-2003</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:59:25</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:07:48</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:07:02</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26020522834400001534</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>347901</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90066</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4251279557</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>24-12-2003</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>MMIT7584@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:32</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:49:09</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:48:32</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26020522898370001644</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347864</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90029</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KARYME ITALLETZY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SALINAS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>7331429496</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>15-12-1994</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>KARYME.ITA22@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:15:45</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:47:58</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:46:52</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26020522895730001631</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>347972</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90137</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANYELI </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ALVARAN</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TABARES</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6867931588</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>25-10-1986</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ANYELIALVARAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:46:32</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:50:07</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26020522833920001533</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>230237</t>
+          <t>334197</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KARLA YARETZI</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>YAHUACA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,53 +613,57 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6863939274</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>5639259166</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>28-11-2007</t>
+          <t>28-12-1994</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>YARETZIYAHUACA212@GMAIL.COM</t>
+          <t>EDUARDO.HERNANDEZ54@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>17-04-2024 18:45:26</t>
+          <t>12-01-2026 22:11:53</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 13:30:43</t>
+          <t>04-03-2026 19:22:35</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -667,13 +671,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:22:06</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,36 +693,44 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26030522839980002779</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26020522897300001639</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346598</t>
+          <t>230237</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ENRIQUE ISRAEL</t>
+          <t>KARLA YARETZI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MOTA</t>
+          <t>YAHUACA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DE HOYOS</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,33 +760,33 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6864042804</t>
+          <t>6863939274</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21-07-1979</t>
+          <t>28-11-2007</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
+          <t>YARETZIYAHUACA212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25-02-2026 19:49:07</t>
+          <t>17-04-2024 18:45:26</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -776,28 +796,28 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:18</t>
+          <t>03-03-2026 13:30:43</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -808,40 +828,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26020522860410001589</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26030522839980002779</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346036</t>
+          <t>347508</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88201</t>
+          <t>89673</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -851,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SANDRA PAOLA</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -871,32 +887,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6865244707</t>
+          <t>6861060685</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>AV RIO CHAMPOTON</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>08-08-2005</t>
+          <t>29-09-1958</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SANDRAPAOLASILVA08@GMAIL.COM</t>
+          <t>SADUCA987@GMAILC.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23-02-2026 20:00:53</t>
+          <t>02-03-2026 11:27:00</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -921,17 +937,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>05-03-2026 20:37:15</t>
+          <t>02-03-2026 11:31:38</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>05-03-2026 20:36:33</t>
+          <t>02-03-2026 11:30:55</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -951,19 +967,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26020522931600001695</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020522789300001457</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -971,24 +979,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347814</t>
+          <t>346598</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89979</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LYDIA MARGARITA</t>
+          <t>ENRIQUE ISRAEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>MOTA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>DE HOYOS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,79 +1026,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6862028587</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6864042804</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>05-08-2000</t>
+          <t>21-07-1979</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>LYDIAMAGUILAR05@GMAIL.COM</t>
+          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:16</t>
+          <t>25-02-2026 19:49:07</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>05-03-2026 18:33:12</t>
+          <t>03-03-2026 20:07:18</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>05-03-2026 18:32:34</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1098,7 +1094,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020522927530001685</t>
+          <t>26020522860410001589</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1109,7 +1105,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1126,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347508</t>
+          <t>346036</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89673</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>SANDRA PAOLA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,32 +1157,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6861060685</t>
+          <t>6865244707</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AV RIO CHAMPOTON</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>29-09-1958</t>
+          <t>08-08-2005</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SADUCA987@GMAILC.COM</t>
+          <t>SANDRAPAOLASILVA08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 11:27:00</t>
+          <t>23-02-2026 20:00:53</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1211,17 +1207,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 11:31:38</t>
+          <t>05-03-2026 20:37:15</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 11:30:55</t>
+          <t>05-03-2026 20:36:33</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1241,11 +1237,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26020522789300001457</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26020522931600001695</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1253,24 +1257,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347805</t>
+          <t>347901</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89970</t>
+          <t>90066</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1280,17 +1284,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>MANUEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1300,7 +1304,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6861960430</t>
+          <t>4251279557</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1310,22 +1314,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24-07-1997</t>
+          <t>24-12-2003</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ANGELINAMARGARITAT@GMAIL.COM</t>
+          <t>MMIT7584@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 18:18:19</t>
+          <t>02-03-2026 20:30:32</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1340,27 +1344,27 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-03-2026 18:26:25</t>
+          <t>04-03-2026 19:49:09</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>05-03-2026 18:25:28</t>
+          <t>04-03-2026 19:48:32</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1370,7 +1374,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1380,7 +1384,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26020522927170001684</t>
+          <t>26020522898370001644</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1391,29 +1395,29 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>334197</t>
+          <t>347805</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>89970</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1423,17 +1427,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1443,7 +1447,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5639259166</t>
+          <t>6861960430</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1453,22 +1457,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-12-1994</t>
+          <t>24-07-1997</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>EDUARDO.HERNANDEZ54@UABC.EDU.MX</t>
+          <t>ANGELINAMARGARITAT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>12-01-2026 22:11:53</t>
+          <t>02-03-2026 18:18:19</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1483,17 +1487,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-03-2026 19:22:35</t>
+          <t>05-03-2026 18:26:25</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1503,7 +1507,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>04-03-2026 19:22:06</t>
+          <t>05-03-2026 18:25:28</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1513,7 +1517,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1523,7 +1527,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26020522897300001639</t>
+          <t>26020522927170001684</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1531,14 +1535,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1555,12 +1555,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347997</t>
+          <t>347864</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90162</t>
+          <t>90029</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NOEMI</t>
+          <t>KARYME ITALLETZY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VERASTEGUI</t>
+          <t>SALINAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6861199558</t>
+          <t>7331429496</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV DEL CARRIZO </t>
+          <t>N</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13-09-1962</t>
+          <t>15-12-1994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MIMI_FLORESV@HOTMAIL.COM</t>
+          <t>KARYME.ITA22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 10:09:42</t>
+          <t>02-03-2026 19:15:45</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 10:19:45</t>
+          <t>04-03-2026 18:47:58</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>03-03-2026 10:19:01</t>
+          <t>04-03-2026 18:46:52</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1670,10 +1670,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26020522836240001536</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26020522895730001631</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1694,12 +1698,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347980</t>
+          <t>347972</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90145</t>
+          <t>90137</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1709,17 +1713,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t xml:space="preserve">ANYELI </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>ALVARAN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>TABARES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1729,14 +1733,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6865499684</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CASA DEL LAGO 379</t>
-        </is>
-      </c>
+          <t>6867931588</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>03-10-2003</t>
+          <t>25-10-1986</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
+          <t>ANYELIALVARAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 08:59:25</t>
+          <t>03-03-2026 08:46:32</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1764,44 +1764,36 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 09:07:48</t>
+          <t>03-03-2026 08:50:07</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>03-03-2026 09:07:02</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1809,14 +1801,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26020522834400001534</t>
+          <t>26020522833920001533</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1833,12 +1825,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347901</t>
+          <t>347814</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90066</t>
+          <t>89979</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1848,17 +1840,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MANUEL</t>
+          <t>LYDIA MARGARITA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1868,7 +1860,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4251279557</t>
+          <t>6862028587</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1878,47 +1870,47 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-12-2003</t>
+          <t>05-08-2000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MMIT7584@GMAIL.COM</t>
+          <t>LYDIAMAGUILAR05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 20:30:32</t>
+          <t>02-03-2026 18:23:16</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-03-2026 19:49:09</t>
+          <t>05-03-2026 18:33:12</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1928,7 +1920,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>04-03-2026 19:48:32</t>
+          <t>05-03-2026 18:32:34</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1948,7 +1940,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26020522898370001644</t>
+          <t>26020522927530001685</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1959,29 +1951,29 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347864</t>
+          <t>347997</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90029</t>
+          <t>90162</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1991,17 +1983,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KARYME ITALLETZY</t>
+          <t>NOEMI</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>VERASTEGUI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2011,12 +2003,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7331429496</t>
+          <t>6861199558</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t xml:space="preserve">AV DEL CARRIZO </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2026,17 +2018,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15-12-1994</t>
+          <t>13-09-1962</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>KARYME.ITA22@GMAIL.COM</t>
+          <t>MIMI_FLORESV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 19:15:45</t>
+          <t>03-03-2026 10:09:42</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2061,17 +2053,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 18:47:58</t>
+          <t>03-03-2026 10:19:45</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>04-03-2026 18:46:52</t>
+          <t>03-03-2026 10:19:01</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2081,7 +2073,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2091,14 +2083,10 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522895730001631</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020522836240001536</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2119,12 +2107,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347972</t>
+          <t>347854</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90137</t>
+          <t>90019</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2134,17 +2122,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANYELI </t>
+          <t>CARLOS GABRIEL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ALVARAN</t>
+          <t>BONILLA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TABARES</t>
+          <t>MELENDREZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2154,33 +2142,33 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6867931588</t>
+          <t>6863672365</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25-10-1986</t>
+          <t>13-09-2010</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ANYELIALVARAN@GMAIL.COM</t>
+          <t>CARLOSBONILLA20000@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 08:46:32</t>
+          <t>02-03-2026 18:56:13</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2190,28 +2178,28 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 08:50:07</t>
+          <t>06-03-2026 20:13:10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -2222,22 +2210,431 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26020522833920001533</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26020522961430001733</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>347980</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90145</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LAURA </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6865499684</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CASA DEL LAGO 379</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>03-10-2003</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:59:25</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:07:48</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:07:02</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26020522834400001534</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348576</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90741</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LUIS GERARDO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MONTIJO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VILLA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6863987172</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>09-04-2008</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NOTIENEEEEEEEEEEEEEE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:49:53</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:02:58</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26020522959710001726</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348375</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90540</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DAYANA ESCARLET</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CUEN</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MIRAMONTES</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6531015715</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>28-11-2000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>DAYANACUEN00@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:09:26</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>06-03-2026 10:39:39</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26020522946540001709</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>334197</t>
+          <t>261991</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>59495</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t xml:space="preserve">ADRIAN </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">MONDACA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5639259166</t>
+          <t>6861343419</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t xml:space="preserve">RIO ZITACUARO </t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>28-12-1994</t>
+          <t>30-12-1983</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>EDUARDO.HERNANDEZ54@UABC.EDU.MX</t>
+          <t>ADRIANRBC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>12-01-2026 22:11:53</t>
+          <t>14-10-2024 18:12:07</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -653,27 +653,27 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>04-03-2026 19:22:35</t>
+          <t>10-03-2026 05:35:49</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>04-03-2026 19:22:06</t>
+          <t>10-03-2026 05:30:24</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,32 +693,24 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26020522897300001639</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26020523035950001830</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -852,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347508</t>
+          <t>295586</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89673</t>
+          <t>93084</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>ADRIANA LIZBETH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>PADILLA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,12 +879,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6861060685</t>
+          <t>6862670839</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AV RIO CHAMPOTON</t>
+          <t>RIO GARONA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -902,17 +894,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>29-09-1958</t>
+          <t>27-09-1999</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SADUCA987@GMAILC.COM</t>
+          <t>LIZBETH1117@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:27:00</t>
+          <t>30-05-2025 17:04:32</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -937,17 +929,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:31:38</t>
+          <t>19-03-2026 12:18:48</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>18-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:30:55</t>
+          <t>19-03-2026 12:17:49</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -967,7 +959,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26020522789300001457</t>
+          <t>26020523326600002232</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -979,24 +971,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346598</t>
+          <t>65492</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>63327</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ENRIQUE ISRAEL</t>
+          <t>JOAQUIN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MOTA</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DE HOYOS</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,10 +1018,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6864042804</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6861161597</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AV RIO NEVADA 3532</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1037,56 +1033,64 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>21-07-1979</t>
+          <t>01-02-1999</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
+          <t>JOAQUIN.SALAZAR@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>25-02-2026 19:49:07</t>
+          <t>10-01-2022 16:33:07</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:18</t>
+          <t>09-03-2026 22:45:05</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>09-03-2026 22:44:18</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,40 +1098,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020522860410001589</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020523034370001827</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>346036</t>
+          <t>231562</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88201</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SANDRA PAOLA</t>
+          <t>ANA CAMILA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">BEJARANO </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>CORIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6865244707</t>
+          <t>6863511928</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>GN</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>08-08-2005</t>
+          <t>23-01-2002</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SANDRAPAOLASILVA08@GMAIL.COM</t>
+          <t>ANACAMILABEJARONCORIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>23-02-2026 20:00:53</t>
+          <t>27-04-2024 09:38:18</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>05-03-2026 20:37:15</t>
+          <t>14-03-2026 13:54:39</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>13-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>05-03-2026 20:36:33</t>
+          <t>14-03-2026 13:54:04</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1237,19 +1237,11 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26020522931600001695</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26010523184790006624</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1269,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347901</t>
+          <t>276336</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90066</t>
+          <t>73837</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1284,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MANUEL</t>
+          <t>LUIS ARMANDO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1304,12 +1296,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4251279557</t>
+          <t>6644920547</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1319,17 +1311,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24-12-2003</t>
+          <t>29-06-1996</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MMIT7584@GMAIL.COM</t>
+          <t>LUIS.DIAZHERRERA@GNP.COM.MX</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 20:30:32</t>
+          <t>28-01-2025 19:51:50</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1354,17 +1346,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>04-03-2026 19:49:09</t>
+          <t>17-03-2026 19:34:46</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>04-03-2026 19:48:32</t>
+          <t>17-03-2026 19:33:31</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1374,7 +1366,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1384,14 +1376,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26020522898370001644</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26030523270510003524</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1400,24 +1388,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347805</t>
+          <t>334197</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89970</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1427,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1447,7 +1435,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6861960430</t>
+          <t>5639259166</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1457,22 +1445,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24-07-1997</t>
+          <t>28-12-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ANGELINAMARGARITAT@GMAIL.COM</t>
+          <t>EDUARDO.HERNANDEZ54@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:18:19</t>
+          <t>12-01-2026 22:11:53</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1487,27 +1475,27 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>05-03-2026 18:26:25</t>
+          <t>04-03-2026 19:22:35</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>05-03-2026 18:25:28</t>
+          <t>04-03-2026 19:22:06</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1517,7 +1505,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1527,7 +1515,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26020522927170001684</t>
+          <t>26020522897300001639</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1535,32 +1523,36 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347864</t>
+          <t>311707</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90029</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1570,17 +1562,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KARYME ITALLETZY</t>
+          <t>JESUS ALONSO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1590,32 +1582,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7331429496</t>
+          <t>6866043202</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>EJIDO YUCATAN</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15-12-1994</t>
+          <t>10-01-1996</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>KARYME.ITA22@GMAIL.COM</t>
+          <t>ALBERTO.ROCHAAAA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:15:45</t>
+          <t>29-08-2025 14:24:08</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1640,17 +1632,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 18:47:58</t>
+          <t>16-03-2026 19:12:02</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>04-03-2026 18:46:52</t>
+          <t>16-03-2026 19:11:38</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1670,14 +1662,10 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26020522895730001631</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020523232390002075</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1698,12 +1686,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347972</t>
+          <t>313295</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90137</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1713,17 +1701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANYELI </t>
+          <t xml:space="preserve">FERNANDO OMAR </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ALVARAN</t>
+          <t xml:space="preserve"> TORREROS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TABARES</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1733,67 +1721,79 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6867931588</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6862809692</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>VILLA DEL BOSQUE</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25-10-1986</t>
+          <t>09-07-1987</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ANYELIALVARAN@GMAIL.COM</t>
+          <t>OMARTB87FB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 08:46:32</t>
+          <t>08-09-2025 16:24:06</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 08:50:07</t>
+          <t>10-03-2026 21:08:25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>10-03-2026 21:06:57</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1801,14 +1801,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26020522833920001533</t>
+          <t>26020523072640001893</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1825,12 +1825,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347814</t>
+          <t>324164</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89979</t>
+          <t>21103</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LYDIA MARGARITA</t>
+          <t xml:space="preserve">SANDRA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t xml:space="preserve">LUGO </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6862028587</t>
+          <t>6861322733</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>QUIROZ 1228</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>05-08-2000</t>
+          <t>04-10-1983</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LYDIAMAGUILAR05@GMAIL.COM</t>
+          <t>SAFRALU2020@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:16</t>
+          <t>18-11-2025 11:06:19</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1910,17 +1910,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-03-2026 18:33:12</t>
+          <t>10-03-2026 18:36:50</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>05-03-2026 18:32:34</t>
+          <t>10-03-2026 17:10:12</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26020522927530001685</t>
+          <t>26020523064850001873</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1948,7 +1948,11 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>MAGALI  ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1956,24 +1960,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347997</t>
+          <t>346598</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90162</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1983,17 +1987,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NOEMI</t>
+          <t>ENRIQUE ISRAEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>MOTA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VERASTEGUI</t>
+          <t>DE HOYOS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2003,57 +2007,53 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6861199558</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AV DEL CARRIZO </t>
-        </is>
-      </c>
+          <t>6864042804</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13-09-1962</t>
+          <t>21-07-1979</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MIMI_FLORESV@HOTMAIL.COM</t>
+          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 10:09:42</t>
+          <t>25-02-2026 19:49:07</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 10:19:45</t>
+          <t>03-03-2026 20:07:18</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2061,21 +2061,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>03-03-2026 10:19:01</t>
-        </is>
-      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2083,36 +2075,40 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522836240001536</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26020522860410001589</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347854</t>
+          <t>346036</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90019</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2122,17 +2118,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CARLOS GABRIEL</t>
+          <t>SANDRA PAOLA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BONILLA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MELENDREZ</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2142,43 +2138,47 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6863672365</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6865244707</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13-09-2010</t>
+          <t>08-08-2005</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CARLOSBONILLA20000@GMAIL.COM</t>
+          <t>SANDRAPAOLASILVA08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 18:56:13</t>
+          <t>23-02-2026 20:00:53</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2188,21 +2188,29 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>06-03-2026 20:13:10</t>
+          <t>05-03-2026 20:37:15</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:36:33</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2210,7 +2218,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26020522961430001733</t>
+          <t>26020522931600001695</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2218,7 +2226,11 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>549</t>
@@ -2226,24 +2238,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347980</t>
+          <t>347508</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90145</t>
+          <t>89673</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2253,17 +2265,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2273,37 +2285,37 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6865499684</t>
+          <t>6861060685</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CASA DEL LAGO 379</t>
+          <t>AV RIO CHAMPOTON</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>03-10-2003</t>
+          <t>29-09-1958</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
+          <t>SADUCA987@GMAILC.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 08:59:25</t>
+          <t>02-03-2026 11:27:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2313,27 +2325,27 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 09:07:48</t>
+          <t>02-03-2026 11:31:38</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-03-2026 09:07:02</t>
+          <t>02-03-2026 11:30:55</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2353,19 +2365,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26020522834400001534</t>
+          <t>26020522789300001457</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2377,12 +2389,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>347864</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90741</t>
+          <t>90029</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2392,17 +2404,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LUIS GERARDO</t>
+          <t>KARYME ITALLETZY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MONTIJO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>SALINAS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2412,43 +2424,47 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6863987172</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>7331429496</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>09-04-2008</t>
+          <t>15-12-1994</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NOTIENEEEEEEEEEEEEEE@GMAIL.COM</t>
+          <t>KARYME.ITA22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>04-03-2026 18:49:53</t>
+          <t>02-03-2026 19:15:45</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2458,21 +2474,29 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>06-03-2026 19:02:58</t>
+          <t>04-03-2026 18:47:58</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:46:52</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2480,7 +2504,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26020522959710001726</t>
+          <t>26020522895730001631</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2496,7 +2520,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2508,12 +2532,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348375</t>
+          <t>347972</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90540</t>
+          <t>90137</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2523,17 +2547,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DAYANA ESCARLET</t>
+          <t xml:space="preserve">ANYELI </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CUEN</t>
+          <t>ALVARAN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>TABARES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2543,7 +2567,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6531015715</t>
+          <t>6867931588</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2554,17 +2578,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>28-11-2000</t>
+          <t>25-10-1986</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>DAYANACUEN00@GMAIL.COM</t>
+          <t>ANYELIALVARAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>04-03-2026 10:09:26</t>
+          <t>03-03-2026 08:46:32</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2579,22 +2603,22 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>06-03-2026 10:39:39</t>
+          <t>03-03-2026 08:50:07</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2611,30 +2635,4104 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
+          <t>26020522833920001533</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>347814</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>89979</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LYDIA MARGARITA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MENDEZ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6862028587</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>05-08-2000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>LYDIAMAGUILAR05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:23:16</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:33:12</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:32:34</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26020522927530001685</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>347980</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90145</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIANA LAURA </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MONTOYA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6865499684</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CASA DEL LAGO 379</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>03-10-2003</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:59:25</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:07:48</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:07:02</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26020522834400001534</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>347805</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>89970</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CAROLINA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6861960430</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>24-07-1997</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ANGELINAMARGARITAT@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:18:19</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:26:25</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:25:28</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26020522927170001684</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>347854</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90019</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CARLOS GABRIEL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BONILLA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MELENDREZ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6863672365</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>13-09-2010</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CARLOSBONILLA20000@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:56:13</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>06-03-2026 20:13:10</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26020522961430001733</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>347901</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>90066</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MANUEL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4251279557</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>24-12-2003</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>MMIT7584@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:30:32</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:49:09</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>04-03-2026 19:48:32</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26020522898370001644</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>347997</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90162</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NOEMI</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VERASTEGUI</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6861199558</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV DEL CARRIZO </t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>13-09-1962</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MIMI_FLORESV@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:09:42</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:19:45</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:19:01</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26020522836240001536</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>348484</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>90649</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ANDREA FERNANDA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CERVANTES</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HURTADO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6864198624</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AV LIMOLITA 1412</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>18-11-1997</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ANDREA_CERVANTES97@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>04-03-2026 16:32:06</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:55:15</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:54:19</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26020523015500001786</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348375</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90540</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DAYANA ESCARLET</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CUEN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MIRAMONTES</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6531015715</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>28-11-2000</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>DAYANACUEN00@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:09:26</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>06-03-2026 10:39:39</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
           <t>26020522946540001709</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>Eliazar Flores Vargas</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348576</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90741</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LUIS GERARDO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MONTIJO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VILLA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6863987172</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>09-04-2008</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NOTIENEEEEEEEEEEEEEE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:49:53</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>06-03-2026 19:02:58</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26020522959710001726</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348830</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90995</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GUSTAVO ALFONSO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CARAVEO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6641626298</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>09-02-1980</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>TORRESCARAVEO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>06-03-2026 05:50:48</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>18-03-2026 05:04:47</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26030523276420003546</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Miguel Angel  Nava Correa</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>348765</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90930</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CRUZ AZUCENA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6866055064</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>RIO GAMBIA 3416</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>15-07-1976</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>SUSSYMORENO15@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:15:43</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:49:38</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:48:49</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26020523019290001791</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>349545</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>91710</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>JOSE MANUEL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ZUÑIGA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>FONSECA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6861636263</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>POBLADO CERRO PRIETO</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>27-10-1993</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>JOSE011668@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:24:04</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:29:36</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:28:39</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26020523017740001789</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>349702</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>91867</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAHI </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>JAIME</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VALLE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6863958644</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>DE LOS ROCIOS NORTE</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>24-11-2004</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ANAHIJAIME2004@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:05:22</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:10:35</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:09:47</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26020523030620001817</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>349866</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>92031</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ILEANA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PRECIADO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6862023698</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>10-08-2005</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PRECIADOILEANA631@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:02:44</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:04:04</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26020523054260001855</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>349884</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>92049</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DANIELA GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AHUMADA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6861888423</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>13-11-1985</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AHUMADARAMIREZDANIELA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>10-03-2026 16:14:56</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>10-03-2026 16:19:11</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26020523056700001862</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>349855</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>92020</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DANIA ISELA </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORALES </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6861907163</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>CASCADA DE LA BALSA 4356</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>30-09-1991</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DR084861@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:28:30</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:41:30</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:36:33</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26020523053430001852</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>350678</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>92842</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FRANCISCO JAVIER</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BALERA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MALDONADO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>7621155727</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>25-05-1989</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>BALERAARQ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:24:26</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:21:25</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26020523221350002047</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>350256</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>92420</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>SERGIO JASSIEL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>JOCOBI</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6863832310</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>23-11-1999</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>SERGIOJOCOBI23@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>12-03-2026 06:49:33</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>12-03-2026 06:50:56</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26020523115640001949</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>350539</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>92703</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VICTOR NOE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VELAZQUEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6863867166</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>06-02-2002</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>VELAZQUEZ.VICTOR.CETIS75@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:45:52</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:49:48</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26020523150210001996</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>349979</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>92144</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OMAR ULISES</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MONTES</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6681903519</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>17-05-1990</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ULISESACOSTA1790@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:10:24</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:41:50</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:41:18</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26020523132200001971</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>350918</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>93082</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SARAI</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CERDA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6863865765</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>25-09-1987</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>SACI0878@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>15-03-2026 13:20:40</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:20:45</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:19:16</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26010523228480006746</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Eduardo  Rivera Ramirez</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>351144</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>93308</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>KELLY DENISSE</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>JUAREZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ALFAN</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>5527997427</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>12-05-1987</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>VENUS.HS16@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>16-03-2026 12:26:10</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>16-03-2026 12:31:54</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>16-03-2026 12:31:15</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26020523219270002040</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>350676</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>92840</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BALERA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>MALDONADO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7778923229</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>12-12-1998</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>BALERAJOSE.27@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>13-03-2026 19:21:14</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:18:23</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26020523221210002046</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>351309</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>93473</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NANCY ALEXANDRA </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6863358342</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>PITAYA160</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>24-03-1994</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>ALEXAESQUIVEL2403@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:46:54</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17-03-2026 21:53:31</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>17-03-2026 21:52:37</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26020523276060002160</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>351996</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>94160</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AGUSTIN ELIEZER</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RUBIO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>BARRAGAN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6862591682</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>16-11-1989</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ELIEZZERUB@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:12:20</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:17:59</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:16:39</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26020523309280002213</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>351760</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>93924</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LUIS LEONARDO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DE LEON</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>VALDES</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6863164327</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>RIO MEZCALAPA 3677</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>24-09-2008</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>LEONARDO.24DELEON2008@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>18-03-2026 08:25:13</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>18-03-2026 08:32:57</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>18-03-2026 08:31:57</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26020523285970002167</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>350913</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>93077</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AARON </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CAÑEDO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>LAFARGA</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6863917755</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>DFTG</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>21-12-1987</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>AARONCANEDO2@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>15-03-2026 13:16:02</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:24:28</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:23:59</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26010523228600006747</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Eduardo  Rivera Ramirez</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>351979</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>94143</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GLISERIA </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6862822480</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>21-12-1971</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>GLISLUNA2171@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:50:11</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:56:30</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:54:34</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26020523308150002207</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>351396</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>93560</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ESAU</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>TORRES RETAMOZA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TORRES RETAMOZA</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6861644228</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>av chila 781</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>31-12-9999</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>ing.yaneth.nunez@gmail.com</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:50:25</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:50:26</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26020523236460002092</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>351757</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>93921</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>IRMA BEATRIZ</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6731001122</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>24-12-1970</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>RAGI171@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>18-03-2026 08:01:28</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>18-03-2026 08:03:40</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26020523285130002166</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLA VERDE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>261991</t>
+          <t>230237</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59495</t>
+          <t>27742</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIAN </t>
+          <t>KARLA YARETZI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONDACA </t>
+          <t>YAHUACA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,47 +613,43 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6861343419</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RIO ZITACUARO </t>
-        </is>
-      </c>
+          <t>6863939274</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30-12-1983</t>
+          <t>28-11-2007</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ADRIANRBC@GMAIL.COM</t>
+          <t>YARETZIYAHUACA212@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>14-10-2024 18:12:07</t>
+          <t>17-04-2024 18:45:26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,29 +659,21 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>10-03-2026 05:35:49</t>
+          <t>03-03-2026 13:30:43</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>10-03-2026 05:30:24</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,7 +681,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26020523035950001830</t>
+          <t>26030522839980002779</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -705,7 +693,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Karla Carolina Gonzalez Gonzalez</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -717,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>230237</t>
+          <t>261991</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>59495</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KARLA YARETZI</t>
+          <t xml:space="preserve">ADRIAN </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>YAHUACA</t>
+          <t xml:space="preserve">MONDACA </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,43 +740,47 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6863939274</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6861343419</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIO ZITACUARO </t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28-11-2007</t>
+          <t>30-12-1983</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>YARETZIYAHUACA212@GMAIL.COM</t>
+          <t>ADRIANRBC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>17-04-2024 18:45:26</t>
+          <t>14-10-2024 18:12:07</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -798,21 +790,29 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 13:30:43</t>
+          <t>10-03-2026 05:35:49</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>10-03-2026 05:30:24</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26030522839980002779</t>
+          <t>26020523035950001830</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Karla Carolina Gonzalez Gonzalez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -844,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>295586</t>
+          <t>262120</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>93084</t>
+          <t>59624</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ADRIANA LIZBETH</t>
+          <t>ALMA GISSEL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PADILLA</t>
+          <t>VALVERDE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>VARGAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6862670839</t>
+          <t>6863562554</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RIO GARONA</t>
+          <t>RIO HONDO 3437</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -894,17 +894,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-09-1999</t>
+          <t>24-11-2007</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>LIZBETH1117@HOTMAIL.COM</t>
+          <t>VALVERDEVARGASALMAGISSEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>30-05-2025 17:04:32</t>
+          <t>14-10-2024 22:53:24</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19-03-2026 12:18:48</t>
+          <t>23-03-2026 09:29:57</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
+          <t>22-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>19-03-2026 12:17:49</t>
+          <t>23-03-2026 09:29:13</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26020523326600002232</t>
+          <t>26020523420220002327</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -983,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>65492</t>
+          <t>295586</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>63327</t>
+          <t>93084</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JOAQUIN</t>
+          <t>ADRIANA LIZBETH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>PADILLA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6861161597</t>
+          <t>6862670839</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AV RIO NEVADA 3532</t>
+          <t>RIO GARONA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,17 +1033,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>01-02-1999</t>
+          <t>27-09-1999</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JOAQUIN.SALAZAR@UABC.EDU.MX</t>
+          <t>LIZBETH1117@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10-01-2022 16:33:07</t>
+          <t>30-05-2025 17:04:32</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1068,17 +1068,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>09-03-2026 22:45:05</t>
+          <t>19-03-2026 12:18:48</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>18-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>09-03-2026 22:44:18</t>
+          <t>19-03-2026 12:17:49</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26020523034370001827</t>
+          <t>26020523326600002232</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1110,24 +1110,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>231562</t>
+          <t>335815</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>25040</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ANA CAMILA</t>
+          <t xml:space="preserve">OMAR PAVEL </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEJARANO </t>
+          <t>CALVO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CORIA</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,47 +1157,43 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6863511928</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>GN</t>
-        </is>
-      </c>
+          <t>6863928600</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23-01-2002</t>
+          <t>14-03-1984</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ANACAMILABEJARONCORIA@GMAIL.COM</t>
+          <t>OPCALVO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>27-04-2024 09:38:18</t>
+          <t>19-01-2026 09:09:07</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1207,29 +1203,21 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>14-03-2026 13:54:39</t>
+          <t>23-03-2026 09:02:01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>13-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>14-03-2026 13:54:04</t>
-        </is>
-      </c>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1237,11 +1225,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26010523184790006624</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26020523419410002322</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>MAGALI  ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1249,24 +1245,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>276336</t>
+          <t>65492</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73837</t>
+          <t>63327</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1272,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LUIS ARMANDO</t>
+          <t>JOAQUIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,12 +1292,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6644920547</t>
+          <t>6861161597</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>AV RIO NEVADA 3532</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1311,52 +1307,52 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>29-06-1996</t>
+          <t>01-02-1999</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LUIS.DIAZHERRERA@GNP.COM.MX</t>
+          <t>JOAQUIN.SALAZAR@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>28-01-2025 19:51:50</t>
+          <t>10-01-2022 16:33:07</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>17-03-2026 19:34:46</t>
+          <t>09-03-2026 22:45:05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>17-03-2026 19:33:31</t>
+          <t>09-03-2026 22:44:18</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1376,36 +1372,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26030523270510003524</t>
+          <t>26020523034370001827</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>334197</t>
+          <t>231562</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t>ANA CAMILA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">BEJARANO </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>CORIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,67 +1431,67 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5639259166</t>
+          <t>6863511928</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>GN</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-12-1994</t>
+          <t>23-01-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>EDUARDO.HERNANDEZ54@UABC.EDU.MX</t>
+          <t>BEJARONCORIAANACAMILA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>12-01-2026 22:11:53</t>
+          <t>27-04-2024 09:38:18</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-03-2026 19:22:35</t>
+          <t>14-03-2026 13:54:39</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>13-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>04-03-2026 19:22:06</t>
+          <t>14-03-2026 13:54:04</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1505,7 +1501,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1515,44 +1511,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26020522897300001639</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26010523184790006624</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>311707</t>
+          <t>334197</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1562,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JESUS ALONSO</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1582,12 +1570,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6866043202</t>
+          <t>5639259166</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EJIDO YUCATAN</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1597,52 +1585,52 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10-01-1996</t>
+          <t>28-12-1994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ALBERTO.ROCHAAAA@GMAIL.COM</t>
+          <t>EDUARDO.HERNANDEZ54@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>29-08-2025 14:24:08</t>
+          <t>12-01-2026 22:11:53</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>16-03-2026 19:12:02</t>
+          <t>04-03-2026 19:22:35</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>16-03-2026 19:11:38</t>
+          <t>04-03-2026 19:22:06</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1662,36 +1650,44 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26020523232390002075</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26020522897300001639</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>313295</t>
+          <t>346036</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>88201</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1701,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDO OMAR </t>
+          <t>SANDRA PAOLA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> TORREROS</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1721,32 +1717,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6862809692</t>
+          <t>6865244707</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>VILLA DEL BOSQUE</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>09-07-1987</t>
+          <t>08-08-2005</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>OMARTB87FB@GMAIL.COM</t>
+          <t>SANDRAPAOLASILVA08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>08-09-2025 16:24:06</t>
+          <t>23-02-2026 20:00:53</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1771,17 +1767,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>10-03-2026 21:08:25</t>
+          <t>05-03-2026 20:37:15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>10-03-2026 21:06:57</t>
+          <t>05-03-2026 20:36:33</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1801,11 +1797,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26020523072640001893</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26020522931600001695</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>549</t>
@@ -1813,7 +1817,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1825,12 +1829,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>324164</t>
+          <t>311707</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21103</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1840,17 +1844,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA </t>
+          <t>JESUS ALONSO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUGO </t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1860,32 +1864,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6861322733</t>
+          <t>6866043202</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>QUIROZ 1228</t>
+          <t>EJIDO YUCATAN</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>04-10-1983</t>
+          <t>10-01-1996</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SAFRALU2020@GMAIL.COM</t>
+          <t>ALBERTO.ROCHAAAA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>18-11-2025 11:06:19</t>
+          <t>29-08-2025 14:24:08</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1910,17 +1914,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>10-03-2026 18:36:50</t>
+          <t>16-03-2026 19:12:02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>10-03-2026 17:10:12</t>
+          <t>16-03-2026 19:11:38</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1940,19 +1944,11 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26020523064850001873</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>MAGALI  ROJAS RIVAS</t>
-        </is>
-      </c>
+          <t>26020523232390002075</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1960,7 +1956,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1972,12 +1968,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>346598</t>
+          <t>335811</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88763</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1987,17 +1983,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ENRIQUE ISRAEL</t>
+          <t xml:space="preserve">LIDIETH ELENA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MOTA</t>
+          <t xml:space="preserve">GALAVIZ </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DE HOYOS</t>
+          <t>OBESO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2007,28 +2003,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6864042804</t>
+          <t>6861220189</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21-07-1979</t>
+          <t>30-04-1985</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
+          <t>LIDIETH.GALAVIZ0430@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>25-02-2026 19:49:07</t>
+          <t>19-01-2026 09:04:01</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2043,28 +2039,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:18</t>
+          <t>23-03-2026 09:04:41</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>22-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2075,7 +2071,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26020522860410001589</t>
+          <t>26020523419480002323</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2083,15 +2079,19 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>MAGALI ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2103,12 +2103,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>346036</t>
+          <t>276336</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>88201</t>
+          <t>73837</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2118,17 +2118,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SANDRA PAOLA</t>
+          <t>LUIS ARMANDO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2138,67 +2138,67 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6865244707</t>
+          <t>6644920547</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>08-08-2005</t>
+          <t>29-06-1996</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SANDRAPAOLASILVA08@GMAIL.COM</t>
+          <t>LUIS.DIAZHERRERA@GNP.COM.MX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23-02-2026 20:00:53</t>
+          <t>28-01-2025 19:51:50</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>05-03-2026 20:37:15</t>
+          <t>17-03-2026 19:34:46</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>05-03-2026 20:36:33</t>
+          <t>17-03-2026 19:33:31</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2218,44 +2218,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26020522931600001695</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>KATIA YOLANDA ACOSTA MARQUEZ</t>
-        </is>
-      </c>
+          <t>26030523270510003524</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347508</t>
+          <t>313295</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89673</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2265,17 +2257,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t xml:space="preserve">FERNANDO OMAR </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t xml:space="preserve"> TORREROS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2285,12 +2277,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6861060685</t>
+          <t>6862809692</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AV RIO CHAMPOTON</t>
+          <t>VILLA DEL BOSQUE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2300,17 +2292,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29-09-1958</t>
+          <t>09-07-1987</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SADUCA987@GMAILC.COM</t>
+          <t>OMARTB87FB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 11:27:00</t>
+          <t>08-09-2025 16:24:06</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2335,17 +2327,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 11:31:38</t>
+          <t>10-03-2026 21:08:25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 11:30:55</t>
+          <t>10-03-2026 21:06:57</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2365,7 +2357,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26020522789300001457</t>
+          <t>26020523072640001893</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2377,7 +2369,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2389,12 +2381,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347864</t>
+          <t>324164</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90029</t>
+          <t>21103</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2404,17 +2396,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KARYME ITALLETZY</t>
+          <t xml:space="preserve">SANDRA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">LUGO </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2424,12 +2416,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7331429496</t>
+          <t>6861322733</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>QUIROZ 1228</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2439,17 +2431,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>15-12-1994</t>
+          <t>04-10-1983</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>KARYME.ITA22@GMAIL.COM</t>
+          <t>SAFRALU2020@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 19:15:45</t>
+          <t>18-11-2025 11:06:19</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2474,17 +2466,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>04-03-2026 18:47:58</t>
+          <t>10-03-2026 18:36:50</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>04-03-2026 18:46:52</t>
+          <t>10-03-2026 17:10:12</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2504,7 +2496,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26020522895730001631</t>
+          <t>26020523064850001873</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2512,7 +2504,11 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>MAGALI  ROJAS RIVAS</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>549</t>
@@ -2520,7 +2516,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2532,12 +2528,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347972</t>
+          <t>347864</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90137</t>
+          <t>90029</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2547,17 +2543,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANYELI </t>
+          <t>KARYME ITALLETZY</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ALVARAN</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TABARES</t>
+          <t>SALINAS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2567,10 +2563,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6867931588</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>7331429496</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2578,56 +2578,64 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25-10-1986</t>
+          <t>15-12-1994</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANYELIALVARAN@GMAIL.COM</t>
+          <t>KARYME.ITA22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 08:46:32</t>
+          <t>02-03-2026 19:15:45</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 08:50:07</t>
+          <t>04-03-2026 18:47:58</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:46:52</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2635,19 +2643,23 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26020522833920001533</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+          <t>26020522895730001631</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2659,12 +2671,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347814</t>
+          <t>346598</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89979</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2674,17 +2686,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LYDIA MARGARITA</t>
+          <t>ENRIQUE ISRAEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>MOTA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>DE HOYOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2694,79 +2706,67 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6862028587</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6864042804</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>05-08-2000</t>
+          <t>21-07-1979</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LYDIAMAGUILAR05@GMAIL.COM</t>
+          <t>MOTTAENRIQUEISRAEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:16</t>
+          <t>25-02-2026 19:49:07</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>05-03-2026 18:33:12</t>
+          <t>03-03-2026 20:07:18</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>05-03-2026 18:32:34</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26020522927530001685</t>
+          <t>26020522860410001589</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2785,12 +2785,12 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347980</t>
+          <t>347508</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90145</t>
+          <t>89673</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2837,37 +2837,37 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6865499684</t>
+          <t>6861060685</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CASA DEL LAGO 379</t>
+          <t>AV RIO CHAMPOTON</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03-10-2003</t>
+          <t>29-09-1958</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
+          <t>SADUCA987@GMAILC.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 08:59:25</t>
+          <t>02-03-2026 11:27:00</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2877,27 +2877,27 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 09:07:48</t>
+          <t>02-03-2026 11:31:38</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>03-03-2026 09:07:02</t>
+          <t>02-03-2026 11:30:55</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26020522834400001534</t>
+          <t>26020522789300001457</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2941,12 +2941,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347805</t>
+          <t>347854</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89970</t>
+          <t>90019</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>CARLOS GABRIEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>BONILLA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>MELENDREZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2976,79 +2976,67 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6861960430</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6863672365</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>24-07-1997</t>
+          <t>13-09-2010</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ANGELINAMARGARITAT@GMAIL.COM</t>
+          <t>CARLOSBONILLA20000@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 18:18:19</t>
+          <t>02-03-2026 18:56:13</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>05-03-2026 18:26:25</t>
+          <t>06-03-2026 20:13:10</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>05-03-2026 18:25:28</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3056,7 +3044,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26020522927170001684</t>
+          <t>26020522961430001733</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3067,7 +3055,7 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3084,12 +3072,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347854</t>
+          <t>347814</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90019</t>
+          <t>89979</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3099,17 +3087,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CARLOS GABRIEL</t>
+          <t>LYDIA MARGARITA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BONILLA</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MELENDREZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3119,43 +3107,47 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6863672365</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6862028587</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13-09-2010</t>
+          <t>05-08-2000</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CARLOSBONILLA20000@GMAIL.COM</t>
+          <t>LYDIAMAGUILAR05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 18:56:13</t>
+          <t>02-03-2026 18:23:16</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3165,21 +3157,29 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>06-03-2026 20:13:10</t>
+          <t>05-03-2026 18:33:12</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:32:34</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26020522961430001733</t>
+          <t>26020522927530001685</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3215,12 +3215,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347901</t>
+          <t>347972</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90066</t>
+          <t>90137</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3230,17 +3230,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MANUEL</t>
+          <t xml:space="preserve">ANYELI </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>ALVARAN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>TABARES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3250,32 +3250,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4251279557</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6867931588</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>24-12-2003</t>
+          <t>25-10-1986</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MMIT7584@GMAIL.COM</t>
+          <t>ANYELIALVARAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 20:30:32</t>
+          <t>03-03-2026 08:46:32</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3285,44 +3281,36 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-03-2026 19:49:09</t>
+          <t>03-03-2026 08:50:07</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>04-03-2026 19:48:32</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3330,23 +3318,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26020522898370001644</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020522833920001533</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3358,12 +3342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347997</t>
+          <t>347901</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90162</t>
+          <t>90066</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3373,17 +3357,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NOEMI</t>
+          <t>MANUEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VERASTEGUI</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3393,67 +3377,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6861199558</t>
+          <t>4251279557</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AV DEL CARRIZO </t>
+          <t>N</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13-09-1962</t>
+          <t>24-12-2003</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MIMI_FLORESV@HOTMAIL.COM</t>
+          <t>MMIT7584@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 10:09:42</t>
+          <t>02-03-2026 20:30:32</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-03-2026 10:19:45</t>
+          <t>04-03-2026 19:49:09</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03-03-2026 10:19:01</t>
+          <t>04-03-2026 19:48:32</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3463,7 +3447,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3473,19 +3457,23 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26020522836240001536</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+          <t>26020522898370001644</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3497,12 +3485,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>348484</t>
+          <t>347805</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90649</t>
+          <t>89970</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3512,17 +3500,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ANDREA FERNANDA</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3532,12 +3520,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6864198624</t>
+          <t>6861960430</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AV LIMOLITA 1412</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3547,52 +3535,52 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18-11-1997</t>
+          <t>24-07-1997</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ANDREA_CERVANTES97@OUTLOOK.COM</t>
+          <t>ANGELINAMARGARITAT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>04-03-2026 16:32:06</t>
+          <t>02-03-2026 18:18:19</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-03-2026 16:55:15</t>
+          <t>05-03-2026 18:26:25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>09-03-2026 16:54:19</t>
+          <t>05-03-2026 18:25:28</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3602,7 +3590,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3612,7 +3600,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26020523015500001786</t>
+          <t>26020522927170001684</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3623,7 +3611,7 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3640,12 +3628,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348375</t>
+          <t>347997</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90540</t>
+          <t>90162</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3655,17 +3643,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DAYANA ESCARLET</t>
+          <t>NOEMI</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CUEN</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>VERASTEGUI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3675,10 +3663,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6531015715</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6861199558</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV DEL CARRIZO </t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3686,56 +3678,64 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>28-11-2000</t>
+          <t>13-09-1962</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>DAYANACUEN00@GMAIL.COM</t>
+          <t>MIMI_FLORESV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-03-2026 10:09:26</t>
+          <t>03-03-2026 10:09:42</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>06-03-2026 10:39:39</t>
+          <t>03-03-2026 10:19:45</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:19:01</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3743,27 +3743,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26020522946540001709</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
-        </is>
-      </c>
+          <t>26020522836240001536</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Eliazar Flores Vargas</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3906,12 +3898,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348830</t>
+          <t>349545</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90995</t>
+          <t>91710</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3921,17 +3913,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GUSTAVO ALFONSO</t>
+          <t>JOSE MANUEL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ZUÑIGA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CARAVEO</t>
+          <t>FONSECA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3941,10 +3933,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6641626298</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6861636263</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>POBLADO CERRO PRIETO</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3952,32 +3948,32 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>09-02-1980</t>
+          <t>27-10-1993</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TORRESCARAVEO@GMAIL.COM</t>
+          <t>JOSE011668@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>06-03-2026 05:50:48</t>
+          <t>09-03-2026 17:24:04</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3987,21 +3983,29 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>18-03-2026 05:04:47</t>
+          <t>09-03-2026 17:29:36</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:28:39</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4009,14 +4013,10 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26030523276420003546</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26020523017740001789</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Miguel Angel  Nava Correa</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4037,12 +4037,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>348765</t>
+          <t>349702</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90930</t>
+          <t>91867</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4052,17 +4052,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRUZ AZUCENA</t>
+          <t xml:space="preserve">ANAHI </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>JAIME</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>VALLE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6866055064</t>
+          <t>6863958644</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>RIO GAMBIA 3416</t>
+          <t>DE LOS ROCIOS NORTE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4087,17 +4087,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15-07-1976</t>
+          <t>24-11-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>SUSSYMORENO15@GMAIL.COM</t>
+          <t>ANAHIJAIME2004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>05-03-2026 17:15:43</t>
+          <t>09-03-2026 20:05:22</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-03-2026 17:49:38</t>
+          <t>09-03-2026 20:10:35</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09-03-2026 17:48:49</t>
+          <t>09-03-2026 20:09:47</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4152,14 +4152,10 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26020523019290001791</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020523030620001817</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4168,7 +4164,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4180,12 +4176,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>349545</t>
+          <t>348375</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>91710</t>
+          <t>90540</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4195,17 +4191,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSE MANUEL</t>
+          <t>DAYANA ESCARLET</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ZUÑIGA</t>
+          <t>CUEN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FONSECA</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4215,79 +4211,67 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6861636263</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>POBLADO CERRO PRIETO</t>
-        </is>
-      </c>
+          <t>6531015715</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>27-10-1993</t>
+          <t>28-11-2000</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>JOSE011668@HOTMAIL.COM</t>
+          <t>DAYANACUEN00@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-03-2026 17:24:04</t>
+          <t>04-03-2026 10:09:26</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-03-2026 17:29:36</t>
+          <t>06-03-2026 10:39:39</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>09-03-2026 17:28:39</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4295,19 +4279,27 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26020523017740001789</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26020522946540001709</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Eliazar Flores Vargas</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4319,12 +4311,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>349702</t>
+          <t>349586</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>91867</t>
+          <t>91751</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4334,17 +4326,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANAHI </t>
+          <t>MONICA ARIANNE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JAIME</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VALLE</t>
+          <t>CORRAL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4354,14 +4346,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6863958644</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>DE LOS ROCIOS NORTE</t>
-        </is>
-      </c>
+          <t>6863991702</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4369,64 +4357,52 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24-11-2004</t>
+          <t>01-05-2011</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ANAHIJAIME2004@GMAIL.COM</t>
+          <t>MONIE.88@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-03-2026 20:05:22</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>09-03-2026 18:02:49</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-03-2026 20:10:35</t>
+          <t>25-03-2026 18:08:56</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>09-03-2026 20:09:47</t>
-        </is>
-      </c>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4434,14 +4410,22 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26020523030620001817</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>26020523510830002483</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4458,12 +4442,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>349866</t>
+          <t>348830</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>92031</t>
+          <t>90995</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4473,17 +4457,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ILEANA</t>
+          <t>GUSTAVO ALFONSO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PRECIADO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CARAVEO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4493,28 +4477,28 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6862023698</t>
+          <t>6641626298</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10-08-2005</t>
+          <t>09-02-1980</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PRECIADOILEANA631@GMAIL.COM</t>
+          <t>TORRESCARAVEO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10-03-2026 15:02:44</t>
+          <t>06-03-2026 05:50:48</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4539,12 +4523,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>10-03-2026 15:04:04</t>
+          <t>18-03-2026 05:04:47</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4561,10 +4545,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26020523054260001855</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
+          <t>26030523276420003546</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4573,7 +4561,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Miguel Angel  Nava Correa</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4585,12 +4573,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>349884</t>
+          <t>349866</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>92049</t>
+          <t>92031</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4600,17 +4588,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DANIELA GUADALUPE</t>
+          <t>ILEANA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AHUMADA</t>
+          <t>PRECIADO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4620,7 +4608,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6861888423</t>
+          <t>6862023698</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4631,17 +4619,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>13-11-1985</t>
+          <t>10-08-2005</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>AHUMADARAMIREZDANIELA@GMAIL.COM</t>
+          <t>PRECIADOILEANA631@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-03-2026 16:14:56</t>
+          <t>10-03-2026 15:02:44</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4666,7 +4654,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-03-2026 16:19:11</t>
+          <t>10-03-2026 15:04:04</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4688,7 +4676,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26020523056700001862</t>
+          <t>26020523054260001855</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4700,7 +4688,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4712,12 +4700,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>349855</t>
+          <t>349884</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>92020</t>
+          <t>92049</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4727,17 +4715,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA ISELA </t>
+          <t>DANIELA GUADALUPE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>AHUMADA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4747,14 +4735,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6861907163</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>CASCADA DE LA BALSA 4356</t>
-        </is>
-      </c>
+          <t>6861888423</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4762,42 +4746,42 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30-09-1991</t>
+          <t>13-11-1985</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DR084861@GMAIL.COM</t>
+          <t>AHUMADARAMIREZDANIELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-03-2026 14:28:30</t>
+          <t>10-03-2026 16:14:56</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10-03-2026 14:41:30</t>
+          <t>10-03-2026 16:19:11</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4805,21 +4789,13 @@
           <t>09-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>10-03-2026 14:36:33</t>
-        </is>
-      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4827,19 +4803,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26020523053430001852</t>
+          <t>26020523056700001862</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Jesus Antonio Arroyo Alvarez</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4851,12 +4827,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>350678</t>
+          <t>349855</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>92842</t>
+          <t>92020</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4866,17 +4842,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t xml:space="preserve">DANIA ISELA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BALERA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4886,28 +4862,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7621155727</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6861907163</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CASCADA DE LA BALSA 4356</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>25-05-1989</t>
+          <t>30-09-1991</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BALERAARQ@GMAIL.COM</t>
+          <t>DR084861@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>13-03-2026 19:24:26</t>
+          <t>10-03-2026 14:28:30</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4917,36 +4897,44 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16-03-2026 13:21:25</t>
+          <t>10-03-2026 14:41:30</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>10-03-2026 14:36:33</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4954,23 +4942,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26020523221350002047</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020523053430001852</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5236,12 +5220,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>349979</t>
+          <t>347980</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>92144</t>
+          <t>90145</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5251,17 +5235,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OMAR ULISES</t>
+          <t xml:space="preserve">DIANA LAURA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5271,37 +5255,37 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6681903519</t>
+          <t>6865499684</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>CASA DEL LAGO 379</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17-05-1990</t>
+          <t>03-10-2003</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ULISESACOSTA1790@GMAIL.COM</t>
+          <t>DIANAQUINTEROMONTOYA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-03-2026 19:10:24</t>
+          <t>03-03-2026 08:59:25</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5311,27 +5295,27 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO PLAN ULTRA PAGO INCIAL 12 MESES $1,449</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>12-03-2026 18:41:50</t>
+          <t>03-03-2026 09:07:48</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>12-03-2026 18:41:18</t>
+          <t>03-03-2026 09:07:02</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5351,27 +5335,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26020523132200001971</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
-        </is>
-      </c>
+          <t>26020522834400001534</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Arturo Israel  Flores Oronia</t>
+          <t>Jesus Antonio Arroyo Alvarez</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5661,12 +5637,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>350676</t>
+          <t>348484</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>92840</t>
+          <t>90649</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5676,17 +5652,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE </t>
+          <t>ANDREA FERNANDA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BALERA</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5696,67 +5672,79 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7778923229</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6864198624</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>AV LIMOLITA 1412</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>12-12-1998</t>
+          <t>18-11-1997</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BALERAJOSE.27@GMAIL.COM</t>
+          <t>ANDREA_CERVANTES97@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>13-03-2026 19:21:14</t>
+          <t>04-03-2026 16:32:06</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>16-03-2026 13:18:23</t>
+          <t>09-03-2026 16:55:15</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>15-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:54:19</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5764,7 +5752,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26020523221210002046</t>
+          <t>26020523015500001786</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5775,12 +5763,12 @@
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>Arturo Israel  Flores Oronia</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5792,12 +5780,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>351309</t>
+          <t>351760</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>93473</t>
+          <t>93924</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5807,17 +5795,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">NANCY ALEXANDRA </t>
+          <t>LUIS LEONARDO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>DE LEON</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>VALDES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5827,32 +5815,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6863358342</t>
+          <t>6863164327</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PITAYA160</t>
+          <t>RIO MEZCALAPA 3677</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>24-03-1994</t>
+          <t>24-09-2008</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ALEXAESQUIVEL2403@GMAIL.COM</t>
+          <t>LEONARDO.24DELEON2008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>16-03-2026 18:46:54</t>
+          <t>18-03-2026 08:25:13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5877,17 +5865,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-03-2026 21:53:31</t>
+          <t>18-03-2026 08:32:57</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>17-03-2026 21:52:37</t>
+          <t>18-03-2026 08:31:57</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5907,14 +5895,10 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26020523276060002160</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26020523285970002167</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
@@ -5935,12 +5919,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>351996</t>
+          <t>350678</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>92842</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5950,17 +5934,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AGUSTIN ELIEZER</t>
+          <t>FRANCISCO JAVIER</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RUBIO</t>
+          <t>BALERA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BARRAGAN</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5970,14 +5954,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6862591682</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>7621155727</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5985,64 +5965,56 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>16-11-1989</t>
+          <t>25-05-1989</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ELIEZZERUB@GMAIL.COM</t>
+          <t>BALERAARQ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>18-03-2026 20:12:20</t>
+          <t>13-03-2026 19:24:26</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>18-03-2026 20:17:59</t>
+          <t>16-03-2026 13:21:25</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>18-03-2026 20:16:39</t>
-        </is>
-      </c>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6050,36 +6022,40 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26020523309280002213</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>26020523221350002047</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>351760</t>
+          <t>350676</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>93924</t>
+          <t>92840</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6089,17 +6065,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO</t>
+          <t xml:space="preserve">JOSE </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DE LEON</t>
+          <t>BALERA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>VALDES</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6109,14 +6085,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6863164327</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>RIO MEZCALAPA 3677</t>
-        </is>
-      </c>
+          <t>7778923229</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6124,64 +6096,56 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>24-09-2008</t>
+          <t>12-12-1998</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LEONARDO.24DELEON2008@GMAIL.COM</t>
+          <t>BALERAJOSE.27@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18-03-2026 08:25:13</t>
+          <t>13-03-2026 19:21:14</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>18-03-2026 08:32:57</t>
+          <t>16-03-2026 13:18:23</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>18-03-2026 08:31:57</t>
-        </is>
-      </c>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6189,14 +6153,18 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26020523285970002167</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
+          <t>26020523221210002046</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6213,12 +6181,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>350913</t>
+          <t>351309</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>93077</t>
+          <t>93473</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6228,17 +6196,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">AARON </t>
+          <t xml:space="preserve">NANCY ALEXANDRA </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CAÑEDO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LAFARGA</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6248,32 +6216,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6863917755</t>
+          <t>6863358342</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DFTG</t>
+          <t>PITAYA160</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>21-12-1987</t>
+          <t>24-03-1994</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>AARONCANEDO2@GMAIL.COM</t>
+          <t>ALEXAESQUIVEL2403@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>15-03-2026 13:16:02</t>
+          <t>16-03-2026 18:46:54</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6298,17 +6266,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-03-2026 17:24:28</t>
+          <t>17-03-2026 21:53:31</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>16-03-2026 17:23:59</t>
+          <t>17-03-2026 21:52:37</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6328,10 +6296,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26010523228600006747</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
+          <t>26020523276060002160</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
@@ -6340,7 +6312,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Eduardo  Rivera Ramirez</t>
+          <t>Manuel Moreno Del Bosque</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6352,12 +6324,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>351979</t>
+          <t>351889</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>94143</t>
+          <t>94053</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6367,17 +6339,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLISERIA </t>
+          <t>PERLA JOSSEL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6387,14 +6359,10 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6862822480</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>6864320545</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6402,32 +6370,32 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>21-12-1971</t>
+          <t>30-08-2008</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>GLISLUNA2171@GMAIL.COM</t>
+          <t>PERLAJOSSELLOPEZLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>18-03-2026 19:50:11</t>
+          <t>18-03-2026 17:08:29</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6437,29 +6405,21 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>18-03-2026 19:56:30</t>
+          <t>23-03-2026 17:32:39</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>18-03-2026 19:54:34</t>
-        </is>
-      </c>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6467,11 +6427,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26020523308150002207</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+          <t>26020523435890002359</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>549</t>
@@ -6491,12 +6459,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>351396</t>
+          <t>351979</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>93560</t>
+          <t>94143</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6506,17 +6474,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ESAU</t>
+          <t xml:space="preserve">GLISERIA </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TORRES RETAMOZA</t>
+          <t>LUNA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TORRES RETAMOZA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6526,34 +6494,42 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6861644228</t>
+          <t>6862822480</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>av chila 781</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>31-12-9999</t>
+          <t>21-12-1971</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ing.yaneth.nunez@gmail.com</t>
+          <t>GLISLUNA2171@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-03-2026 23:50:25</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>18-03-2026 19:50:11</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6568,21 +6544,29 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16-03-2026 23:50:26</t>
+          <t>18-03-2026 19:56:30</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>18-03-2026 19:54:34</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6590,7 +6574,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26020523236460002092</t>
+          <t>26020523308150002207</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6602,139 +6586,2978 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Manuel Moreno Del Bosque</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>349581</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>91746</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MONICA </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CORRAL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>RUBIO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6862459334</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>09-01-1988</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>MONICA.CORRAL0105@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:00:14</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:08:56</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:07:31</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26020523510830002483</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>348765</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>90930</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CRUZ AZUCENA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6866055064</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>RIO GAMBIA 3416</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>15-07-1976</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>SUSSYMORENO15@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:15:43</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:49:38</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:48:49</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26020523019290001791</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>351893</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>94057</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MONSERRAT </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ARREDONDO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6863841310</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>14-08-2008</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>MONSERRATARREDONDO47@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:13:09</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>23-03-2026 16:32:32</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26020523432320002347</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>351996</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>94160</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AGUSTIN ELIEZER</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RUBIO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BARRAGAN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6862591682</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>16-11-1989</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>ELIEZZERUB@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:12:20</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:17:59</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:16:39</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26020523309280002213</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>351990</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>94154</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISELA </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6862097962</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>06-09-1975</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>ISELACHAVEZLEON1975@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:08:29</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>27-03-2026 20:13:41</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>26-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26020523575640002584</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>349979</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>92144</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>OMAR ULISES</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MONTES</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ACOSTA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6681903519</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>17-05-1990</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>ULISESACOSTA1790@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:10:24</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:41:50</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:41:18</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26020523132200001971</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>PERLA ANGELICA LILIAN GAYTAN SOLIS</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>352666</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>94830</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDGAR </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">URRIETA </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>AMADO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>5535869657</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>RIO COATZACOALCOS 2378</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>05-08-1984</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>EDURAM84@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>23-03-2026 08:36:49</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>23-03-2026 08:41:02</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>23-03-2026 08:40:27</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26020523418880002320</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>352675</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>94839</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ARACELI DAYANE</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUIRRE </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6861333835</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>MALVAS 960</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>04-12-1995</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>AGUIRREARACELI0@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:05:01</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:18:30</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:17:38</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26020523419960002326</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>353167</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>95331</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ELIAS III</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CONTRERAS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BARAJAS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6864414365</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>24-10-2007</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ELIASLLL247@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>24-03-2026 17:50:59</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>24-03-2026 17:53:36</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26020523475920002433</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>352676</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>94840</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>KEVIN ALEXIS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAÑUELOS </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>VALTIERRA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6861755308</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>MALVAS 960</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>13-11-1994</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>KEVIN.BANUELOS@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:07:08</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:34:44</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:34:01</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26020523420360002329</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>353277</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>95441</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BRANDON ALFREDO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>FIERRO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6863156243</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>27-03-2006</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>BARONSAMEDI1921@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>25-03-2026 08:29:01</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>25-03-2026 08:31:03</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26020523495760002468</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>353267</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>95431</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>THAYDEE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ACUÑA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6867729763</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>08-08-2008</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>THAYDEEMORALES305@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>25-03-2026 07:08:54</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>27-03-2026 07:27:13</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26020523558240002555</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>352824</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>94988</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>KASSANDRA MARISELA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ARREDONDO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6861949286</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>15-02-2004</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>KASSANDRAARRESAN46@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>23-03-2026 16:35:44</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:09:36</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:08:50</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26020523507550002478</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>354330</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>96494</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIZALDE </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ORTEGA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6861906454</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>18-09-2001</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>ELIZALDE.ALEJANDRA09@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:40:17</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:41:46</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26020523638600002649</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>353440</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>95604</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALIA </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>BOLAÑOS</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6862287209</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>21-12-2009</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>02405555@COBACHBC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>25-03-2026 19:01:26</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>25-03-2026 19:03:29</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26020523513950002489</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>350913</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>93077</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AARON </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CAÑEDO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>LAFARGA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6863917755</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>DFTG</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>21-12-1987</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>AARONCANEDO2@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>15-03-2026 13:16:02</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:24:28</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>16-03-2026 17:23:59</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26010523228600006747</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Eduardo  Rivera Ramirez</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>351396</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>93560</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ESAU</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>TORRES RETAMOZA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>TORRES RETAMOZA</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6861644228</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>av chila 781</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>31-12-9999</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ing.yaneth.nunez@gmail.com</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:50:25</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:50:26</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26020523236460002092</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Manuel Moreno Del Bosque</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>351757</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>93921</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>VILLA VERDE</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>IRMA BEATRIZ</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>RAMOS</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>GONZALEZ</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>6731001122</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>24-12-1970</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>RAGI171@HOTMAIL.COM</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>18-03-2026 08:01:28</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Tarifas 2026 LE</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Sin contrato</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>1 MES $899</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>899</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>18-03-2026 08:03:40</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>17-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr">
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>26020523285130002166</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr">
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
         <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>Eliazar Flores Vargas</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>352275</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>94439</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>JOSE JESUS</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ARROYO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>FRAGA</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6864620459</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>RIO SANTA MARIA 2471</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>22-05-1978</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>ARROYOFRAGAJOSEJESUS22051978@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>20-03-2026 10:36:21</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>20-03-2026 10:49:43</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>19-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>20-03-2026 10:46:03</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26020523361570002281</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Jesus Antonio Arroyo Alvarez</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>353269</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>95433</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>KARLA ALEXANDRA</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NORIEGA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ROSALES</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6863999249</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>26-11-2008</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>KARLAROSALES8080@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>25-03-2026 07:14:23</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>27-03-2026 07:28:55</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26020523558260002556</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Eliazar Flores Vargas</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>353435</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>95599</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LEIMY XIOMARA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6464138229</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>30-12-2009</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>LEIMYXRMTZ@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:57:21</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:59:13</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26020523513600002488</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Arturo Israel  Flores Oronia</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>353607</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>95771</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VILLA VERDE</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDUARDO </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LIZARDI</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>BALLESTEROS</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6861934041</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>25-12-1983</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>LIC.ELIZARDI@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>26-03-2026 17:39:53</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>30-03-2026 14:26:07</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>30-03-2026 14:25:31</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26020523629960002631</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
